--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D443"/>
+  <dimension ref="A1:D449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7980,6 +7980,108 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_teams</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>チームを組める</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Players can be in teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_teams</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>プレイヤーはチームに入れる。誰がどのチームかはホストのセーブに残る。チームのないプレイヤーは放浪者。オフ：チームはなく、以前どおり</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Players can be in teams, the host keeps who is in which team in its save. A player in no team is a Wanderer. Off: no teams, everything as before</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_bases</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>拠点はチームのもの</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>A base belongs to its team</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_bases</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>拠点は権利書を読んだプレイヤーのチームのもの。ほかのチームのプレイヤーはそこで箱を開けられず、物を拾えず、建築も拠点の管理もできない。オフ：以前どおり誰でもどの拠点も使える</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>A base belongs to the team of the player who claimed it: the players of another team cannot open its chests, pick up its things, build there or manage it. Off: every player uses every base as before</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>emp_team_belongs</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>これは{0}のものだ。</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>This belongs to {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>emp_team_wanderers</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>放浪者</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>the Wanderers</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8082,6 +8082,40 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_pvp</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>チーム間のPvP</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>PvP between teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_pvp</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>異なるチームのプレイヤーは、町とスポーン地点の外では互いに敵になる。放浪者は誰とも戦わない。プレイヤーが本当に死ぬのは「プレイヤー同士で倒せる」がオンのときだけ。オフ：異なるチームのプレイヤーは戦えない</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Players of different teams are enemies to each other outside towns and the spawn zone. Wanderers fight nobody. A player only really dies if players can kill each other. Off: players of different teams cannot fight</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8082,6 +8082,159 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_approval</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>チームに入るにはリーダーの承認が必要</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Joining a team needs its leader's approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_approval</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>チームに入りたいプレイヤーはリーダーを待つ。リーダーはプレイヤー一覧で承認か拒否を選ぶ。オフ：すぐに入れる</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>A player who asks to join a team waits for its leader, who accepts or refuses in the list of players. Off: a player joins at once</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>emp_team_found</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>チームを結成する</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Found a team</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>emp_team_join</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>{0}に入る</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Join {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>emp_team_leave</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>{0}を抜ける</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Leave {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>emp_team_accept</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>{0}を受け入れる</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Accept {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>emp_team_refuse</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>{0}を断る</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Refuse {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>emp_team_now</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>あなたは今{0}にいる。</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>You are now with {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>emp_team_asks</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>{0}が{1}に入りたがっている。</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>{0} asks to join {1}.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D458"/>
+  <dimension ref="A1:D465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8235,6 +8235,125 @@
         </is>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_deed</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>新しいチームに権利書を1枚</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>A land deed for a new team</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_deed</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>新しいチームを作ったプレイヤーは土地の権利書を1枚もらう。チームごとに1回、プレイヤーごとに1回。オフ：権利書はゲームどおり商人から買う</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>The player who founds a new team receives one land deed, once per team and once per player. Off: a deed is bought from the merchant as in the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_spawn_zone</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>新しいプレイヤーが現れる場所</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Where a new player appears</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_spawn_zone</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>チームがあるとき、新しいプレイヤーと拠点のないチームのプレイヤーは参加するとここへ向かう（一人旅が必要）</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>With teams, a new player and a player whose team has no base go there when they join (needs travelling alone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_spawn_zone_start</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>始まりの草原</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>The meadow where a game starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_spawn_zone_host</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>ホストのいるマップ</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>The host's map</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>emp_team_deed_mail</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>{0}のチームの権利書</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>{0}'s team deed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D465"/>
+  <dimension ref="A1:D468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8354,6 +8354,57 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_personal</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>チームの中でも自分の物を持てる</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Personal ownership inside a team</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_personal</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>チームの土地にプレイヤーが置いた箱・扉・ベッドはそのプレイヤーのもの。仲間は箱を開けて中を見られるが取れず、扉は通れない。メニューの「チームと共有」でチームのものに戻る。オフ：チームの土地の物はチーム全員のもの</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>A chest, door or bed a player installs on its team's land is that player's: teammates open the chest and see inside but cannot take, and cannot pass the door. "Share with team" in its menu gives it back to the team. Off: what is on a team's land is the whole team's</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>emp_team_share</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>チームと共有</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Share with team</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D470"/>
+  <dimension ref="A1:D472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8439,6 +8439,40 @@
         </is>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_public_game</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>公開ゲーム</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Public game</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_public_game</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>ゲーム一覧で見つけた人は誰でも参加できる（ホストのSteamフレンドや招待されたプレイヤーだけでなく）。自動で開いたゲーム（保管庫、共有ワールド）はそのワールドのプレイヤーだけ。オフ：フレンドと招待されたプレイヤーのみ</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Anybody who finds the game in the list of games can join, not only the host's Steam friends and invited players. A game opened by itself (depot, shared world) still lets in only its world's players. Off: friends and invited players only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D472"/>
+  <dimension ref="A1:D474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8473,6 +8473,40 @@
         </is>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_look_mods_own</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>見た目だけのModは各自のもの</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Look-only mods: each player's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_look_mods_own</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>見た目だけを変えるMod（画像、肖像、音、翻訳：コード、アイテム、マップなし）は参加者に求められない：そのために再起動する人はおらず、各プレイヤーは自分のものを使い続ける。オフ：参加者はホストのすべてのModが必要</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Mods that only change the look (pictures, portraits, sounds, translations: no code, no items, no maps) are not asked of the players who join: nobody restarts for them, and every player keeps their own. Off: the players who join need every mod of the host</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D474"/>
+  <dimension ref="A1:D475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8507,6 +8507,23 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>emp_team_beaten</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>{0}は{1}に敗れた。</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>{0} was beaten by {1}.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D475"/>
+  <dimension ref="A1:D486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8524,6 +8524,193 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_characters</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>参加するキャラクター</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Characters of joining friends</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_characters</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>新しいキャラ：毎回新しく作ります。自分のキャラを選ぶ：この世界の自分のキャラを選ぶか、新しく作ります。選ぶか連れてくる：自分のセーブからキャラ（装備、バッグ、お金、名声とカルマ）を連れてくることもできます。</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>New character: a new one each time. Pick one of yours: one of their characters in this world, or a new one. Pick or bring one: also a character from their own saves (gear, bag, gold, fame and karma; the save is never changed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_characters_new</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>新しいキャラ</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>New character</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_characters_pick</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>自分のキャラを選ぶ</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Pick one of yours</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_characters_both</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>選ぶか連れてくる</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Pick or bring one</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_travel</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>旅</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_travel</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>一緒に：全員がホストについていきます。一人で、共有時計：好きな場所へ行けて、ワールドマップで誰かが一歩進むたびに日付が進みます。一人で、自分のペース：同じですが、一人で旅するプレイヤーは世界より先に進み、その時間は本人の満腹度とクエストが払います。</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Together: everyone follows the host. Alone, shared clock: players go anywhere; every step of anyone on the world map moves the date. Alone, own pace: the same, but a player travelling alone runs ahead of the world: its hunger and its own quests pay the hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_travel_together</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>一緒に</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Together</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_travel_alone</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>一人で、共有時計</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Alone, shared clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_travel_own_pace</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>一人で、自分のペース</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Alone, own pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_friends</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>友人はホストと同じことができる</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Friends can do what the host does</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9510" yWindow="2685" windowWidth="31695" windowHeight="18195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D486"/>
+  <dimension ref="A1:D487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>プレイヤー {@Peer} が接続しました</t>
+          <t>{0}がゲームに参加しました。</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Player {@Peer} connected</t>
+          <t>{0} joined the game.</t>
         </is>
       </c>
     </row>
@@ -1190,14 +1190,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>プレイヤー {@Peer} が切断しました
-{DisconnectInfo}</t>
+          <t>{0}がゲームから退出しました。</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Player {@Peer} disconnected
-{DisconnectInfo}</t>
+          <t>{0} left the game.</t>
         </is>
       </c>
     </row>
@@ -8711,6 +8709,23 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>emp_player_someone</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>プレイヤー</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>A player</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -884,12 +884,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>遅延: {0}ms{1}</t>
+          <t>遅延 {0} ms{1}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ping: {0}ms{1}</t>
+          <t>Ping {0} ms{1}</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>遅延: N/A（ホスト）</t>
+          <t>遅延 - （ホスト）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ping: N/A (Host)</t>
+          <t>Ping - (Host)</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 品質: {0}</t>
+          <t>, 品質 {0}%</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Quality: {0}</t>
+          <t>, Quality {0}%</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4909,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>参加するゲームのMODで足りない Workshop のものを、購読せずにダウンロードします。Elin は一度再起動し、自動でゲームに戻ります。MOD一覧は次の起動で元に戻ります。オフ：違うMODを知らせるだけ。</t>
+          <t>参加するゲームに足りない Workshop の MOD を、購読せずにダウンロードします。Elin は一度再起動します。</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Missing Workshop mods of the game you join are downloaded without subscribing. Elin restarts once with those mods and comes back by itself. Your own list returns at the next start. Unticked, you are only told which mods differ.</t>
+          <t>Downloads the Workshop mods you lack for the game you join, without subscribing. Elin restarts once.</t>
         </is>
       </c>
     </row>
@@ -5147,12 +5147,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>参加するゲームのMODを Steam アカウントで購読し、自分のMOD一覧に残します。最初の一度だけ再起動し、以降は Elin を閉じても再起動なしで同じゲームに入れます。取り消すには Workshop で購読を解除します。オフ：購読せず取得し、起動後の最初の参加で毎回再起動します。</t>
+          <t>参加するゲームの MOD を Steam で購読し、次からは再起動なしで参加できます。</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Your Steam account subscribes to the mods of the game you join and keeps them on. Elin restarts once, the first time. After that you rejoin the same game with no restart. To undo, unsubscribe on the Workshop. Unticked, Elin restarts at the first join of every start.</t>
+          <t>Subscribes to the game's mods on Steam, so you can rejoin without restarting.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>遅延 - （ホスト）</t>
+          <t>遅延 -（ホスト）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>, 品質 {0}%</t>
+          <t>、品質 {0}%</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D487"/>
+  <dimension ref="A1:D477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Connected Players</t>
+          <t>Connected players</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ping - (Host)</t>
+          <t>Ping - (host)</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Game Info</t>
+          <t>Game info</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Invite Friend</t>
+          <t>Invite a friend</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Start Server</t>
+          <t>Start server</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bind Ping Key: {0}</t>
+          <t>Bind ping key: {0}</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Client Settings</t>
+          <t>Client settings</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>出荷はプレイヤーごと</t>
+          <t>出荷のお金は出荷した人に</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Shipping per player</t>
+          <t>Shipping pays the player who ships</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>戦闘はプレイヤーごとの時間で</t>
+          <t>モンスターはプレイヤーごとのペースで動く</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Combat at each player's pace</t>
+          <t>Monsters act at each player's pace</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>依頼・名声・カルマはプレイヤーごと</t>
+          <t>クエストはプレイヤーごと</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Quests, fame and karma per player</t>
+          <t>Each player has their own quests</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Friends choose a character when they join</t>
+          <t>Friends pick a character when joining</t>
         </is>
       </c>
     </row>
@@ -2601,1132 +2601,1064 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_players</t>
+          <t>emp_ui_sv_desc_choose_chara</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>プレイヤーと移動</t>
+          <t>参加するとき、この世界での自分のキャラを選ぶか、新しく作ります。オフ：毎回新しいキャラを作ります。</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Players and travel</t>
+          <t>Friends pick one of their characters in this world, or make a new one. Off: they make a new character each time.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_own</t>
+          <t>emp_ui_sv_desc_independent_travel</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>プレイヤーごとのもの</t>
+          <t>好きな場所へ、ひとりでも仲間とでも行けます。オフ：全員がホストについていきます。</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>One for each player</t>
+          <t>Players go anywhere, alone or together. Off: everyone follows the host.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_time</t>
+          <t>emp_ui_sv_desc_personal_quests</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>時間と戦闘</t>
+          <t>依頼は1人5件ずつ。報酬・名声・カルマも別々で、ストーリーは共通です。オフ：元のゲームと同じ。</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Time and combat</t>
+          <t>Each player gets 5 quests, with their own reward, fame and karma; story quests stay shared. Off: as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_checks</t>
+          <t>emp_ui_sv_desc_player_shipping</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>参加チェック</t>
+          <t>出荷箱のお金は、入れたプレイヤーのものになります。オフ：すべてホストへ（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Joining checks</t>
+          <t>Shipping money goes to the player who put the item in. Off: the host gets it all, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_choose_chara</t>
+          <t>emp_ui_sv_desc_player_trade</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>参加するとき、この世界での自分のキャラを選ぶか、新しく作ります。</t>
+          <t>ほかのプレイヤーをクリックすると、アイテムやお金を取引できます。双方の確認が必要です。</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Joining players pick one of their characters in this world, or make a new one.</t>
+          <t>Click another player to trade items and gold; both must confirm.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_independent_travel</t>
+          <t>emp_ui_sv_desc_combat_time</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>好きな場所へ、ひとりでも仲間とでも行けます。オフ：全員がホストについていきます。</t>
+          <t>モンスターは、戦っているプレイヤーが動くときに動き、誰も待ちません。ターン制より優先されます。オフ：ターン制と平均速度の設定で決まります。</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Players can go anywhere, alone or together. Unticked, everyone follows the host.</t>
+          <t>A monster acts when the player it fights acts, so nobody waits; this comes before turn-based combat. Off: the turn-based and average speed boxes decide.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_personal_quests</t>
+          <t>emp_ui_sv_desc_turn_combat</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>依頼は1人5件ずつ。報酬・名声・カルマも別々です。ストーリーは共通です。</t>
+          <t>戦闘中、プレイヤーは順番に行動します。「モンスターはプレイヤーごとのペースで動く」がオンの間は何もしません。</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Each player gets 5 quests, with their own reward, fame and karma. Story quests stay shared.</t>
+          <t>In a fight, players take turns. Does nothing while "Monsters act at each player's pace" is on.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_shipping</t>
+          <t>emp_ui_sv_desc_shared_speed</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>出荷箱のお金は、入れたプレイヤーのものに。オフ：すべてホストへ。</t>
+          <t>全員が平均の速さで動きます。オフ：それぞれの速さのまま。</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Shipping money goes to the player who put the item in. Unticked, the host gets it all.</t>
+          <t>Everyone moves at the average speed. Off: each keeps their own.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_trade</t>
+          <t>emp_ui_sv_desc_validation</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーをクリックすると、アイテムやお金を取引できます。双方の確認が必要です。</t>
+          <t>友人のゲームがホストと同じでなければならないもの。なし：誰でも参加できます。ソース：同じゲームデータ。プラグイン：同じMOD。すべて：同じデータ、MOD、ゲームファイル。「なし」と「すべて」は他と組み合わせられません。</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Click another player to trade items and gold. Both must confirm.</t>
+          <t>What a friend's game must share with the host's. None: anyone can join. Source: the same game data. Plugin: the same mods. All: the same data, mods and game files. None and All cannot be combined.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_combat_time</t>
+          <t>emp_ui_sv_cfg_player_clock</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>モンスターは、戦っているプレイヤーが動くときに動きます。誰も待ちません。ターン制より優先されます。</t>
+          <t>プレイヤーごとの時間で動く</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>A monster acts when the player it fights acts. Nobody waits. This comes before turn-based combat.</t>
+          <t>Each player moves at their own pace</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_turn_combat</t>
+          <t>emp_ui_sv_desc_player_clock</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>戦闘中、プレイヤーは順番に行動します。各自のペースの戦闘がオンの間は何もしません。</t>
+          <t>友人もホストと同じように滑らかに動きます。「モンスターはプレイヤーごとのペースで動く」が必要です。</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>In a fight, players take turns. Does nothing while combat at each player's pace is on.</t>
+          <t>Friends move as smoothly as the host. Needs "Monsters act at each player's pace".</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_speed</t>
+          <t>emp_ui_sv_cfg_step_pace</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>全員が平均の速さで動きます。オフ：それぞれの速さのまま。</t>
+          <t>全員がひとり用の速さで歩く</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Everyone moves at the average speed. Unticked, each keeps their own.</t>
+          <t>Everyone walks as in a solo game</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_validation</t>
+          <t>emp_ui_sv_desc_step_pace</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>参加するプレイヤーのゲームがあなたと同じでなければならないもの。「なし」：誰でも。「すべて」：同じデータとMOD。「なし」と「すべて」は単独で選びます。</t>
+          <t>歩く速さが、ほかのプレイヤーの速さに左右されません（戦闘では速さが効きます）。「モンスターはプレイヤーごとのペースで動く」が必要です。</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods. None and All stand alone.</t>
+          <t>A step no longer depends on the others' speed; speed still counts in fights. Needs "Monsters act at each player's pace".</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_clock</t>
+          <t>emp_ui_sv_cfg_import_chara</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>プレイヤーごとの時間で動く</t>
+          <t>友人はセーブのキャラクターを連れてこられる</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Each player moves at their own pace</t>
+          <t>Friends can bring a saved character</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_clock</t>
+          <t>emp_ui_sv_desc_import_chara</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>友人もホストと同じように滑らかに動きます。各自のペースの戦闘が必要です。</t>
+          <t>自分のセーブから、キャラ本人、装備、バッグ、お金、名声とカルマを連れてきます（仲間、拠点、依頼、銀行は含まず、セーブは変更されません）。オフ：連れてこられません。</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Friends move as smoothly as the host. Needs combat at each player's pace.</t>
+          <t>Friends bring the character, gear, bag, gold, fame and karma from their own saves, never changing them; not companions, base, quests or bank. Off: they cannot.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_step_pace</t>
+          <t>emp_ui_chara_import</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>全員がひとり用の速さで歩く</t>
+          <t>自分のセーブのキャラ…</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Everyone walks as in a solo game</t>
+          <t>A character from my saves…</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_step_pace</t>
+          <t>emp_ui_chara_import_pick</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>歩く速さが、ほかのプレイヤーの速さに左右されません。戦闘では速さが効きます。「戦闘はプレイヤーごとの時間で」が必要です。</t>
+          <t>どのセーブのキャラを連れてきますか？（セーブは変更されません）</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>A step no longer depends on the others' speed. Speed still counts in a fight. Needs "Combat at each player's pace".</t>
+          <t>Which save? It will not be changed.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_import_chara</t>
+          <t>emp_ui_chara_import_back</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>友人は自分のセーブからキャラクターを連れてこられる</t>
+          <t>戻る</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Friends can bring a character from their own saves</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_import_chara</t>
+          <t>emp_ui_chara_import_none</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>キャラ本人、装備、バッグ、お金、名声とカルマ。仲間、拠点、依頼、銀行は含みません。セーブは読むだけで、変更されません。</t>
+          <t>読み込めるセーブが見つかりません。</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>The character, gear, bag, gold, fame and karma. Not companions, base, quests or bank. The save is never changed.</t>
+          <t>No save was found.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import</t>
+          <t>emp_ui_chara_import_fail</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラ…</t>
+          <t>そのキャラを連れてこられませんでした。</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>A character from my saves…</t>
+          <t>That character can't be brought.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_pick</t>
+          <t>emp_ui_chara_import_twice</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>どのセーブのキャラを連れてきますか？（セーブは変更されません）</t>
+          <t>そのセーブのキャラは、すでにこの世界にいます。</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Which save? It will not be changed.</t>
+          <t>That character is already in this world.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_back</t>
+          <t>emp_ui_sv_cfg_world_time</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>戻る</t>
+          <t>世界で日付をひとつにする</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>One date for the whole world</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_none</t>
+          <t>emp_ui_sv_desc_world_time</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>読み込めるセーブが見つかりません。</t>
+          <t>別のマップにひとりでいるプレイヤーの時間も、全員に反映されます。いちばん進んだ日付が世界の日付です。オフ：ホストの日付のみ。</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>No save was found.</t>
+          <t>Time spent alone on another map counts for everyone; the latest date is the world's. Off: only the host's date counts.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_fail</t>
+          <t>emp_ui_sv_cfg_world_keeper</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>そのキャラを連れてこられませんでした。</t>
+          <t>天気、税、手紙は一度だけ起こる</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>That character can't be brought.</t>
+          <t>Weather, taxes and letters happen once</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_twice</t>
+          <t>emp_ui_sv_desc_world_keeper</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>そのセーブのキャラは、すでにこの世界にいます。</t>
+          <t>天気、依頼の期限切れ、税金、給料、手紙は、ひとりのゲームだけが処理します。オフ：マップを持つ全員が処理します。</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>That character is already in this world.</t>
+          <t>Weather, expired quests, taxes, salaries and letters are handled by one player only. Off: every player holding a map handles them.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_time</t>
+          <t>emp_ui_depot_take</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>世界で日付をひとつにする</t>
+          <t>デポから世界を取り出してホストする</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>One date for the whole world</t>
+          <t>Take the world from the depot and host it</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_time</t>
+          <t>emp_ui_depot_put</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>別のマップにひとりでいるプレイヤーの時間も、全員に反映されます。いちばん進んだ日付が世界の日付です。オフ：ホストの日付のみ。</t>
+          <t>このセーブをデポに置く</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Time spent alone on another map counts for everyone. The latest date is the world's. Unticked, only the host's date counts.</t>
+          <t>Put this save in the depot</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_keeper</t>
+          <t>emp_ui_depot_held</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>天気、税、手紙はワールドで一度だけ起こる</t>
+          <t>{0} が世界をホスト中です。Steam で参加してください。招待してもらうか、Steam のフレンド一覧で「ゲームに参加」を選びます。抜けた直後なら、3分ほど待ってください。</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Weather, taxes and letters happen once for the world</t>
+          <t>{0} is hosting the world. Join through Steam: ask for an invite, or use "Join Game" on their name in your friends list. If they just left, wait up to 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_keeper</t>
+          <t>emp_ui_depot_empty</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>天気、依頼の期限切れ、税金、給料、手紙は、ひとりのゲームだけが処理します。オフ：マップを持つ全員が処理します。</t>
+          <t>デポにはまだ世界がありません。ゲームを始めるかロードして、このパネルをもう一度開き、ロビーのタブで「このセーブをデポに置く」を選んでください。</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Weather, expired quests, taxes, salaries and letters are handled by one player only. Unticked, every player holding a map handles them.</t>
+          <t>The depot has no world yet. Start or load a game, then open this panel again and use "Put this save in the depot" in the Lobby tab.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>emp_ui_depot_take</t>
+          <t>emp_ui_depot_fail</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>デポから世界を取り出してホストする</t>
+          <t>デポに接続できませんでした。</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Take the world from the depot and host it</t>
+          <t>Could not reach the depot.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put</t>
+          <t>emp_ui_depot_put_done</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>このセーブをデポに置く</t>
+          <t>この世界をデポに置きました。ゲームはそこから読み込み直します。これからのセーブはすべてデポに送られます。</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Put this save in the depot</t>
+          <t>The world is now in the depot. The game loads it again from there. From now on, every save goes to the depot.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held</t>
+          <t>emp_ui_depot_folder</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中です。Steam で参加してください。招待してもらうか、Steam のフレンド一覧で「ゲームに参加」を選びます。抜けた直後なら、3分ほど待ってください。</t>
+          <t>デポ</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{0} is hosting the world. Join through Steam: ask for an invite, or use "Join Game" on their name in your friends list. If they just left, wait up to 3 minutes.</t>
+          <t>Depot</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>emp_ui_depot_empty</t>
+          <t>emp_ui_depot_folder_ask</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>デポにはまだ世界がありません。ゲームを始めるかロードして、このパネルをもう一度開き、ロビーのタブで「このセーブをデポに置く」を選んでください。</t>
+          <t>セーブの置き場所：Elin Together Server のアドレス（ホスト:55557）、全員が使えるフォルダ、または非公開の GitHub リポジトリ（github:ユーザー/リポジトリ）。空欄なら使いません</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>The depot has no world yet. Start or load a game, then open this panel again and use "Put this save in the depot" in the Lobby tab.</t>
+          <t>Where the world is kept: the address of Elin Together Server (host:55557), a folder everyone can reach, or a private GitHub repository (github:owner/repository). Leave empty for none.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>emp_ui_depot_fail</t>
+          <t>emp_ui_join_address</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>デポに接続できませんでした。</t>
+          <t>アドレスで参加</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Could not reach the depot.</t>
+          <t>Join by address</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put_done</t>
+          <t>emp_ui_join_address_ask</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>この世界をデポに置きました。ゲームはそこから読み込み直します。これからのセーブはすべてデポに送られます。</t>
+          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、なしは 55557）</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>The world is now in the depot. The game loads it again from there. From now on, every save goes to the depot.</t>
+          <t>Server address (host:port). The port is 55556 with Elin, 55557 without.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder</t>
+          <t>emp_ui_depot_password</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>デポ</t>
+          <t>デポのキー</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Depot</t>
+          <t>Depot key</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder_ask</t>
+          <t>emp_ui_depot_password_ask</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>セーブの置き場所：Elin Together Server のアドレス（ホスト:55557）、全員が使えるフォルダ、または非公開の GitHub リポジトリ（github:ユーザー/リポジトリ）。空欄なら使いません</t>
+          <t>デポのパスワード（設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。変えないなら空欄のままにしてください</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Where the world is kept: the address of Elin Together Server (host:55557), a folder everyone can reach, or a private GitHub repository (github:owner/repository). Leave empty for none.</t>
+          <t>The depot password (if one was set), or the GitHub key. A key is never shown again. Leave empty to keep it.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>emp_ui_join_address</t>
+          <t>emp_ui_timeout</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>アドレスで参加</t>
+          <t>サーバーが応答しません。アドレスとポートを確認してください。</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Join by address</t>
+          <t>The server does not answer. Check the address and the port.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>emp_ui_join_address_ask</t>
+          <t>emp_ui_depot_password_wrong</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、なしは 55557）</t>
+          <t>サーバーにパスワードを断られました。クライアント設定の「デポのキー」で設定してください。</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Server address (host:port). The port is 55556 with Elin, 55557 without.</t>
+          <t>The server refused the password. Set it in Client settings, under "Depot key".</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password</t>
+          <t>emp_ui_depot_lost</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>デポのキー</t>
+          <t>接続が切れている間に、{0} がデポの世界を引き継ぎました。これ以降のプレイはデポに届きません。タイトルに戻って、その人のゲームに参加してください。</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Depot key</t>
+          <t>{0} took over the world while you were cut off. What you play now won't reach the depot. Go back to the title screen and join them.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_ask</t>
+          <t>emp_ui_depot_unsaved</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>デポのパスワード（設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。変えないなら空欄のままにしてください</t>
+          <t>デポにセーブが届きませんでした。このPCに残してあり、次のセーブでもう一度送ります。</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>The depot password (if one was set), or the GitHub key. A key is never shown again. Leave empty to keep it.</t>
+          <t>The save didn't reach the depot. It is kept on this PC and sent again at the next save.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>emp_ui_timeout</t>
+          <t>emp_ui_depot_unsent</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>サーバーが応答しません。アドレスとポートを確認してください。</t>
+          <t>前回の最後のセーブが、デポに届いていません。今送りますか？（はい：デポにある世界は別に取っておきます。いいえ：このセーブは捨てて、デポの世界を使います。）</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>The server does not answer. Check the address and the port.</t>
+          <t>Your last save never reached the depot. Send it now? Yes keeps the depot's world aside. No drops your save and uses the depot's world.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_wrong</t>
+          <t>emp_quest_follow_ask</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>サーバーにパスワードを断られました。クライアント設定の「デポのキー」で設定してください。</t>
+          <t>{0} が依頼に出かけます。ついていきますか？報酬は {0} のものになります。</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>The server refused the password. Set it in Client Settings, under "Depot key".</t>
+          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>emp_ui_depot_lost</t>
+          <t>emp_quest_follow_declined</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>接続が切れている間に、{0} がデポの世界を引き継ぎました。これ以降のプレイはデポに届きません。タイトルに戻って、その人のゲームに参加してください。</t>
+          <t>{0} は同行を断りました。</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{0} took over the world while you were cut off. What you play now won't reach the depot. Go back to the title screen and join them.</t>
+          <t>{0} won't come along.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsaved</t>
+          <t>emp_quest_follow_no_answer</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>デポにセーブが届きませんでした。このPCに残してあり、次のセーブでもう一度送ります。</t>
+          <t>{0} から返事がありません。</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>The save didn't reach the depot. It is kept on this PC and sent again at the next save.</t>
+          <t>{0} didn't answer.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsent</t>
+          <t>emp_quest_follow_asked</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>前回の最後のセーブが、デポに届いていません。今送りますか？（はい：デポにある世界は別に取っておきます。いいえ：このセーブは捨てて、デポの世界を使います。）</t>
+          <t>{0} に同行を頼んでいます…</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Your last save never reached the depot. Send it now? Yes keeps the depot's world aside. No drops your save and uses the depot's world.</t>
+          <t>Asking {0} to come along...</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>emp_quest_follow_ask</t>
+          <t>emp_base_host_only</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{0} が依頼に出かけます。ついていきますか？報酬は {0} のものになります。</t>
+          <t>今はホストだけができます。</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
+          <t>Only the host can do this for now.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>emp_quest_follow_declined</t>
+          <t>emp_trade_equipped</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{0} は同行を断りました。</t>
+          <t>取引は中止されました：渡す物が装備中です</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>{0} won't come along.</t>
+          <t>Trade cancelled: an item is equipped.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>emp_quest_follow_no_answer</t>
+          <t>emp_trade_nodrop</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{0} から返事がありません。</t>
+          <t>取引は中止されました：捨てられない物、渡せない物があります</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>{0} didn't answer.</t>
+          <t>Trade cancelled: an item can't be given away.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>emp_quest_follow_asked</t>
+          <t>emp_trade_npcprop</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{0} に同行を頼んでいます…</t>
+          <t>取引は中止されました：NPCの持ち物が含まれています</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Asking {0} to come along...</t>
+          <t>Trade cancelled: an item belongs to an NPC.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>emp_base_host_only</t>
+          <t>emp_trade_gifted</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>今はホストだけができます。</t>
+          <t>取引は中止されました：贈り物は取引できません</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Only the host can do this for now.</t>
+          <t>Trade cancelled: a gift can't be traded.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>emp_trade_equipped</t>
+          <t>emp_trade_bound</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>取引は中止されました：渡す物が装備中です</t>
+          <t>取引は中止されました：キャラに結びついた物があります</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item is equipped.</t>
+          <t>Trade cancelled: an item is bound to a character.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>emp_trade_nodrop</t>
+          <t>emp_trade_full</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>取引は中止されました：捨てられない物、渡せない物があります</t>
+          <t>取引は中止されました：バッグの空きが足りません</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item can't be given away.</t>
+          <t>Trade cancelled: a bag is full.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>emp_trade_npcprop</t>
+          <t>emp_travel_recalled_by</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>取引は中止されました：NPCの持ち物が含まれています</t>
+          <t>{@Peer} がここに来ます。合流のため画面を読み込み直します…</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item belongs to an NPC.</t>
+          <t>{@Peer} is coming here. The screen reloads to join them…</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>emp_trade_gifted</t>
+          <t>emp_ui_thing_gone</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>取引は中止されました：贈り物は取引できません</t>
+          <t>遅かった：ほかの人が先に取りました</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Trade cancelled: a gift can't be traded.</t>
+          <t>Too late. Someone else took it.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>emp_trade_bound</t>
+          <t>emp_base_refused</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>取引は中止されました：キャラに結びついた物があります</t>
+          <t>ホストに断られました：拠点か所持金では払えません。</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item is bound to a character.</t>
+          <t>The host refused. The base or your purse can't pay for this.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>emp_trade_full</t>
+          <t>emp_base_pending</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>取引は中止されました：バッグの空きが足りません</t>
+          <t>前の頼みが、まだホストの返事待ちです。</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Trade cancelled: a bag is full.</t>
+          <t>Your last request is still waiting for the host.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>emp_travel_recalled_by</t>
+          <t>emp_game_version_differs</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{@Peer} がここに来ます。合流のため画面を読み込み直します…</t>
+          <t>{0} の Elin はバージョンが違います（{1}、自分は {2}）。接続はできます。問題が起きたら同じバージョンにしてください。</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>{@Peer} is coming here. The screen reloads to join them…</t>
+          <t>{0} has another version of Elin ({1}, yours is {2}). You can still join. If something goes wrong, use the same version.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>emp_ui_thing_gone</t>
+          <t>emp_ui_sv_cfg_same_game_version</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>遅かった：ほかの人が先に取りました</t>
+          <t>友人も同じElinのバージョンが必要</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Too late. Someone else took it.</t>
+          <t>Friends need the same Elin version</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>emp_base_refused</t>
+          <t>emp_ui_sv_desc_same_game_version</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ホストに断られました：拠点か所持金では払えません。</t>
+          <t>参加するには、ホストと同じ Elin のバージョンが必要です（Elin Together は常に一致が必要）。オフ：警告つきで参加できます。</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The host refused. The base or your purse can't pay for this.</t>
+          <t>Friends need the host's Elin version to join; Elin Together must always match. Off: they join with a warning.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>emp_base_pending</t>
+          <t>emp_ui_sv_cfg_guest_build</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>前の頼みが、まだホストの返事待ちです。</t>
+          <t>友人も建築できる</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Your last request is still waiting for the host.</t>
+          <t>Friends can build</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>emp_game_version_differs</t>
+          <t>emp_ui_sv_desc_guest_build</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{0} の Elin はバージョンが違います（{1}、自分は {2}）。接続はできます。問題が起きたら同じバージョンにしてください。</t>
+          <t>友人も拠点で建築モード（床、壁、家具、採掘、伐採）を使えます。お金と素材は本人が払います。オフ：建築できるのはホストだけ。</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>{0} has another version of Elin ({1}, yours is {2}). You can still join. If something goes wrong, use the same version.</t>
+          <t>Friends use build mode in the base (floors, walls, furniture, mining, cutting) and pay the gold and materials. Off: only the host builds.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_same_game_version</t>
+          <t>emp_ui_depot_gh_help</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
-        <is>
-          <t>友人も同じElinのバージョンが必要</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Friends need the same Elin version</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_same_game_version</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Elin のバージョンが違うプレイヤーは入れません。オフ：警告つきで入れます。MODのバージョンは常に同じである必要があります。</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Players with another Elin version can't join. Unticked, they join with a warning. The mod version must always match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_cfg_guest_build</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>ほかのプレイヤーも建築できる</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Other players can build</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_guest_build</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>拠点の建築モード（床、壁、家具、採掘、伐採）を使えます。お金と素材は本人が払います。オフ：建築できるのはホストだけ。</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Others can use build mode in the base: floors, walls, furniture, mining, cutting. They pay the gold and materials. Unticked, only the host builds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>emp_ui_depot_gh_help</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
         <is>
           <t>非公開の GitHub リポジトリを、デポにできます。サーバーも共有フォルダも要らず、友達に GitHub アカウントも要りません。
 1. github.com で、この世界専用の空の非公開リポジトリを作ります。
@@ -3735,7 +3667,7 @@
 4. 同じ2行を友達に送ります。友達もここに入力します。キーで開けるのはこのリポジトリだけです。</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>A private GitHub repository can be the depot. No server, no shared folder, and your friends need no GitHub account.
 1. On github.com, create an empty private repository just for this world.
@@ -3745,4982 +3677,4920 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_key</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GitHub にアクセスキーを断られました。期限切れでないか、このリポジトリを含み「Contents: Read and write」であるかを確認して、クライアント設定でもう一度貼ってください。</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GitHub refused the key. Check that it hasn't expired and covers this repository with "Contents: Read and write", then paste it again in Client settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_missing</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>GitHub でこのリポジトリが見つかりません。クライアント設定で名前（github:ユーザー/リポジトリ）を確認し、アクセスキーがそれを含んでいるか確認してください。</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>GitHub can't find the repository. Check its name (github:owner/repository) in Client settings, and that your key covers it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_public</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>この GitHub リポジトリは公開です。世界とその履歴が誰にでも見えてしまいます。非公開に変えて（Settings、Danger Zone、Change visibility）、もう一度試してください。</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>This GitHub repository is public. Everyone could see your world and its history. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_big</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>この世界は20MBを超えていて、GitHub には大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに残っています。</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>This world is over 20 MB, too big for GitHub. Use Elin Together Server or a shared folder. The save stays on this PC.</t>
+        </is>
+      </c>
+    </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_key</t>
+          <t>emp_ui_depot_gh_changed</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>GitHub にアクセスキーを断られました。期限切れでないか、このリポジトリを含み「Contents: Read and write」であるかを確認して、クライアント設定でもう一度貼ってください。</t>
+          <t>接続が切れている間に、別の人が世界をホストしてセーブしました。あなたのセーブはこのPCに残り、これ以上デポに送られません。タイトルに戻って、世界を取り直してください。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>GitHub refused the key. Check that it hasn't expired and covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
+          <t>Someone else hosted the world and saved while you were cut off. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_missing</t>
+          <t>emp_ui_depot_gh_down</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>GitHub でこのリポジトリが見つかりません。クライアント設定で名前（github:ユーザー/リポジトリ）を確認し、アクセスキーがそれを含んでいるか確認してください。</t>
+          <t>GitHub が応答しません。接続を確認して、少し待ってからもう一度試してください。</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>GitHub can't find the repository. Check its name (github:owner/repository) in Client Settings, and that your key covers it.</t>
+          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_public</t>
+          <t>emp_ui_sv_cfg_player_kill</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>この GitHub リポジトリは公開です。世界とその履歴が誰にでも見えてしまいます。非公開に変えて（Settings、Danger Zone、Change visibility）、もう一度試してください。</t>
+          <t>プレイヤー同士で倒せる</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>This GitHub repository is public. Everyone could see your world and its history. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+          <t>Players can kill each other</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_big</t>
+          <t>emp_ui_sv_desc_player_kill</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>この世界は20MBを超えていて、GitHub には大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに残っています。</t>
+          <t>プレイヤーや仲間の攻撃で、ほかのプレイヤーを倒せます。オフ：致命傷でもHP0で生き残ります。</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>This world is over 20 MB, too big for GitHub. Use Elin Together Server or a shared folder. The save stays on this PC.</t>
+          <t>Players and their companions can kill other players. Off: a deadly blow leaves them alive at 0 HP.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_changed</t>
+          <t>emp_ui_sv_cfg_host_manages_base</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>接続が切れている間に、別の人が世界をホストしてセーブしました。あなたのセーブはこのPCに残り、これ以上デポに送られません。タイトルに戻って、世界を取り直してください。</t>
+          <t>拠点を管理できるのはホストだけ</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Someone else hosted the world and saved while you were cut off. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
+          <t>Only the host manages the base</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_down</t>
+          <t>emp_ui_sv_desc_host_manages_base</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>GitHub が応答しません。接続を確認して、少し待ってからもう一度試してください。</t>
+          <t>友人は拠点を変更できません（研究、炉の技能、方針、名前、設定、住人、建築）。オフ：全員ができます。拠点を完全に手放せるのはホストだけです。</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
+          <t>Friends cannot change the base: research, hearth skills, policies, names, settings, residents, build mode. Off: everyone can; only the host can ever give the base up.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_kill</t>
+          <t>emp_ui_sv_cfg_duels</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>プレイヤー同士で倒せる</t>
+          <t>プレイヤー同士で決闘できる</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Players can kill each other</t>
+          <t>Players can duel</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_kill</t>
+          <t>emp_ui_sv_desc_duels</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>プレイヤーや仲間の攻撃で、ほかのプレイヤーを倒せます。オフ：致命傷でもHP0で生き残ります。</t>
+          <t>相手のキャラのメニューから決闘を申し込めます。誰も死なず、終わると全員回復し、何も失いません。</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Players and their companions can kill other players. Unticked, a deadly blow leaves them alive at 0 HP.</t>
+          <t>Challenge another player from the menu on their character; nobody dies, both are healed and nothing is lost.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_host_manages_base</t>
+          <t>emp_act_duel</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>拠点を管理できるのはホストだけ</t>
+          <t>決闘を申し込む</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Only the host manages the base</t>
+          <t>Challenge to a duel</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_host_manages_base</t>
+          <t>emp_duel_invite</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーの拠点操作（研究、炉の技能、方針、名前、設定、住人、建築）は断られます。オフ：全員がホストと同じように管理できます。拠点を完全に手放せるのは常にホストだけです。</t>
+          <t>{0}が決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Others can't change the base: research, hearth skills, policies, names, settings, residents, build mode. Unticked, all can. Only the host can give up the base for good.</t>
+          <t>{0} challenges you to a duel. Nobody dies, but what you use up stays used. Accept?</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_duels</t>
+          <t>emp_duel_asked</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>プレイヤー同士の決闘</t>
+          <t>{0} に決闘を申し込みました…</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Duels between players</t>
+          <t>You challenge {0} to a duel…</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_duels</t>
+          <t>emp_duel_countdown</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>相手のキャラのメニューから決闘を申し込めます。誰も死なず、終わると全員回復し、何も失いません。</t>
+          <t>{0} と {1} が向かい合います。3秒後に決闘開始。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Challenge another player from the menu on their character. Nobody dies, both are healed and nothing is lost.</t>
+          <t>{0} and {1} face each other. The duel starts in 3 seconds.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>emp_act_duel</t>
+          <t>emp_duel_fight</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>決闘を申し込む</t>
+          <t>始め！</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Challenge to a duel</t>
+          <t>Fight!</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>emp_duel_invite</t>
+          <t>emp_duel_declined</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{0}が決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
+          <t>決闘を断られました。</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>{0} challenges you to a duel. Nobody dies, but what you use up stays used. Accept?</t>
+          <t>Your challenge was declined.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>emp_duel_asked</t>
+          <t>emp_duel_noanswer</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{0} に決闘を申し込みました…</t>
+          <t>決闘の返事がありません。</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>You challenge {0} to a duel…</t>
+          <t>Nobody answered your challenge.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>emp_duel_countdown</t>
+          <t>emp_duel_busy</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{0} と {1} が向かい合います。3秒後に決闘開始。</t>
+          <t>そのプレイヤーは決闘中か取引中です。</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>{0} and {1} face each other. The duel starts in 3 seconds.</t>
+          <t>That player is busy in a duel or a trade.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>emp_duel_fight</t>
+          <t>emp_duel_over</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>始め！</t>
+          <t>決闘は引き分けです。</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Fight!</t>
+          <t>The duel ends in a draw.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>emp_duel_declined</t>
+          <t>emp_handover_failed</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>決闘を断られました。</t>
+          <t>キャラ {0} はこの世界に入れませんでした（死亡しています）。セーブのキャラで遊びます。</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Your challenge was declined.</t>
+          <t>Your character {0} can't join this world because it is dead. You play the character of the save.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>emp_duel_noanswer</t>
+          <t>emp_ui_depot_held_btn</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>決闘の返事がありません。</t>
+          <t>{0} が世界をホスト中</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Nobody answered your challenge.</t>
+          <t>{0} is hosting the world</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>emp_duel_busy</t>
+          <t>emp_error_connection</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>そのプレイヤーは決闘中か取引中です。</t>
+          <t>接続できません：ゲームが応答しません。ゲームが開いているか確認して、もう一度試してください。</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>That player is busy in a duel or a trade.</t>
+          <t>Could not connect. The game does not answer. Check that it is open, then try again.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>emp_duel_over</t>
+          <t>emp_not_allowed</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>決闘は引き分けです。</t>
+          <t>このゲームには、Steam ロビーから参加したプレイヤーしか入れません。</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>The duel ends in a draw.</t>
+          <t>Only players who join through its Steam lobby can enter this game.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>emp_handover_failed</t>
+          <t>emp_connection_no_server</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>キャラ {0} はこの世界に入れませんでした（死亡しています）。セーブのキャラで遊びます。</t>
+          <t>そのゲームはまだ開いていません。少し待ってからもう一度試してください。</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Your character {0} can't join this world because it is dead. You play the character of the save.</t>
+          <t>That game is not open yet. Try again in a moment.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held_btn</t>
+          <t>emp_zone_session_empty</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中</t>
+          <t>ここにはもう誰もいません</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>{0} is hosting the world</t>
+          <t>Nobody else is here anymore.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>emp_error_connection</t>
+          <t>emp_ui_timeout_steam</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>接続できません：ゲームが応答しません。ゲームが開いているか確認して、もう一度試してください。</t>
+          <t>ゲームが応答しません。相手が抜けたか、接続が切れたのかもしれません。</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Could not connect. The game does not answer. Check that it is open, then try again.</t>
+          <t>The game does not answer. The player may have left or lost the connection.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>emp_not_allowed</t>
+          <t>emp_ui_reconnecting</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>このゲームには、Steam ロビーから参加したプレイヤーしか入れません。</t>
+          <t>接続が切れました。ゲームに戻っています…</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Only players who join through its Steam lobby can enter this game.</t>
+          <t>Connection lost. Going back into the game…</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>emp_connection_no_server</t>
+          <t>emp_ui_reconnect_cancel</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>そのゲームはまだ開いていません。少し待ってからもう一度試してください。</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>That game is not open yet. Try again in a moment.</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>emp_zone_session_empty</t>
+          <t>emp_ui_reconnect_failed</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ここにはもう誰もいません</t>
+          <t>ゲームに戻れませんでした。3分間応答がなく、終わった可能性があります。</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Nobody else is here anymore.</t>
+          <t>Could not get back into the game. It didn't answer for 3 minutes and may be over.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>emp_ui_timeout_steam</t>
+          <t>emp_ui_save_kept</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ゲームが応答しません。相手が抜けたか、接続が切れたのかもしれません。</t>
+          <t>進行状況は、参加したゲームが保存します。</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>The game does not answer. The player may have left or lost the connection.</t>
+          <t>The game you joined keeps your progress.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>emp_ui_reconnecting</t>
+          <t>emp_ui_sv_cfg_auto_reconnect</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>接続が切れました。ゲームに戻っています…</t>
+          <t>切れたプレイヤーは自動で戻る</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Connection lost. Going back into the game…</t>
+          <t>Dropped players rejoin by themselves</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect_cancel</t>
+          <t>emp_ui_sv_desc_auto_reconnect</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>接続が切れたプレイヤーは、3分間自動で再参加を試みます。オフ：タイトルに戻ります。</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>A player who drops tries to rejoin for 3 min. Off: they go back to the title screen.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect_failed</t>
+          <t>emp_ui_sv_cfg_auto_host</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ゲームに戻れませんでした。3分間応答がなく、終わった可能性があります。</t>
+          <t>世界を読み込むと友人が参加できる</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Could not get back into the game. It didn't answer for 3 minutes and may be over.</t>
+          <t>Friends can join once a world loads</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>emp_ui_save_kept</t>
+          <t>emp_ui_sv_desc_auto_host</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>進行状況は、参加したゲームが保存します。</t>
+          <t>サーバーを手で始める必要はありません（所有した土地が必要）。オフ：ホストが自分でサーバーを始めます。</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>The game you joined keeps your progress.</t>
+          <t>No need to start the server; the world needs a claimed land. Off: the host starts the server.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_reconnect</t>
+          <t>emp_ui_sv_cfg_auto_save</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>切れたプレイヤーは自動で戻る</t>
+          <t>友人がいる間は自動でセーブ</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Players rejoin by themselves after a drop</t>
+          <t>The game saves while friends play</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_reconnect</t>
+          <t>emp_ui_sv_desc_auto_save</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>接続が切れたプレイヤーは、3分間自動で再参加を試みます。オフ：タイトルに戻ります。</t>
+          <t>友人がいる間は2分ごと（遅いときは5分ごと）と、最後の人が抜けたときにセーブします。オフ：ホストがセーブしたときだけ。</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>A player who drops tries to rejoin for 3 minutes. Unticked, they go back to the title screen.</t>
+          <t>Saves every 2 min while friends are in the game (5 min if saving is slow), and when the last one leaves. Off: only when the host saves.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_host</t>
+          <t>emp_ui_load_blocked</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>世界を読み込むと自動でフレンドに公開</t>
+          <t>みんなで遊んでいる間は、セーブをロードできません。</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Open the game to friends when a world loads</t>
+          <t>You can't load a save while players are together.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_host</t>
+          <t>emp_ui_depot_join_btn</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>世界を読み込むとすぐ、サーバーを手で始めなくてもフレンドが参加できます（所有した土地が必要）。オフ：ホストが自分でサーバーを始めます。</t>
+          <t>{0} に参加</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Friends can join as soon as the world loads, with no need to start the server. The world needs a claimed land. Unticked, the host starts the server.</t>
+          <t>Join {0}</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_save</t>
+          <t>emp_ui_depot_join_fail</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>他のプレイヤーがいる間は自動でセーブ</t>
+          <t>{0} が世界を持っていますが、そのゲームはまだ開いていません。少し待ってからもう一度試してください。ゲームが止まっていたら、3分以内に世界は空きます。</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Save automatically while others play</t>
+          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_save</t>
+          <t>emp_ui_box_far</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>他のプレイヤーがいる間は2分ごと（遅いときは5分ごと）と、最後の人が抜けたときにセーブします。オフ：ホストがセーブしたときだけ。</t>
+          <t>この箱は世界全体のもので、ホストが預かっています。ホストから離れていても入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Saves every 2 minutes while others are in the game (5 if saving is slow), and when the last one leaves. Unticked, only when the host saves.</t>
+          <t>This chest belongs to the whole world and the host keeps it. If you are away from the host, what you put in still arrives, but you only see it again back on the host's map.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>emp_ui_load_blocked</t>
+          <t>emp_ui_sv_cfg_own_sleep</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>みんなで遊んでいる間は、セーブをロードできません。</t>
+          <t>各自で眠る</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>You can't load a save while players are together.</t>
+          <t>Everyone sleeps on their own</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>emp_ui_depot_join_btn</t>
+          <t>emp_ui_sv_desc_own_sleep</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>{0} に参加</t>
+          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは、全員が同時に眠っているときだけです。オフ：全員が揃うまで待ちます。</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Join {0}</t>
+          <t>A player in bed sleeps at once; the night passes only when everyone sleeps at the same time. Off: everyone waits for everyone.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>emp_ui_depot_join_fail</t>
+          <t>emp_ui_sv_cfg_dump_spares_belt</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>{0} が世界を持っていますが、そのゲームはまだ開いていません。少し待ってからもう一度試してください。ゲームが止まっていたら、3分以内に世界は空きます。</t>
+          <t>自動整理で手持ちとツールベルトを残す</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
+          <t>Dump spares keeps held and belt items</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>emp_ui_box_far</t>
+          <t>emp_ui_sv_desc_dump_spares_belt</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>この箱は世界全体のもので、ホストが預かっています。ホストから離れていても入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
+          <t>手に持っている物とツールベルトの中身は、ホットバーと同じように、まとめて入れても残ります。オフ：元のゲームと同じ。</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>This chest belongs to the whole world and the host keeps it. If you are away from the host, what you put in still arrives, but you only see it again back on the host's map.</t>
+          <t>Dump spares keeps what you hold and what is in your tool belt, like the hotbar. Off: as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_own_sleep</t>
+          <t>emp_ui_travel_no_date</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>各自で眠る</t>
+          <t>仲間は別の場所にいます。あなたの旅では日付は進みません。</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Everyone sleeps on their own</t>
+          <t>Your friends are elsewhere. Your trip doesn't move the date.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_own_sleep</t>
+          <t>emp_ui_bill_paid</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは、全員が同時に眠っているときだけです。オフ：全員が揃うまで待ちます。</t>
+          <t>{0}が請求書を支払いました：{1}（{2}）</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>A player in bed sleeps at once. The night passes only when everyone sleeps at the same time. Unticked, everyone waits for everyone.</t>
+          <t>{0} paid a bill: {1} ({2})</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_time_jumps_together</t>
+          <t>emp_ui_bill_already_paid</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>全員一緒のときだけ時間が進む</t>
+          <t>この請求書はもう払われています。お金は引かれていません。</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Time moves only when all travel together</t>
+          <t>This bill is already paid. Nothing was taken from you.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_time_jumps_together</t>
+          <t>emp_ui_sleep_alone</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ワールドマップの一歩で日付が進むのは、全員が一緒に旅しているときだけです。そうでなければ旅人だけがターンを消費します。オフ：誰かの一歩ごとに全員が3時間進みます。</t>
+          <t>あなたは眠りました。世界は進みません：{0} がまだ起きています。</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>On the world map, the date moves only when all players travel together. Otherwise only the traveller's turns pass. Unticked, every step by anyone adds 3 hours for all.</t>
+          <t>You slept. The world did not move on, as {0} is still awake.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_dump_spares_belt</t>
+          <t>emp_ui_sleep_count</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>自動整理で手持ちとツールベルトを残す</t>
+          <t>{0} は眠っている（{1}/{2}）</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Auto-dump leaves your hands and tool belt alone</t>
+          <t>{0} is asleep ({1} of {2})</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_dump_spares_belt</t>
+          <t>emp_ui_sleep_all</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>手に持っている物とツールベルトの中身は、ホットバーと同じように、まとめて入れても残ります。オフ：元のゲームと同じ。</t>
+          <t>全員が眠りました。夜が明けます。</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Dump spares keeps what you hold and what is in your tool belt, like the hotbar. Unticked, it works as in the base game.</t>
+          <t>Everyone is asleep. The night passes.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>emp_ui_travel_no_date</t>
+          <t>emp_ui_resync</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>仲間は別の場所にいます。あなたの旅では日付は進みません。</t>
+          <t>マップを整えています…</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Your friends are elsewhere. Your trip doesn't move the date.</t>
+          <t>Fixing the map…</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>emp_ui_bill_paid</t>
+          <t>emp_ui_sv_cfg_auto_resync</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>{0}が請求書を支払いました：{1}（{2}）</t>
+          <t>ずれたマップは自動で読み込み直す</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>{0} paid a bill: {1} ({2})</t>
+          <t>Out-of-sync maps reload by themselves</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>emp_ui_bill_already_paid</t>
+          <t>emp_ui_sv_desc_auto_resync</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>この請求書はもう払われています。お金は引かれていません。</t>
+          <t>マップがホストと食い違う（物やキャラが足りない）と、自動で読み込み直します。30秒に1回まで。オフ：違いはログに書くだけ。</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>This bill is already paid. Nothing was taken from you.</t>
+          <t>A player's map that differs from the host's (an item or character missing) reloads, at most every 30 s. Off: the difference is only logged.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_alone</t>
+          <t>emp_ui_bank_deposit</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>あなたは眠りました。世界は進みません：{0} がまだ起きています。</t>
+          <t>{0}が銀行に{1}を預けました</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>You slept. The world did not move on, as {0} is still awake.</t>
+          <t>{0} put {1} in the bank</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_count</t>
+          <t>emp_ui_bank_withdraw</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>{0} は眠っている（{1}/{2}）</t>
+          <t>{0}が銀行から{1}を引き出しました</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>{0} is asleep ({1} of {2})</t>
+          <t>{0} took {1} out of the bank</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_all</t>
+          <t>emp_ui_sv_cfg_world_copy</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>全員が眠りました。夜が明けます。</t>
+          <t>友人も世界のコピーを持つ</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Everyone is asleep. The night passes.</t>
+          <t>Friends keep a copy of the world</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>emp_ui_resync</t>
+          <t>emp_ui_sv_desc_world_copy</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>マップを整えています…</t>
+          <t>自動セーブのたびに、友人のPCが自分のセーブとは別に世界のコピーを保管します。オフ：世界はホストのPCにしかありません。</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Fixing the map…</t>
+          <t>After each automatic save, every friend's PC keeps a copy of the world, apart from their own saves. Off: only the host's PC has it.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_resync</t>
+          <t>emp_ui_sv_cfg_shared_tax</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ホストと違うマップは自動で読み込み直される</t>
+          <t>税金は最も有名なプレイヤーで計算</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>A map that differs from the host's loads again by itself</t>
+          <t>Tax follows the most famous player</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_resync</t>
+          <t>emp_ui_sv_desc_shared_tax</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>マップがホストと食い違う（物やキャラが足りない）と、自動で読み込み直します。30秒に1回まで。オフ：違いはログに書くだけ。</t>
+          <t>毎月の税金は、プレイヤーの中でいちばん高い名声で計算します。オフ：ホストの名声（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>If a player's map differs from the host's, with an item or character missing, it loads again by itself, at most every 30 seconds. Unticked, the difference is only logged.</t>
+          <t>Monthly tax uses the highest fame among the players. Off: the host's fame, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>emp_ui_bank_deposit</t>
+          <t>emp_ui_sv_cfg_soft_recall</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>{0}が銀行に{1}を預けました</t>
+          <t>合流のとき世界を読み込み直さない</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>{0} put {1} in the bank</t>
+          <t>Meeting up does not reload the world</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>emp_ui_bank_withdraw</t>
+          <t>emp_ui_sv_desc_soft_recall</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>{0}が銀行から{1}を引き出しました</t>
+          <t>ホストとプレイヤーが同じマップになるとき、そのマップだけを読み込むか、何も読み込みません。合わないときは世界を読み込み直します。オフ：毎回読み込み直します。</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>{0} took {1} out of the bank</t>
+          <t>When the host and a player meet on one map, only that map loads, or nothing; on a mismatch the world reloads. Off: the world always reloads.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_copy</t>
+          <t>emp_ui_sv_cfg_publish_mods</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーも世界のコピーを持つ</t>
+          <t>友人にゲームのMODを見せる</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Other players keep a copy of the world</t>
+          <t>Friends see the game's mods</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_copy</t>
+          <t>emp_ui_sv_desc_publish_mods</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>自動セーブのたびに、全員のPCが自分のセーブとは別に世界のコピーを保管します。オフ：世界はホストのPCにしかありません。</t>
+          <t>友人は参加前と参加時にMOD一覧を見られ、断られたときは違うMODが分かります（デポの世界はその modlist.txt を使います）。オフ：何も見せません。</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>After each automatic save, every player's PC keeps a copy of the world, apart from their own saves. Unticked, only the host's PC has it.</t>
+          <t>Friends see the mod list before and when joining, and which mods differ if refused (a depot world uses its modlist.txt). Off: nothing is shown.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_shared_tax</t>
+          <t>emp_ui_cl_fetch_mods</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>税金は最も有名なプレイヤーで計算</t>
+          <t>ゲームのMODをダウンロードする</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Tax follows the most famous player</t>
+          <t>Download the game's mods</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_tax</t>
+          <t>emp_ui_cl_desc_fetch_mods</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>毎月の税金は、接続中のプレイヤーでいちばん高い名声で計算します。オフ：ホストの名声で計算（元のゲームと同じ）。</t>
+          <t>参加するゲームに足りない Workshop の MOD を、購読せずにダウンロードします。Elin は一度再起動します。</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Monthly tax uses the highest fame among the players. Unticked, it uses the host's fame, as in the base game.</t>
+          <t>Downloads the Workshop mods you lack for the game you join, without subscribing. Elin restarts once.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_soft_recall</t>
+          <t>emp_ui_mods_lobby</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>合流のとき世界を読み込み直さない</t>
+          <t>Mod {0} 個</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Rejoin without reloading the world</t>
+          <t>{0} mods</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_soft_recall</t>
+          <t>emp_ui_mods_lobby_missing</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ホストとプレイヤーが同じマップになるとき、世界全体は読み込み直さず、そのまま、またはそのマップだけを読み込みます。合わないときは従来どおり読み込み直します。オフ：毎回読み込み直します。</t>
+          <t>{0} 個のMOD（{1} 個が足りません）</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>When the host and a player meet on one map, the whole world does not reload. Only that map loads, or nothing. If something doesn't match, the world reloads as before. Unticked, it always reloads.</t>
+          <t>{0} mods, {1} missing</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_publish_mods</t>
+          <t>emp_ui_mods_world</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ゲームのMOD一覧をプレイヤーに見せる</t>
+          <t>この世界のMODのうち {0} 個が読み込まれていません：{1}。一覧はログにあります。</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Show the game's mods to players</t>
+          <t>{0} mods of this world are not loaded: {1}. The full list is in the log.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_publish_mods</t>
+          <t>emp_ui_mods_missing</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>参加前（ゲーム一覧）と参加時にMOD一覧が分かり、断られたときは違うMODが名前で表示されます。デポから取った世界では、デポの一覧（modlist.txt）を使います。オフ：何も伝えません。</t>
+          <t>ホストのMODで足りないもの（{0}）：{1}</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Players see the mod list before joining and when joining. If refused, they are told which mods differ. For a world from a depot, the depot's list (modlist.txt) is used. Unticked, nothing is shown.</t>
+          <t>Host mods you don't have ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>emp_ui_cl_fetch_mods</t>
+          <t>emp_ui_mods_hand</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ゲームのMODをダウンロードする</t>
+          <t>手動で入れるMOD（{0}）：{1}</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Download the game's mods</t>
+          <t>Mods to install yourself ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_fetch_mods</t>
+          <t>emp_ui_mods_extra</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>参加するゲームに足りない Workshop の MOD を、購読せずにダウンロードします。Elin は一度再起動します。</t>
+          <t>ホストにないMOD（{0}）：{1}</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Downloads the Workshop mods you lack for the game you join, without subscribing. Elin restarts once.</t>
+          <t>Mods the host doesn't have ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>emp_ui_mods_lobby</t>
+          <t>emp_ui_mods_fetching</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Mod {0} 個</t>
+          <t>ゲームのMODをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>{0} mods</t>
+          <t>Downloading the game's mods {0}/{1}: {2} {3}% (Esc to cancel)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>emp_ui_mods_lobby_missing</t>
+          <t>emp_ui_mods_fetch_failed</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>{0} 個のMOD（{1} 個が足りません）</t>
+          <t>ゲームのMODをダウンロードできませんでした。何も変更していません。</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>{0} mods, {1} missing</t>
+          <t>Could not download the mods. Nothing was changed.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>emp_ui_mods_world</t>
+          <t>emp_ui_mods_restart</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>この世界のMODのうち {0} 個が読み込まれていません：{1}。一覧はログにあります。</t>
+          <t>Elin はゲームのMODで再起動し、自動でゲームに戻ります。起動しないときは、Elin をもう一度起動してください。</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>{0} mods of this world are not loaded: {1}. The full list is in the log.</t>
+          <t>Elin restarts with the game's mods and comes back by itself. If it doesn't start, start Elin again.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>emp_ui_mods_missing</t>
+          <t>emp_ui_mods_restart_manual</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ホストのMODで足りないもの（{0}）：{1}</t>
+          <t>Elin を閉じます。もう一度起動すると、ゲームのMODで自動でゲームに戻ります。</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Host mods you don't have ({0}): {1}</t>
+          <t>Elin closes. Start it again and it comes back to the game by itself, with its mods.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>emp_ui_mods_hand</t>
+          <t>emp_ui_mods_session</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>手動で入れるMOD（{0}）：{1}</t>
+          <t>今回の Elin は、マルチプレイのMODで動いています。MOD一覧は次の起動で元に戻ります。次回の再起動を省くには、クライアント設定の「ゲームのMODを購読する」にチェックしてください。</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Mods to install yourself ({0}): {1}</t>
+          <t>This time Elin runs with the game's mods. Your own list returns at the next start. To skip this restart next time, tick "Subscribe to the game's mods" in Client settings.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>emp_ui_mods_extra</t>
+          <t>emp_ui_mods_session_locked</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ホストにないMOD（{0}）：{1}</t>
+          <t>今回はMOD一覧を保存しません。次の起動で元の一覧に戻ります。</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Mods the host doesn't have ({0}): {1}</t>
+          <t>The mod list is not saved this time. Yours returns at the next start of Elin.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>emp_ui_mods_fetching</t>
+          <t>emp_ui_cl_keep_mods</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ゲームのMODをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
+          <t>ゲームのMODを購読する</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Downloading the game's mods {0}/{1}: {2} {3}% (Esc to cancel)</t>
+          <t>Subscribe to the game's mods</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>emp_ui_mods_fetch_failed</t>
+          <t>emp_ui_cl_desc_keep_mods</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ゲームのMODをダウンロードできませんでした。何も変更していません。</t>
+          <t>参加するゲームの MOD を Steam で購読し、次からは再起動なしで参加できます。</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Could not download the mods. Nothing was changed.</t>
+          <t>Subscribes to the game's mods on Steam, so you can rejoin without restarting.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>emp_ui_mods_restart</t>
+          <t>emp_ui_sv_cfg_takeover</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Elin はゲームのMODで再起動し、自動でゲームに戻ります。起動しないときは、Elin をもう一度起動してください。</t>
+          <t>ホストが抜けたら友人が引き継ぐ</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Elin restarts with the game's mods and comes back by itself. If it doesn't start, start Elin again.</t>
+          <t>A friend takes over if the host leaves</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>emp_ui_mods_restart_manual</t>
+          <t>emp_ui_sv_desc_takeover</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Elin を閉じます。もう一度起動すると、ゲームのMODで自動でゲームに戻ります。</t>
+          <t>ホストが抜けると、友人のひとりが自分のコピーから世界を開き、ゲームが続きます（「友人も世界のコピーを持つ」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Elin closes. Start it again and it comes back to the game by itself, with its mods.</t>
+          <t>When the host leaves, a friend opens the world from their copy and the game goes on; needs "Friends keep a copy of the world". Off: the game ends with the host.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>emp_ui_mods_session</t>
+          <t>emp_takeover_begin</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>今回の Elin は、マルチプレイのMODで動いています。MOD一覧は次の起動で元に戻ります。次回の再起動を省くには、クライアント設定の「ゲームのMODを残す」にチェックしてください。</t>
+          <t>ホストが抜けました。あなたが世界を引き継ぎます。まもなくここでゲームが続きます。</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>This time Elin runs with the game's mods. Your own list returns at the next start. To skip this restart next time, tick "Keep the game's mods" in Client Settings.</t>
+          <t>The host left. You take over the world. The game goes on here in a moment.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>emp_ui_mods_session_locked</t>
+          <t>emp_takeover_leaving</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>今回はMOD一覧を保存しません。次の起動で元の一覧に戻ります。</t>
+          <t>退出中：ほかのプレイヤーに最後のセーブを渡しています…</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>The mod list is not saved this time. Yours returns at the next start of Elin.</t>
+          <t>Leaving. Giving the last save to the others…</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>emp_ui_cl_keep_mods</t>
+          <t>emp_ui_limited_bought</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ゲームのMODを残す（Workshop で購読）</t>
+          <t>それはもう買いました。</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Keep the game's mods (subscribe on the Workshop)</t>
+          <t>You already bought this one.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_keep_mods</t>
+          <t>emp_story_share</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>参加するゲームの MOD を Steam で購読し、次からは再起動なしで参加できます。</t>
+          <t>{0}の分け前</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Subscribes to the game's mods on Steam, so you can rejoin without restarting.</t>
+          <t>{0}'s share</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_takeover</t>
+          <t>emp_ui_sv_cfg_once_per_player</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ホストが抜けたら別のプレイヤーが引き継ぐ</t>
+          <t>一度きりの報酬を全員がもらえる</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Another player takes over when the host leaves</t>
+          <t>Every player gets one-time rewards</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_takeover</t>
+          <t>emp_ui_sv_desc_once_per_player</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ホストが抜けると、プレイヤーのひとりが自分のコピーから世界を開き、そこでゲームが続きます（「世界のコピー」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
+          <t>店の限定品と、ストーリーでもらえる物（依頼の報酬、会話の贈り物）が、プレイヤーごとに1回ずつ手に入ります。オフ：最初のひとりだけ（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>When the host leaves, a player opens the world from their copy and the game goes on. Needs the world copy option. Unticked, the game ends with the host.</t>
+          <t>One-time shop goods and story gifts, like quest rewards, go once to each player. Off: only the first player gets them, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>emp_takeover_begin</t>
+          <t>emp_takeover_rejoin</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ホストが抜けました。あなたが世界を引き継ぎます。まもなくここでゲームが続きます。</t>
+          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>The host left. You take over the world. The game goes on here in a moment.</t>
+          <t>Another player took over this world. Joining them…</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>emp_takeover_leaving</t>
+          <t>emp_story_share_got</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>退出中：ほかのプレイヤーに最後のセーブを渡しています…</t>
+          <t>ストーリーでもらえた物のうち、あなたの分を受け取りました：{0}。</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Leaving. Giving the last save to the others…</t>
+          <t>You get your share of what the story gave: {0}.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>emp_ui_limited_bought</t>
+          <t>emp_story_share_mail</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>それはもう買いました。</t>
+          <t>ストーリーでもらえた物のうち、あなたの分（{0}）を拠点の郵便に送りました。</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>You already bought this one.</t>
+          <t>Your share of what the story gave ({0}) was sent to the base's mail.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>emp_story_share</t>
+          <t>emp_ui_report</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>{0}の分け前</t>
+          <t>不具合レポートを作成</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>{0}'s share</t>
+          <t>Prepare a bug report</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_once_per_player</t>
+          <t>emp_ui_report_desc</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>一度きりの報酬をプレイヤーごとに</t>
+          <t>ゲームとMODのログをまとめた zip をデスクトップに作ります。セーブと設定ファイルは含みません。不具合を報告するときに送ってください。</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>One-time rewards for every player</t>
+          <t>Writes a zip with the game and mod logs on your desktop. No save, no settings. Send it when you report a problem.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_once_per_player</t>
+          <t>emp_ui_report_done</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>店の限定品と、ストーリーでもらえる物（依頼の報酬、会話の贈り物）が、プレイヤーごとに1回ずつ手に入ります。オフ：最初のひとりだけ（元のゲームと同じ）。</t>
+          <t>レポートを作成しました：{0}</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>One-time shop goods and story gifts, like quest rewards, go once to each player. Unticked, only the first player gets them, as in the base game.</t>
+          <t>Bug report written: {0}</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>emp_takeover_rejoin</t>
+          <t>emp_ui_report_failed</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
+          <t>レポートを作成できませんでした。</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Another player took over this world. Joining them…</t>
+          <t>The bug report could not be written.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>emp_story_share_got</t>
+          <t>emp_ui_sv_bills</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ストーリーでもらえた物のうち、あなたの分を受け取りました：{0}。</t>
+          <t>税金請求書の数を修復（カウント {0}、実在 {1}）</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>You get your share of what the story gave: {0}.</t>
+          <t>Repair the tax bill count ({0} counted, {1} exist)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>emp_story_share_mail</t>
+          <t>emp_ui_sv_bills_desc</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ストーリーでもらえた物のうち、あなたの分（{0}）を拠点の郵便に送りました。</t>
+          <t>カウントが実際の請求書より多いとき（古い不具合）、実際の数に合わせます。増やすことはありません。</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Your share of what the story gave ({0}) was sent to the base's mail.</t>
+          <t>If the count is above the bills that exist (an old bug), it is set to the real number. It is never raised.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>emp_ui_report</t>
+          <t>emp_ui_sv_bills_done</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>不具合レポートを作成</t>
+          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Prepare a bug report</t>
+          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>emp_ui_report_desc</t>
+          <t>emp_ui_sv_bills_none</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ゲームとMODのログをまとめた zip をデスクトップに作ります。セーブと設定ファイルは含みません。不具合を報告するときに送ってください。</t>
+          <t>カウントは実在する請求書と一致しています。</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Writes a zip with the game and mod logs on your desktop. No save, no settings. Send it when you report a problem.</t>
+          <t>The count matches the bills that exist.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>emp_ui_report_done</t>
+          <t>emp_ui_chara_delete</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>レポートを作成しました：{0}</t>
+          <t>キャラクターを削除する</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Bug report written: {0}</t>
+          <t>Delete a character</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>emp_ui_report_failed</t>
+          <t>emp_ui_chara_delete_confirm</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>レポートを作成できませんでした。</t>
+          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>The bug report could not be written.</t>
+          <t>Delete #1? Its belongings go with it. Its companions stay in this world.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills</t>
+          <t>emp_ui_chara_deleted</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>未払いの税金請求書：カウント {0}、実在 {1}（修復する）</t>
+          <t>キャラクターを削除しました。</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Unpaid tax bills: counted {0}, existing {1} (repair)</t>
+          <t>The character was deleted.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills_desc</t>
+          <t>emp_ui_sv_cfg_delete_chara</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>カウントが実際の請求書より多いとき（古い不具合）、実際の数に合わせます。増やすことはありません。</t>
+          <t>プレイヤーが自分のキャラを削除できる</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>If the count is above the bills that exist (an old bug), it is set to the real number. It is never raised.</t>
+          <t>Players can delete their characters</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills_done</t>
+          <t>emp_ui_sv_desc_delete_chara</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
+          <t>キャラの一覧から削除します（確認は2回）。持ち物も消え、仲間は世界に残ります。</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
+          <t>From the character list, with two confirmations; belongings go too, companions stay in the world.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills_none</t>
+          <t>emp_world_setting_host</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>カウントは実在する請求書と一致しています。</t>
+          <t>世界の設定はホストのものです。変更は保存されませんでした。</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>The count matches the bills that exist.</t>
+          <t>World settings belong to the host. Your changes were not kept.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>emp_ui_chara_delete</t>
+          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>キャラクターを削除する</t>
+          <t>自動戦闘はそれぞれ自分の仲間を守る</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Delete a character</t>
+          <t>Auto combat guards each player's party</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>emp_ui_chara_delete_confirm</t>
+          <t>emp_ui_sv_desc_auto_combat_per_player</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
+          <t>自動戦闘は、使っているプレイヤーとその仲間を、本人の戦術とスタミナで致命的な一撃から守ります。オフ：ホストの自動戦闘が全員を守り、友人の自動戦闘は誰も守りません。</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Delete #1? Its belongings go with it. Its companions stay in this world.</t>
+          <t>Auto combat saves its user and their companions from a deadly hit, with their own tactics and stamina. Off: the host's auto combat protects everyone and a friend's protects no one.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>emp_ui_chara_deleted</t>
+          <t>emp_duel_win</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>キャラクターを削除しました。</t>
+          <t>{0}との決闘に勝った！</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>The character was deleted.</t>
+          <t>You win the duel against {0}!</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_delete_chara</t>
+          <t>emp_duel_lose</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>プレイヤーが自分のキャラを削除できる</t>
+          <t>{0}との決闘に負けた。</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Players can delete their characters</t>
+          <t>You lose the duel against {0}.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_delete_chara</t>
+          <t>emp_duel_wait</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>キャラの一覧から削除します（確認は2回）。持ち物も消え、仲間は世界に残ります。</t>
+          <t>まだ {0} に決闘を申し込めません。</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Done from the character list, with two confirmations. Belongings go too. Companions stay in the world.</t>
+          <t>You can't challenge {0} again so soon.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>emp_world_setting_host</t>
+          <t>emp_trade_gold_button</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>世界の設定はホストのものです。変更は保存されませんでした。</t>
+          <t>お金</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>World settings belong to the host. Your changes were not kept.</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
+          <t>emp_trade_locked</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>自動戦闘はそれぞれ自分の仲間を守る</t>
+          <t>変更があったばかりだ。少し待ってから確定しよう。</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Each player's auto combat protects their own</t>
+          <t>The offer just changed. Wait a moment before validating.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_combat_per_player</t>
+          <t>emp_trade_log_add</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>自動戦闘は、使っているプレイヤーとその仲間を、自分の戦術とスタミナで致命的な一撃から守ります。オフのときは、ホストの自動戦闘が全員を守り、友人の自動戦闘は誰も守りません。</t>
+          <t>{0}が{1}を差し出した。</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Auto combat saves the player using it, and their companions, from a deadly hit, with their own tactics and stamina. Unticked, the host's auto combat protects everyone and a friend's protects no one.</t>
+          <t>{0} offers {1}.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>emp_duel_win</t>
+          <t>emp_trade_log_remove</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>{0}との決闘に勝った！</t>
+          <t>{0}が{1}を引っ込めた。</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>You win the duel against {0}!</t>
+          <t>{0} takes back {1}.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>emp_duel_lose</t>
+          <t>emp_trade_log_gold</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>{0}との決闘に負けた。</t>
+          <t>{0}の提示額は{1}オレンになった。</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>You lose the duel against {0}.</t>
+          <t>{0} now offers {1} gold.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>emp_duel_wait</t>
+          <t>emp_trade_cant_offer</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>まだ {0} に決闘を申し込めません。</t>
+          <t>{0}は差し出せない。</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>You can't challenge {0} again so soon.</t>
+          <t>You can't offer {0}.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>emp_trade_gold_button</t>
+          <t>emp_trade_status</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>お金</t>
+          <t>{0}: {1}オレン、{2}</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>{0}: {1} gold, {2}</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>emp_trade_locked</t>
+          <t>emp_ui_sv_cfg_town_life</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>変更があったばかりだ。少し待ってから確定しよう。</t>
+          <t>全プレイヤーの周りで町の人が暮らす</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>The offer just changed. Wait a moment before validating.</t>
+          <t>Towns live around every player</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>emp_trade_log_add</t>
+          <t>emp_ui_sv_desc_town_life</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>{0}が{1}を差し出した。</t>
+          <t>町の人は、すべてのプレイヤーの近くで雑談し、あいさつし、噂し、石を投げます。噂と石はそのプレイヤーのカルマで決まります。オフ：ホストの近くだけで、ホストのカルマで決まります（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>{0} offers {1}.</t>
+          <t>Townspeople chat, greet, gossip and throw stones near every player, by that player's karma. Off: only near the host, by the host's karma, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>emp_trade_log_remove</t>
+          <t>emp_ui_sv_cfg_town_boards</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>{0}が{1}を引っ込めた。</t>
+          <t>町の掲示板を全員の分で作る</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>{0} takes back {1}.</t>
+          <t>Town boards suit every player present</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>emp_trade_log_gold</t>
+          <t>emp_ui_sv_desc_town_boards</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>{0}の提示額は{1}オレンになった。</t>
+          <t>町の掲示板を引き直すとき、マップにいる中で最も高い名声で名声の必要な依頼が開き、難易度はその場のプレイヤーに合わせます（個人クエストが必要）。オフ：ホストのキャラだけで決まります（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>{0} now offers {1} gold.</t>
+          <t>A redrawn town board opens fame quests by the highest fame on the map and sets difficulty by the players present; needs personal quests. Off: the host's character alone, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>emp_trade_cant_offer</t>
+          <t>emp_ui_sv_cfg_shops_from_every_player</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>{0}は差し出せない。</t>
+          <t>全員の進行に合わせた店</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>You can't offer {0}.</t>
+          <t>Shops suit every player present</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>emp_trade_status</t>
+          <t>emp_ui_sv_desc_shops_from_every_player</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>{0}: {1}オレン、{2}</t>
+          <t>店の仕入れはマップ上で最も良いプレイヤーの特性で決まり、特別な棚（結婚とカセットの店、ロイテルのマート、異国の商人）は店を開いたプレイヤーの進行に従います。オフ：ホストの進行（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>{0}: {1} gold, {2}</t>
+          <t>Restocks use the best stock bonus on the map; special shelves (marriage and tape shop, Loytel's mart, exotic merchant) follow the player who opens the shop. Off: the host's progress, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_town_life</t>
+          <t>emp_ui_sv_cfg_nearest_spawns</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>全プレイヤーの周りで町の人が暮らす</t>
+          <t>スポーンはいちばん近いプレイヤーから</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Town life around every player</t>
+          <t>Spawns follow the nearest player</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_town_life</t>
+          <t>emp_ui_sv_desc_nearest_spawns</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>町の人は、ホストの画面の近くだけでなく、すべてのプレイヤーの近くで雑談し、あいさつし、噂し、石を投げます。噂と石は、その相手のプレイヤー自身のカルマで決まります。オフにすると、ホストの近くだけで、ホストのカルマで決まります（バニラと同じ）。</t>
+          <t>マップのスポーン（伝説の個体の確率、サンタなどの敵味方、進化個体、ビッグダディ、祠）は、いちばん近いプレイヤーの特性で決まります。オフ：ホストの特性（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Townspeople chat, greet, gossip and throw stones near every player, not only near the host's screen. Gossip and stones go by the karma of the player they are about. Unticked: only near the host, by the host's karma (as in vanilla).</t>
+          <t>What a map spawns (legendary chance, Santa's friends or foes, evolved, big daddy, shrines) reads the feats of the nearest player. Off: the host's feats, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_town_boards</t>
+          <t>emp_ui_sv_cfg_enforce_ownership</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>町の掲示板を全員の分で作る</t>
+          <t>他人のキャラクターへの変更を拒否する</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Town boards from every player present</t>
+          <t>Refuse changes to others' characters</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_town_boards</t>
+          <t>emp_ui_sv_desc_enforce_ownership</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ゲームが町の掲示板の依頼を引き直すとき、マップにいる全員の中で最も高い名声が名声が必要な依頼を開き、難易度は在場のプレイヤーの平均になります。オフの場合はホストのキャラだけで決まります（原作どおり）。（個人クエストが有効な場合のみ。）</t>
+          <t>自分のキャラでも仲間でもないキャラについてプレイヤーのゲームが送る情報（行動、ダメージ、スキル、パーティ）を拒否します。取引、贈り物、自分の仲間への命令は拒否されません。オフ：ログに書くだけです。</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>When the game draws a town board's offers again, the highest fame among the players on the map opens the offers that need fame, and the difficulty follows the players present. Unticked, the board is drawn for the host's character alone (as in the base game). Needs personal quests.</t>
+          <t>What a player's game sends about a character neither theirs nor their companion (task, damage, skills, party) is refused; trades, gifts and orders to own companions never are. Off: it is only logged.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_shops_from_every_player</t>
+          <t>emp_ui_sv_cfg_activities_from_actor</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>全員の進行に合わせた店</t>
+          <t>樽と母乳はそのプレイヤーのもの</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Shops from every player present</t>
+          <t>Barrels and milk follow the player</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shops_from_every_player</t>
+          <t>emp_ui_sv_desc_activities_from_actor</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>店の仕入れ量は地図上で最も強いプレイヤーの特性で決まり、特別な棚（結婚とカセットの店、ロイテルのマート、異国の商人）は店を開いたプレイヤーの進行に従います。オフの場合は常にホストの進行（原作と同じ）。</t>
+          <t>樽の酒は樽にいちばん近いプレイヤーの技能で作られ、母乳を飲んだ幼いペットは飼い主の調教で育ち、飼い主が経験を得ます。オフ：ホストのキャラクター（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>A shop restocks with the stock bonus of the best player on the map, and its special shelves (marriage and tape shop, Loytel's mart, exotic merchant) follow the player who opens it. Off: always the host's progress, as the game does.</t>
+          <t>A barrel brews with the skills of the nearest player; a baby pet drinking its mother's milk grows by its owner's taming, and the owner learns from it. Off: the host's character, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_nearest_spawns</t>
+          <t>emp_ui_sv_cfg_summons_follow_master</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>スポーンはいちばん近いプレイヤーから</t>
+          <t>召喚物は召喚者についていく</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Spawns from the nearest player</t>
+          <t>Summons follow their summoner</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_nearest_spawns</t>
+          <t>emp_ui_sv_desc_summons_follow_master</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>マップのスポーン（伝説の個体の確率、サンタなどの敵味方、進化個体、ビッグダディ、祠）は、ホストではなくスポーン地点にいちばん近いプレイヤーの特性で決まります。オフならホストの特性（元のゲームと同じ）。</t>
+          <t>プレイヤーが召喚したものは、ホストと一緒でも単独でも、そのプレイヤーが行く所へ行きます。オフ：ホストがマップを離れると友人の召喚物は消えます。</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>What a map spawns (legendary chance, friend or foe of Santa and the like, evolved, big daddy, shrines) reads the feats of the player nearest to the spawn, not always the host's. Unticked: the host's, as in the game.</t>
+          <t>A player's summons go where that player goes, with the host or not. Off: friends' summons vanish when the host leaves the map.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_enforce_ownership</t>
+          <t>emp_ui_sv_cfg_players_at_base</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>他人のキャラクターについての情報を拒否する</t>
+          <t>拠点はすべてのプレイヤーを数える</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Refuse what a player's game says about someone else's character</t>
+          <t>The base counts every player</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_enforce_ownership</t>
+          <t>emp_ui_sv_desc_players_at_base</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>自分のキャラクターでも自分の仲間でもないキャラクターについて、プレイヤーのゲームが送る情報（行動、ダメージ、スキル、パーティ）を拒否します。オフのときはログに書くだけです。取引、他のプレイヤーへの贈り物、自分の仲間への命令は拒否されません。</t>
+          <t>拠点のマップにいる誰かが起きていれば襲撃が来て、幸運の月は誰かの神に従い、プレイヤーと過ごした日数はどこでも数えます。オフ：拠点のマップを動かすゲームのプレイヤーだけ。</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>What a player's game sends about a character that is neither theirs nor one of their companions (its task, damage, skills, party) is refused. Unticked, it is only written to the log. A trade, a gift to another player or an order to one's own companion is never refused.</t>
+          <t>Raids come while any player on the base map is awake, the lucky month follows any player's god, and days with a player count wherever a player is. Off: only the player whose game runs the base map.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_activities_from_actor</t>
+          <t>emp_ui_travel_bystander</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>樽と母乳はそのプレイヤーのもの</t>
+          <t>{0}が{1}時間旅をした。世界は進んだが、あなたは何も失っていない。</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Barrels and milk follow the player</t>
+          <t>{0} travelled {1} h. The world moved on; you lost nothing.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_activities_from_actor</t>
+          <t>emp_ui_sv_sec_joining</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>オン：樽で醸造された酒は樽に一番近いプレイヤーの技能で作られ、母乳を飲んだ幼いペットは飼い主の調教で育ち、飼い主が経験を得る。オフ：ホストのキャラクターによる（一人で遊ぶ時と同じ）</t>
+          <t>参加</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>On: what a barrel brews is made with the skills of the player nearest to it, and a baby pet drinking its mother's milk grows by its owner's taming, and its owner learns from it. Off: both follow the host's character, as for a player alone</t>
+          <t>Joining</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_summons_follow_master</t>
+          <t>emp_ui_sv_sec_together</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>召喚物は召喚者についていく</t>
+          <t>一緒に遊ぶ</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Summons follow their summoner</t>
+          <t>Playing together</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_summons_follow_master</t>
+          <t>emp_ui_sv_sec_host_leaves</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>プレイヤーが召喚したものは、ホストと一緒でも単独でも、そのプレイヤーが行く所へ行く。オフ：ホストがマップを離れると他のプレイヤーの召喚物は消える</t>
+          <t>ホストが抜けたとき</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>What a player summoned goes where that player goes, with the host or on its own. Off: the summons of the others vanish when the host leaves the map</t>
+          <t>When the host leaves</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_players_at_base</t>
+          <t>emp_ui_sv_sec_fallbacks</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>拠点はすべてのプレイヤーを数える</t>
+          <t>従来のホスト中心のルール</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>The base counts every player</t>
+          <t>Classic host-led fallbacks</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_players_at_base</t>
+          <t>emp_ui_sv_sec_time_details</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>拠点のマップにいる誰かが起きていれば襲撃が来る。幸運の月は誰か一人の神に従う。プレイヤーと過ごした日数はプレイヤーのいる所で数える。オフ：拠点のマップを動かすゲームのプレイヤーだけ</t>
+          <t>時間の詳細</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Raids come while any player on the base map is awake, the lucky month follows the god of any of them, days with a player count wherever a player is. Off: only the player whose game runs the base map</t>
+          <t>Time details</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_map_time</t>
+          <t>emp_ui_sv_sec_comfort</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ワールドマップの時間：{0}</t>
+          <t>快適さ</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>World map time: {0}</t>
+          <t>Comfort</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_map_time</t>
+          <t>emp_ui_sv_sec_repair</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>クリックで切り替え。共有時計：ワールドマップも他のマップと同じで、誰の一歩でも日付が進む。他のプレイヤーは時間に追いつくが、満腹度もクエストの時間も失わない（戦闘中・読み込み中・会話中は最大60秒待つ）。一緒に旅：全員がワールドマップにいる時だけ、誰の一歩でも日付が進む。そうでなければ旅人は自分のターンだけを払い、日付は進まない。</t>
+          <t>接続と修復</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Click to change. Shared clock: the world map is a map like any other, every step of anyone moves the date; the others catch up without losing hunger or quest time (waiting up to 60 s while they fight, load or talk). Travel together: a step moves the date only while all the players are on the world map, whoever steps; otherwise the traveller pays its own turns and the date stays.</t>
+          <t>Connection and repair</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>emp_ui_sv_wmt_SharedClock</t>
+          <t>emp_ui_sv_advanced</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>共有時計</t>
+          <t>詳細な設定を表示</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Shared clock</t>
+          <t>Show advanced options</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>emp_ui_sv_wmt_TravelTogether</t>
+          <t>emp_ui_sv_custom</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>一緒に旅</t>
+          <t>カスタム（詳細な設定を参照）</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Travel together</t>
+          <t>Custom (see Advanced)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>emp_ui_travel_bystander</t>
+          <t>emp_ui_sv_apply_join</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>{0}が{1}時間旅をした。世界は進んだが、あなたは何も失っていない。</t>
+          <t>次に参加するプレイヤーから適用されます。</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>{0} travelled {1} h. The world moved on; you lost nothing.</t>
+          <t>Applies to players who join next.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_joining</t>
+          <t>emp_ui_sv_apply_load</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>参加</t>
+          <t>ワールドの読み込み時に適用されます。</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Joining</t>
+          <t>Applies when a world loads.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_together</t>
+          <t>emp_ui_sv_cfg_who_joins</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>一緒に遊ぶ</t>
+          <t>参加できる人</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Playing together</t>
+          <t>Who can join</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_host_leaves</t>
+          <t>emp_ui_sv_desc_who_joins</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>ホストが抜けたとき</t>
+          <t>誰でも：Elin Together のバージョンだけ一致が必要です。
+同じMOD：友人はホストと同じMODも必要です。
+同じゲームデータ：友人はホストと同じゲームデータも必要です。
+同じMODとゲームデータ：友人は両方とも必要です。</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>When the host leaves</t>
+          <t>Anyone: only the Elin Together version must match.
+Same mods: friends also need the host's mods.
+Same game data: friends also need the host's game data.
+Same mods and game data: friends need both.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_fallbacks</t>
+          <t>emp_ui_sv_opt_who_joins_anyone</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>従来のホスト中心のルール</t>
+          <t>誰でも</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Classic host-led fallbacks</t>
+          <t>Anyone</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_time_details</t>
+          <t>emp_ui_sv_opt_who_joins_mods</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>時間の詳細</t>
+          <t>同じMOD</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Time details</t>
+          <t>Same mods</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_comfort</t>
+          <t>emp_ui_sv_opt_who_joins_data</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>快適さ</t>
+          <t>同じゲームデータ</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Comfort</t>
+          <t>Same game data</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_repair</t>
+          <t>emp_ui_sv_opt_who_joins_both</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>接続と修復</t>
+          <t>同じMODとゲームデータ</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Connection and repair</t>
+          <t>Same mods and game data</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>emp_ui_sv_advanced</t>
+          <t>emp_ui_sv_cfg_world_map_choice</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>詳細な設定を表示</t>
+          <t>ワールドマップの時間</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Show advanced options</t>
+          <t>World map time</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>emp_ui_sv_custom</t>
+          <t>emp_ui_sv_desc_world_map_choice</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>カスタム（詳細な設定を参照）</t>
+          <t>共有時計：ワールドマップで誰かが一歩進むたびに日付が進み、他の人は満腹度やクエストの時間を失わずに追いつきます。
+一緒に旅：全員がワールドマップにいるときだけ日付が進みます。
+自分のペース：共有時計と同じですが、他の人が別の場所にいる間に旅するプレイヤーは先に進み、その時間は本人の満腹度とクエストが払います。日付は、全員がワールドマップに揃うか同じ夜に眠るまで待ちます。</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Custom (see Advanced)</t>
+          <t>Shared clock: every step on the world map moves the date; the others catch up without losing hunger or quest time.
+Travel together: the date moves only while all players are on the world map.
+Personal pace: as Shared clock, but a player travelling while the others are elsewhere runs ahead, paying with their own hunger and quests; the date waits until everyone is on the world map or sleeps the same night.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>emp_ui_sv_apply_join</t>
+          <t>emp_ui_sv_opt_world_map_choice_SharedClock</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>次に参加するプレイヤーから適用されます。</t>
+          <t>共有時計</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Applies to players who join next.</t>
+          <t>Shared clock</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>emp_ui_sv_apply_load</t>
+          <t>emp_ui_sv_opt_world_map_choice_TravelTogether</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>ワールドの読み込み時に適用されます。</t>
+          <t>一緒に旅</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Applies when a world loads.</t>
+          <t>Travel together</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_who_joins</t>
+          <t>emp_ui_sv_cfg_combat_pace</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>参加できる人</t>
+          <t>戦闘のペース</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Who can join</t>
+          <t>Combat pace</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_who_joins</t>
+          <t>emp_ui_sv_desc_combat_pace</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>参加するために、友人のゲームがあなたのゲームと同じでなければならないもの。Elin Together のバージョンは常に一致が必要です。</t>
+          <t>各自のペース：モンスターは戦っているプレイヤーが行動したときに行動し、誰も待たず、全員がソロのように歩きます。
+ターン制：戦闘中はプレイヤーが順番に行動します。
+全員の平均速度：全員が平均の速度で動きます。
+従来どおり：ホストのゲームと同じように進みます。</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>What a friend's game must share with yours to join. The Elin Together version must always match.</t>
+          <t>Each player's own pace: a monster acts when the player it fights acts; nobody waits and everyone walks as in a solo game.
+Turn-based: players take turns in a fight.
+Shared average speed: everyone moves at the average speed.
+Classic: the game runs as it does for the host.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_who_joins_anyone</t>
+          <t>emp_ui_sv_opt_combat_pace_own</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>誰でも</t>
+          <t>各自のペース</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>Each player's own pace</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_who_joins_mods</t>
+          <t>emp_ui_sv_opt_combat_pace_turns</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>同じMOD</t>
+          <t>ターン制</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Same mods</t>
+          <t>Turn-based</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_who_joins_data</t>
+          <t>emp_ui_sv_opt_combat_pace_average</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>同じゲームデータ</t>
+          <t>全員の平均速度</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Same game data</t>
+          <t>Shared average speed</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_who_joins_both</t>
+          <t>emp_ui_sv_opt_combat_pace_classic</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>同じMODとゲームデータ</t>
+          <t>従来どおり</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Same mods and game data</t>
+          <t>Classic</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_map_choice</t>
+          <t>emp_ui_sv_cfg_own_everything</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ワールドマップでの時間</t>
+          <t>誰の進行を使うか</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Time on the world map</t>
+          <t>Whose progress counts</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_map_choice</t>
+          <t>emp_ui_sv_desc_own_everything</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>共有時計：ワールドマップで誰かが一歩進むたびに日付が進み、他の人は満腹度やクエストの時間を失わずに追いつきます。一緒に旅：全員がワールドマップにいるときだけ日付が進みます。自分のペース：共有時計と同じですが、仲間が別の場所にいる間に旅するプレイヤーは世界より先に進みます。その時間は本人の満腹度と自分のクエストが払い、日付は全員がワールドマップに揃うか同じ夜に眠るまで待ちます。</t>
+          <t>各プレイヤー自身：クエスト、名声、出荷のお金、一度きりの報酬、税、掲示板、店、出現、樽、自動戦闘、拠点、召喚がそれぞれのプレイヤーに従います。
+ホストのキャラクター：すべてホストのキャラクターに従います（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Shared clock: every step of anyone on the world map moves the date; the others catch up without losing hunger or quest time. Travel together: the date moves only while all players are on the world map. Personal pace: as the shared clock, but a player travelling while the others are elsewhere runs ahead of the world: its hunger and its own quests pay the hours, and the date waits until everyone is on the world map together or sleeps the same night.</t>
+          <t>Each player's own: quests, fame, shipping money, one-time rewards, tax, town boards, shops, spawns, barrels, auto combat, the base and summons follow each player.
+The host's character: they all follow the host's character, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_choice_SharedClock</t>
+          <t>emp_ui_sv_opt_own_everything_yes</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>共有時計</t>
+          <t>各プレイヤー自身</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Shared clock</t>
+          <t>Each player's own</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_choice_TravelTogether</t>
+          <t>emp_ui_sv_opt_own_everything_no</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>一緒に旅</t>
+          <t>ホストのキャラクター</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Travel together</t>
+          <t>The host's character</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_combat_pace</t>
+          <t>emp_ui_sv_cfg_building</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>戦闘のペース</t>
+          <t>建築と拠点</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Combat pace</t>
+          <t>Building and base</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_combat_pace</t>
+          <t>emp_ui_sv_desc_building</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>各自のペース：モンスターは戦っているプレイヤーが行動したときに行動し、誰も待たず、全員がソロのように歩きます。ターン制：戦闘中はプレイヤーが順番に行動します。平均速度：全員が平均の速度で動きます。従来どおり：ホストのゲームと同じです。</t>
+          <t>全員が建築と管理：全員が拠点で建築モードを使い、拠点を管理（研究、方針、名前、住人）できます。友人は自分のお金と素材を払います。
+全員が管理、建築はホストのみ：全員が拠点を管理でき、建築モードはホストだけが使えます。
+ホストのみ：建築も拠点の管理もホストだけです。</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Own pace: a monster acts when the player it fights acts, nobody waits, everyone walks as in a solo game. Turn-based: players take turns in a fight. Shared average: everyone moves at the average speed. Classic: as the game runs for the host.</t>
+          <t>Everyone builds and manages: all players use build mode in the base and manage it (research, policies, names, residents); friends pay their own gold and materials.
+Everyone manages, only the host builds: all players manage the base; only the host uses build mode.
+Only the host: only the host builds and manages the base.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_combat_pace_own</t>
+          <t>emp_ui_sv_opt_building_all</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>各自のペース</t>
+          <t>全員が建築と管理</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Each player's own pace</t>
+          <t>Everyone builds and manages</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_combat_pace_turns</t>
+          <t>emp_ui_sv_opt_building_manage</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>ターン制</t>
+          <t>全員が管理、建築はホストのみ</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Turn-based</t>
+          <t>Everyone manages, only the host builds</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_combat_pace_average</t>
+          <t>emp_ui_sv_opt_building_host</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>全員の平均速度</t>
+          <t>ホストのみ</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Shared average speed</t>
+          <t>Only the host</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_combat_pace_classic</t>
+          <t>emp_ui_sv_cfg_fights</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>従来どおり</t>
+          <t>プレイヤー同士の戦い</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Classic</t>
+          <t>Fights between players</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_own_everything</t>
+          <t>emp_ui_sv_desc_fights</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>全員が自分のクエスト、店、報酬、町の暮らしを持つ</t>
+          <t>なし：決闘はなく、プレイヤーの致命的な一撃でも相手はHP0で生き残ります。
+決闘のみ：相手のキャラクターのメニューから挑戦でき、誰も死にません。
+決闘と本当に倒す：プレイヤーの致命的な一撃で他のプレイヤーが死ぬこともあります。</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Every player gets their own quests, shops, rewards and town life</t>
+          <t>Off: no duels, and a deadly blow from a player leaves the other alive at 0 HP.
+Duels only: challenge another player from the menu on their character; nobody dies.
+Duels and real kills: a deadly blow from a player can also kill another player.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_own_everything</t>
+          <t>emp_ui_sv_opt_fights_off</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>クエスト、名声、出荷のお金、一度きりの報酬、税、掲示板、店、出現、樽、自動戦闘、拠点、召喚がそれぞれのプレイヤーに従います。いいえ：基本のゲームと同じく、ホストのキャラクターに従います。個別の項目は詳細な設定にあります。</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Quests, fame, shipping money, one-time rewards, tax, town boards, shops, spawns, barrels, auto combat, the base and summons follow each player. No: they follow the host's character, as in the base game. Each one is in Advanced.</t>
+          <t>Off</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_own_everything_yes</t>
+          <t>emp_ui_sv_opt_fights_duels</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>はい</t>
+          <t>決闘のみ</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Duels only</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_own_everything_no</t>
+          <t>emp_ui_sv_opt_fights_kills</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>いいえ、全員ホストのキャラクター基準</t>
+          <t>決闘と本当に倒す</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>No, the host's character for all</t>
+          <t>Duels and real kills</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_building</t>
+          <t>emp_ui_sv_cfg_host_leaves</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>建築と拠点</t>
+          <t>ホストが抜けたとき</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Building and base</t>
+          <t>When the host leaves</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_building</t>
+          <t>emp_ui_sv_desc_host_leaves</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>拠点で建築モードを使い、拠点を管理（研究、方針、名前、住人）できる人。友人は自分のお金と素材を払います。</t>
+          <t>ワールドは待つ：ワールドはホストのPCだけにあります。
+友人がバックアップを持つ：自動保存のたびに、友人のPCにもワールドのコピーが残ります。
+他のプレイヤーが続ける：友人がそのコピーからワールドを開き、ゲームが続きます。</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Who can use build mode in the base and manage it: research, policies, names, residents. Friends pay their own gold and materials.</t>
+          <t>The world waits: the world is on the host's PC only.
+Friends keep a backup: after each automatic save, every friend's PC keeps a copy of the world.
+Another player carries on: a friend opens the world from that copy and the game goes on.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_building_all</t>
+          <t>emp_ui_sv_opt_host_leaves_waits</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>全員が建築と管理</t>
+          <t>ワールドは待つ</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Everyone builds and manages</t>
+          <t>The world waits</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_building_manage</t>
+          <t>emp_ui_sv_opt_host_leaves_backup</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>全員が管理、建築はホストのみ</t>
+          <t>友人がバックアップを持つ</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Everyone manages, only the host builds</t>
+          <t>Friends keep a backup</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_building_host</t>
+          <t>emp_ui_sv_opt_host_leaves_carry_on</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>ホストのみ</t>
+          <t>他のプレイヤーが続ける</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Only the host</t>
+          <t>Another player carries on</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_fights</t>
+          <t>emp_ui_sv_sec_preset</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>プレイヤー同士の戦い</t>
+          <t>一緒に遊ぶ方法</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Fights between players</t>
+          <t>How you play together</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_fights</t>
+          <t>emp_ui_sv_cfg_preset</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>決闘：相手のキャラクターのメニューから挑戦でき、誰も死にません。本当に倒す：プレイヤーの致命的な一撃で他のプレイヤーが死ぬことがあります。</t>
+          <t>ルール</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Duels: challenge another player from the menu on their character; nobody dies. Real kills: a deadly blow from a player can kill another player.</t>
+          <t>Rules</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_fights_off</t>
+          <t>emp_ui_sv_opt_preset_recommended</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>おすすめの協力プレイ</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Recommended co-op</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_fights_duels</t>
+          <t>emp_ui_sv_opt_preset_classic</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>決闘のみ</t>
+          <t>従来のホスト主導</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Duels only</t>
+          <t>Classic host-led</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_fights_kills</t>
+          <t>emp_ui_sv_opt_preset_custom</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>決闘と本当に倒す</t>
+          <t>カスタム</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Duels and real kills</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_host_leaves</t>
+          <t>emp_ui_sv_desc_preset_recommended</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ホストが抜けたら</t>
+          <t>全員が一人前のプレイヤーとして遊びます。自分のクエスト、店、報酬、自分のペースで。</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>If the host leaves</t>
+          <t>Everyone plays as a full player: their own quests, shops and rewards, at their own pace.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_host_leaves</t>
+          <t>emp_ui_sv_desc_preset_classic</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ワールドは待つ：ワールドはホストのPCだけにあります。友人がバックアップを持つ：自動保存のたびに、友人のPCにもコピーが残ります。他のプレイヤーが続ける：友人がそのコピーからワールドを開き、ゲームが続きます。</t>
+          <t>ホストが導きます。全員がホストについて行き、戦闘はターン制、建築と拠点はホストのみ、クエストや報酬はホストのキャラクター基準です。</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>The world waits: it is on the host's PC only. Friends keep a backup: after each automatic save, every friend's PC keeps a copy. Another player carries on: a friend opens the world from that copy and the game goes on.</t>
+          <t>The host leads: everyone follows the host, fights are turn-based, only the host builds and manages the base, and quests and rewards go by the host's character.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_host_leaves_waits</t>
+          <t>emp_ui_sv_diff</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>ワールドは待つ</t>
+          <t>おすすめとの違い（{0}件）：{1}</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>The world waits</t>
+          <t>Differences from recommended ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_host_leaves_backup</t>
+          <t>emp_ui_sv_reset</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>友人がバックアップを持つ</t>
+          <t>おすすめに戻す</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Friends keep a backup</t>
+          <t>Reset to recommended</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_host_leaves_carry_on</t>
+          <t>emp_ui_sv_undo</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>他のプレイヤーが続ける</t>
+          <t>最後の変更を元に戻す</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Another player carries on</t>
+          <t>Undo the last change</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_preset</t>
+          <t>emp_ui_sv_more</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>一緒に遊ぶ方法</t>
+          <t>その他の設定は Elin Together のウィンドウ（「ワールドのルール」タブ）にあります。</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>How you play together</t>
+          <t>More options in the Elin Together window (World rules tab).</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_preset</t>
+          <t>emp_ui_cl_sec_controls</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>ルール</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Controls</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_preset_recommended</t>
+          <t>emp_ui_cl_sec_mods</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>おすすめの協力プレイ</t>
+          <t>ワークショップのMOD</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Recommended co-op</t>
+          <t>Workshop mods</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_preset_classic</t>
+          <t>emp_ui_cl_sec_depot</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>従来のホスト主導</t>
+          <t>共有のセーブフォルダ（任意）</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Classic host-led</t>
+          <t>Shared save folder (optional)</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_preset_custom</t>
+          <t>emp_ui_cl_sec_help</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>カスタム</t>
+          <t>ヘルプ</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Help</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_preset_recommended</t>
+          <t>emp_ui_cl_desc_ping</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>全員が一人前のプレイヤーとして遊びます。自分のクエスト、店、報酬、自分のペースで。</t>
+          <t>このキーを押すと、マップ上の場所を他のプレイヤーに知らせます。</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Everyone plays as a full player: their own quests, shops and rewards, at their own pace.</t>
+          <t>Press this key to show a spot on the map to the other players.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_preset_classic</t>
+          <t>emp_ui_cl_desc_depot</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ホストが導きます。全員がホストについて行き、戦闘はターン制、建築と拠点はホストのみ、クエストや報酬はホストのキャラクター基準です。</t>
+          <t>ワールドを置いておく場所で、誰でもホストになれます。一緒に遊ぶだけなら必要ありません。</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>The host leads: everyone follows the host, fights are turn-based, only the host builds and manages the base, quests and rewards go by the host's character.</t>
+          <t>Where the world is kept so that any of you can host it. Not needed to play together.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>emp_ui_sv_diff</t>
+          <t>emp_ui_rules_title</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>おすすめとの違い {0} 件：{1}</t>
+          <t>このワールドのルール</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>{0} differences from recommended: {1}</t>
+          <t>This world's rules</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>emp_ui_sv_reset</t>
+          <t>emp_ui_rules_note</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>おすすめに戻す</t>
+          <t>ホストが決めたルールです。変更は全員に同時に適用されます。</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Reset to recommended</t>
+          <t>Set by the host. A change applies to everyone at once.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>emp_ui_sv_undo</t>
+          <t>emp_ui_rules_line</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>最後の変更を元に戻す</t>
+          <t>{0}：{1}</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Undo the last change</t>
+          <t>{0}: {1}</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>emp_ui_sv_more</t>
+          <t>emp_ui_rules_changed</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>その他の設定は Elin Together のウィンドウ（「ワールドのルール」タブ）にあります。</t>
+          <t>ホストが「{0}」を変更しました：{1} → {2}</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>More options in the Elin Together window (World rules tab).</t>
+          <t>The host changed "{0}": {1} -&gt; {2}</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>emp_ui_cl_sec_controls</t>
+          <t>emp_ui_rules_yes</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>emp_ui_cl_sec_mods</t>
+          <t>emp_ui_rules_no</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ワークショップのMOD</t>
+          <t>いいえ</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Workshop mods</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>emp_ui_cl_sec_depot</t>
+          <t>emp_ui_rules_custom</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>共有のセーブフォルダ（任意）</t>
+          <t>カスタム</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Shared save folder (optional)</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>emp_ui_cl_sec_help</t>
+          <t>emp_ui_sv_opt_world_map_choice_PersonalPace</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>ヘルプ</t>
+          <t>自分のペース</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Personal pace</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_ping</t>
+          <t>emp_ui_sv_cfg_world_map_lead</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>このキーを押すと、マップ上の場所を他のプレイヤーに知らせます。</t>
+          <t>自分のペースの先行時間</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Press this key to show a spot on the map to the other players.</t>
+          <t>Personal pace lead</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_depot</t>
+          <t>emp_ui_sv_desc_world_map_lead</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ワールドを置いておく場所で、誰でもホストになれます。一緒に遊ぶだけなら必要ありません。</t>
+          <t>自分のペースで一人旅するプレイヤーが世界より先に進める時間。これを超えると、その時間は共有時計と同じように全員の日付を進めます。</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Where the world is kept so that any of you can host it. Not needed to play together.</t>
+          <t>How far a player travelling alone may run ahead of the world with Personal pace; past it, their hours move the date for everyone, as with Shared clock.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>emp_ui_rules_title</t>
+          <t>emp_ui_sv_opt_world_map_lead_12</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>このワールドのルール</t>
+          <t>12時間</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>This world's rules</t>
+          <t>12 h</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>emp_ui_rules_note</t>
+          <t>emp_ui_sv_opt_world_map_lead_24</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ホストが決めたルールです。変更は全員に同時に適用されます。</t>
+          <t>24時間</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Set by the host. A change applies to everyone at once.</t>
+          <t>24 h</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>emp_ui_rules_line</t>
+          <t>emp_ui_sv_opt_world_map_lead_48</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>{0}：{1}</t>
+          <t>48時間</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>{0}: {1}</t>
+          <t>48 h</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>emp_ui_rules_changed</t>
+          <t>emp_ui_sv_opt_world_map_lead_72</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>ホストが「{0}」を変更しました：{1} → {2}</t>
+          <t>72時間</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>The host changed "{0}": {1} -&gt; {2}</t>
+          <t>72 h</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>emp_ui_rules_yes</t>
+          <t>emp_ui_travel_lead</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>はい</t>
+          <t>あなたは世界より{0}時間先にいます（旅の時間は満腹度とクエストが払いました。日付は仲間を待っています）。</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>You are +{0} h ahead of the world (your hunger and your quests paid the trip; the date waits for your friends).</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>emp_ui_rules_no</t>
+          <t>emp_ui_travel_lead_paid</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>いいえ</t>
+          <t>世界があなたの旅に追いつきました。</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>The world caught up with your trip.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>emp_ui_rules_custom</t>
+          <t>emp_ui_sv_cfg_global_chat</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>カスタム</t>
+          <t>全員にチャットを届ける</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Chat is read by every player</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_choice_PersonalPace</t>
+          <t>emp_ui_sv_desc_global_chat</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>自分のペース</t>
+          <t>プレイヤーが入力したチャットは、どこにいる全員にも届きます。住民やゲームのセリフはそのマップだけです。オフ：同じマップのプレイヤーにだけ届きます。</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Personal pace</t>
+          <t>What a player types reaches every player, wherever they are; lines of townspeople and the game stay on their map. Off: only players on the same map read it.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_map_lead</t>
+          <t>emp_act_follow</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>一人旅で世界より先に進める時間（自分のペース）</t>
+          <t>ついていく</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>How far a player travelling alone may run ahead (personal pace)</t>
+          <t>Follow</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_map_lead</t>
+          <t>emp_follow_start</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>自分のペース：この時間を超えると、一人旅の時間は共有時計と同じように全員の日付を進めます。</t>
+          <t>#1についていく。何かキーを押すと止まる。</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Personal pace: past this lead, the hours of a player travelling alone move the date for everyone, as with the shared clock.</t>
+          <t>You follow #1. Press any key to stop.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_lead_12</t>
+          <t>emp_follow_stop</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>12時間</t>
+          <t>#1についていくのをやめた。</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>12 h</t>
+          <t>You stop following #1.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_lead_24</t>
+          <t>emp_follow_left</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>24時間</t>
+          <t>#1はこのマップを離れた。ついていくのをやめた。</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>#1 left the map. You stop following.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_lead_48</t>
+          <t>emp_follow_lost</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>48時間</t>
+          <t>#1を見失った。</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>You lost sight of #1.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_world_map_lead_72</t>
+          <t>emp_follow_danger</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>72時間</t>
+          <t>危険だ。ついていくのをやめた。</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>72 h</t>
+          <t>Danger! You stop following.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>emp_ui_travel_lead</t>
+          <t>emp_ui_sv_cfg_follow</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>あなたは世界より{0}時間先にいます（旅の時間は満腹度とクエストが払いました。日付は仲間を待っています）。</t>
+          <t>ほかのプレイヤーについていける</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>You are +{0} h ahead of the world (your hunger and your quests paid the trip; the date waits for your friends).</t>
+          <t>Players can follow each other</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>emp_ui_travel_lead_paid</t>
+          <t>emp_ui_sv_desc_follow</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>世界があなたの旅に追いつきました。</t>
+          <t>ほかのプレイヤーをクリックして「ついていく」を選ぶと、同じマップの中で自動で後を歩きます。キー、攻撃、敵、相手のマップ移動で止まります。</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>The world caught up with your trip.</t>
+          <t>Click another player and choose Follow to walk after them on the same map; a key, a blow, a monster in sight or that player leaving the map stops it.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_global_chat</t>
+          <t>emp_people_players</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>全員にチャットを届ける</t>
+          <t>プレイヤー</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Chat is read by every player</t>
+          <t>Players</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_global_chat</t>
+          <t>emp_people_offline</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>プレイヤーが入力したチャットは、別のマップ、ワールドマップ、単独行動中など、どこにいる全員にも届きます。オフ：同じマップのプレイヤーにだけ届きます。住民やゲームのセリフは常にそのマップだけです</t>
+          <t>オフライン</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>What a player types in the chat is read by every player, wherever they are: on another map, on the world map, away on their own. Off: only the players on the same map as the speaker read it. Lines of townspeople and the game stay on their map either way</t>
+          <t>offline</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>emp_act_follow</t>
+          <t>emp_act_talk</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>ついていく</t>
+          <t>話す</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Follow</t>
+          <t>Talk</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>emp_follow_start</t>
+          <t>emp_whisper_with</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>#1についていく。何かキーを押すと止まる。</t>
+          <t>#1との内緒話</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>You follow #1. Press any key to stop.</t>
+          <t>Private chat with #1</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>emp_follow_stop</t>
+          <t>emp_whisper_offline</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>#1についていくのをやめた。</t>
+          <t>#1は接続していない。</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>You stop following #1.</t>
+          <t>#1 is not connected.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>emp_follow_left</t>
+          <t>emp_whisper_from</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>#1はこのマップを離れた。ついていくのをやめた。</t>
+          <t>#1（内緒話）</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>#1 left the map. You stop following.</t>
+          <t>#1 (private)</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>emp_follow_lost</t>
+          <t>emp_whisper_to</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>#1を見失った。</t>
+          <t>#1へ</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>You lost sight of #1.</t>
+          <t>To #1</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>emp_follow_danger</t>
+          <t>emp_whisper_you</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>危険だ。ついていくのをやめた。</t>
+          <t>あなた</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Danger! You stop following.</t>
+          <t>You</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_follow</t>
+          <t>emp_ui_sv_cfg_private_chat</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーについていける</t>
+          <t>プレイヤー同士で内緒話ができる</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Players can follow each other</t>
+          <t>Players can chat privately</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_follow</t>
+          <t>emp_ui_sv_desc_private_chat</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーをクリックして「ついていく」を選ぶと、同じマップの中で自動で後を歩きます。キー、攻撃、敵、相手のマップ移動で止まります。</t>
+          <t>他のプレイヤーのキャラに「話す」と、そのプレイヤーとの内緒話が開きます。どこにいてもそのプレイヤーにだけ届きます。</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Click another player and choose Follow: your character walks after it on the same map. A key, a blow, a monster in sight or the other player leaving the map stops it.</t>
+          <t>Talk on another player's character opens a private chat; only that player gets the lines, wherever they are.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>emp_people_players</t>
+          <t>emp_ui_sv_cfg_guest_moongate</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>プレイヤー</t>
+          <t>友人はムーンゲートで一人で移動する</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Players</t>
+          <t>Friends travel alone by moongate</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>emp_people_offline</t>
+          <t>emp_ui_sv_desc_guest_moongate</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>友人のムーンゲートは、ホストがダウンロードしたマップへその友人だけを運びます。ホストは動きません。</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>A friend's moongate takes that friend alone to a map the host downloaded; the host stays put.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>emp_act_talk</t>
+          <t>emp_ui_sv_cfg_guest_landing_portal</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>話す</t>
+          <t>友人は着陸ポータルで一人で移動する</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Friends travel alone by landing portal</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>emp_whisper_with</t>
+          <t>emp_ui_sv_desc_guest_landing_portal</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>#1との内緒話</t>
+          <t>友人の着陸ポータルは、その友人だけをゲートのある場所へ運びます。ホストは動きません。</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Private chat with #1</t>
+          <t>A friend's landing portal takes that friend alone to the gate zone; the host stays put.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>emp_whisper_offline</t>
+          <t>emp_ui_sv_cfg_guest_sky_helm</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>#1は接続していない。</t>
+          <t>友人も空の舵を使える</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>#1 is not connected.</t>
+          <t>Friends can steer the sky helm</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>emp_whisper_from</t>
+          <t>emp_ui_sv_desc_guest_sky_helm</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>#1（内緒話）</t>
+          <t>友人の空の舵は、ホストの行き先の一覧をその友人の画面に出し、その友人の空の切符で払います。ゲートの場所は全員で変わります。</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>#1 (private)</t>
+          <t>A friend's sky helm shows the host's destinations on their screen, paid with their sky tickets; the gate zone moves for everyone.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>emp_whisper_to</t>
+          <t>emp_ui_sv_cfg_shared_marriages</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>#1へ</t>
+          <t>全員が結婚できる</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>To #1</t>
+          <t>Every player can marry</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>emp_whisper_you</t>
+          <t>emp_ui_sv_desc_shared_marriages</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>あなた</t>
+          <t>住人は結婚したキャラクターの配偶者になり、先に求婚した者が優先されます。結婚式・離婚・指輪の再発行はその配偶者だけです。オフ：友人の結婚はその友人のゲームだけに残ります。</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>A resident becomes the spouse of the character who married them and the first to propose wins; wedding, divorce and lost-ring deeds work for that spouse only. Off: a friend's marriage stays in their own game.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_private_chat</t>
+          <t>emp_marriage_taken</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>内緒話</t>
+          <t>{0}はすでに結婚している。</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Private chat</t>
+          <t>{0} is already married.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_private_chat</t>
+          <t>emp_ui_sv_cfg_teams</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>他のプレイヤーのキャラに「話す」と、そのプレイヤーとの内緒話が開く。そのプレイヤーにだけ届く</t>
+          <t>チームを組める</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Talk on another player's character opens a private chat with that player. Only that player gets the lines, wherever they are</t>
+          <t>Players can be in teams</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_guest_moongate</t>
+          <t>emp_ui_sv_desc_teams</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>他プレイヤーのムーンゲート</t>
+          <t>誰がどのチームかはホストのセーブに残ります。チームのないプレイヤーは放浪者です。オフ：チームはありません。</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Moongate for other players</t>
+          <t>The host's save keeps who is in which team; a player in no team is a Wanderer. Off: no teams.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_guest_moongate</t>
+          <t>emp_ui_sv_cfg_team_bases</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>他のプレイヤーのムーンゲートは、ホストがダウンロードしたマップへそのプレイヤーだけを運ぶ。ホストは動かない</t>
+          <t>拠点はチームのもの</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Another player's moongate takes that player alone to a map the host downloaded; the host stays where it is</t>
+          <t>A base belongs to its team</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_guest_landing_portal</t>
+          <t>emp_ui_sv_desc_team_bases</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>他プレイヤーの着陸ポータル</t>
+          <t>拠点は権利書を読んだプレイヤーのチームのものです。ほかのチームは箱を開けられず、物を拾えず、建築も管理もできません。オフ：誰でもどの拠点も使えます。</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Landing portal for other players</t>
+          <t>A base belongs to the team of the player who claimed it; other teams cannot open its chests, take its things, build or manage there. Off: every player uses every base.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_guest_landing_portal</t>
+          <t>emp_team_belongs</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>他のプレイヤーの着陸ポータルは、そのプレイヤーだけをゲートのある場所へ運ぶ。ホストは動かない</t>
+          <t>これは{0}のものだ。</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Another player's landing portal takes that player alone to the gate zone; the host stays where it is</t>
+          <t>This belongs to {0}.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_guest_sky_helm</t>
+          <t>emp_team_wanderers</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>他プレイヤーの空の舵</t>
+          <t>放浪者</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Sky helm for other players</t>
+          <t>the Wanderers</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_guest_sky_helm</t>
+          <t>emp_ui_sv_cfg_team_approval</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>他のプレイヤーの空の舵は、ホストの行き先の一覧をそのプレイヤーの画面に出し、そのプレイヤーの空の切符で払う。ゲートの場所は全員で変わる</t>
+          <t>チームへの参加はリーダーが承認する</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Another player's sky helm shows the host's destinations on that player's screen and its sky tickets pay; the gate zone moves for everyone</t>
+          <t>Team leaders approve new members</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_shared_marriages</t>
+          <t>emp_ui_sv_desc_team_approval</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>共有結婚</t>
+          <t>チームに入りたいプレイヤーは、リーダーがプレイヤー一覧で承認か拒否をするまで待ちます。オフ：すぐに入れます。</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Shared marriages</t>
+          <t>A player asking to join a team waits until its leader accepts or refuses in the player list. Off: players join at once.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_marriages</t>
+          <t>emp_team_found</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>誰でも結婚できる：住人は結婚したキャラクターの配偶者になり、先に求婚した者が優先。結婚式・離婚・指輪の再発行はその配偶者だけ。オフ：以前どおりゲストの結婚はそのゲームだけ</t>
+          <t>チームを結成する</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Every player can marry: a resident is the spouse of the character who married it and the first to propose wins. The wedding, divorce and lost ring deeds work for that spouse only. Off: as before a guest's marriage stays in its own game</t>
+          <t>Found a team</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>emp_marriage_taken</t>
+          <t>emp_team_join</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>{0}はすでに結婚している。</t>
+          <t>{0}に入る</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>{0} is already married.</t>
+          <t>Join {0}</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_teams</t>
+          <t>emp_team_leave</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>チームを組める</t>
+          <t>{0}を抜ける</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Players can be in teams</t>
+          <t>Leave {0}</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_teams</t>
+          <t>emp_team_accept</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>プレイヤーはチームに入れる。誰がどのチームかはホストのセーブに残る。チームのないプレイヤーは放浪者。オフ：チームはなく、以前どおり</t>
+          <t>{0}を受け入れる</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Players can be in teams, the host keeps who is in which team in its save. A player in no team is a Wanderer. Off: no teams, everything as before</t>
+          <t>Accept {0}</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_team_bases</t>
+          <t>emp_team_refuse</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>拠点はチームのもの</t>
+          <t>{0}を断る</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>A base belongs to its team</t>
+          <t>Refuse {0}</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_team_bases</t>
+          <t>emp_team_now</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>拠点は権利書を読んだプレイヤーのチームのもの。ほかのチームのプレイヤーはそこで箱を開けられず、物を拾えず、建築も拠点の管理もできない。オフ：以前どおり誰でもどの拠点も使える</t>
+          <t>あなたは今{0}にいる。</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>A base belongs to the team of the player who claimed it: the players of another team cannot open its chests, pick up its things, build there or manage it. Off: every player uses every base as before</t>
+          <t>You are now with {0}.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>emp_team_belongs</t>
+          <t>emp_team_asks</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>これは{0}のものだ。</t>
+          <t>{0}が{1}に入りたがっている。</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>This belongs to {0}.</t>
+          <t>{0} asks to join {1}.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>emp_team_wanderers</t>
+          <t>emp_ui_sv_cfg_team_deed</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>放浪者</t>
+          <t>新しいチームは権利書を1枚もらう</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>the Wanderers</t>
+          <t>A new team gets a land deed</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_team_approval</t>
+          <t>emp_ui_sv_desc_team_deed</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>チームに入るにはリーダーの承認が必要</t>
+          <t>新しいチームを作ったプレイヤーは土地の権利書を1枚もらいます（チームごとに1回、プレイヤーごとに1回）。オフ：元のゲームと同じく商人から買います。</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Joining a team needs its leader's approval</t>
+          <t>The player who founds a team gets one land deed, once per team and once per player. Off: deeds are bought from the merchant, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_team_approval</t>
+          <t>emp_ui_sv_cfg_spawn_zone</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>チームに入りたいプレイヤーはリーダーを待つ。リーダーはプレイヤー一覧で承認か拒否を選ぶ。オフ：すぐに入れる</t>
+          <t>最初に現れる場所</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>A player who asks to join a team waits for its leader, who accepts or refuses in the list of players. Off: a player joins at once</t>
+          <t>Starting place</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>emp_team_found</t>
+          <t>emp_ui_sv_desc_spawn_zone</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>チームを結成する</t>
+          <t>始まりの草原：チームがあるとき、新しいプレイヤーと拠点のないチームのプレイヤーは、ゲームが始まる草原に参加します（一人旅が必要）。
+ホストのいるマップ：ホストのいるマップに参加します。</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Found a team</t>
+          <t>Starting meadow: with teams, new players and players whose team has no base join in the meadow where a game starts (needs travel alone).
+The host's map: they join on the host's map.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>emp_team_join</t>
+          <t>emp_ui_sv_opt_spawn_zone_start</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>{0}に入る</t>
+          <t>始まりの草原</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Join {0}</t>
+          <t>Starting meadow</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>emp_team_leave</t>
+          <t>emp_ui_sv_opt_spawn_zone_host</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>{0}を抜ける</t>
+          <t>ホストのいるマップ</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Leave {0}</t>
+          <t>The host's map</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>emp_team_accept</t>
+          <t>emp_team_deed_mail</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>{0}を受け入れる</t>
+          <t>{0}のチームの権利書</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Accept {0}</t>
+          <t>{0}'s team deed</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>emp_team_refuse</t>
+          <t>emp_ui_sv_cfg_team_personal</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>{0}を断る</t>
+          <t>チームの土地に置いた物は本人のもの</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Refuse {0}</t>
+          <t>Players own what they place on team land</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>emp_team_now</t>
+          <t>emp_ui_sv_desc_team_personal</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>あなたは今{0}にいる。</t>
+          <t>チームの土地にプレイヤーが置いた箱・扉・ベッドはそのプレイヤーのものです。仲間は箱の中を見られますが取れず、扉は通れません。メニューの「チームと共有」でチームのものに戻ります。オフ：チームの土地の物はチーム全員のものです。</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>You are now with {0}.</t>
+          <t>A chest, door or bed a player places on team land is theirs: teammates can look in the chest but not take, and cannot pass the door; "Share with team" gives it back. Off: all of it is the team's.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>emp_team_asks</t>
+          <t>emp_team_share</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>{0}が{1}に入りたがっている。</t>
+          <t>チームと共有</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>{0} asks to join {1}.</t>
+          <t>Share with team</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_team_deed</t>
+          <t>emp_ui_sv_cfg_team_pvp</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>新しいチームに権利書を1枚</t>
+          <t>チーム同士で戦う</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>A land deed for a new team</t>
+          <t>Teams fight each other</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_team_deed</t>
+          <t>emp_ui_sv_desc_team_pvp</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>新しいチームを作ったプレイヤーは土地の権利書を1枚もらう。チームごとに1回、プレイヤーごとに1回。オフ：権利書はゲームどおり商人から買う</t>
+          <t>異なるチームのプレイヤーは、町とスポーン地点の外では敵同士です（放浪者は誰とも戦わず、本当に死ぬのは「本当に倒す」がオンのときだけ）。オフ：異なるチームは戦えません。</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>The player who founds a new team receives one land deed, once per team and once per player. Off: a deed is bought from the merchant as in the game</t>
+          <t>Players of different teams are enemies outside towns and the spawn zone (Wanderers fight nobody; real deaths need real kills on). Off: teams cannot fight.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_spawn_zone</t>
+          <t>emp_ui_sv_cfg_public_game</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>新しいプレイヤーが現れる場所</t>
+          <t>誰でもゲームを見つけて参加できる</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Where a new player appears</t>
+          <t>Anyone can find and join the game</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_spawn_zone</t>
+          <t>emp_ui_sv_desc_public_game</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>チームがあるとき、新しいプレイヤーと拠点のないチームのプレイヤーは参加するとここへ向かう（一人旅が必要）</t>
+          <t>ゲーム一覧で見つけた人は誰でも参加できます。自動で開いたゲーム（デポ、共有ワールド）はそのワールドのプレイヤーだけです。オフ：ホストのSteamフレンドと招待されたプレイヤーのみ。</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>With teams, a new player and a player whose team has no base go there when they join (needs travelling alone)</t>
+          <t>Anyone who finds the game in the list can join; a game opened by itself (depot, shared world) still admits only its world's players. Off: the host's Steam friends and invited players only.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_spawn_zone_start</t>
+          <t>emp_ui_sv_cfg_look_mods_own</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>始まりの草原</t>
+          <t>見た目だけのMODは各自のまま</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>The meadow where a game starts</t>
+          <t>Each player keeps their look-only mods</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>emp_ui_sv_opt_spawn_zone_host</t>
+          <t>emp_ui_sv_desc_look_mods_own</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>ホストのいるマップ</t>
+          <t>見た目だけを変えるMOD（画像、肖像、音、翻訳。コード、アイテム、マップなし）は友人に求められず、そのために再起動する人はいません。オフ：友人はホストのすべてのMODが必要です。</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>The host's map</t>
+          <t>Mods that only change the look (pictures, portraits, sounds, translations; no code, items or maps) are not asked of friends, so nobody restarts for them. Off: friends need every mod of the host.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>emp_team_deed_mail</t>
+          <t>emp_team_beaten</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>{0}のチームの権利書</t>
+          <t>{0}は{1}に敗れた。</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>{0}'s team deed</t>
+          <t>{0} was beaten by {1}.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_team_personal</t>
+          <t>emp_ui_sv_cfg_characters</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>チームの中でも自分の物を持てる</t>
+          <t>友人のキャラクター</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Personal ownership inside a team</t>
+          <t>Friends' characters</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_team_personal</t>
+          <t>emp_ui_sv_desc_characters</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>チームの土地にプレイヤーが置いた箱・扉・ベッドはそのプレイヤーのもの。仲間は箱を開けて中を見られるが取れず、扉は通れない。メニューの「チームと共有」でチームのものに戻る。オフ：チームの土地の物はチーム全員のもの</t>
+          <t>新しいキャラ：友人は参加するたびに新しくキャラを作ります。
+自分のキャラを選ぶ：この世界の自分のキャラを選ぶか、新しく作ります。
+選ぶか連れてくる：自分のセーブからキャラ（装備、バッグ、お金、名声、カルマ）を連れてくることもできます。セーブは変更されません。</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>A chest, door or bed a player installs on its team's land is that player's: teammates open the chest and see inside but cannot take, and cannot pass the door. "Share with team" in its menu gives it back to the team. Off: what is on a team's land is the whole team's</t>
+          <t>New character: friends make a new character each time they join.
+Pick one of yours: friends pick one of their characters in this world, or make a new one.
+Pick or bring one: friends can also bring a character from their own saves (gear, bag, gold, fame, karma); the save is never changed.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>emp_team_share</t>
+          <t>emp_ui_sv_opt_characters_new</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>チームと共有</t>
+          <t>新しいキャラ</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Share with team</t>
+          <t>New character</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_team_pvp</t>
+          <t>emp_ui_sv_opt_characters_pick</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>チーム間のPvP</t>
+          <t>自分のキャラを選ぶ</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>PvP between teams</t>
+          <t>Pick one of yours</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_team_pvp</t>
+          <t>emp_ui_sv_opt_characters_both</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>異なるチームのプレイヤーは、町とスポーン地点の外では互いに敵になる。放浪者は誰とも戦わない。プレイヤーが本当に死ぬのは「プレイヤー同士で倒せる」がオンのときだけ。オフ：異なるチームのプレイヤーは戦えない</t>
+          <t>選ぶか連れてくる</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Players of different teams are enemies to each other outside towns and the spawn zone. Wanderers fight nobody. A player only really dies if players can kill each other. Off: players of different teams cannot fight</t>
+          <t>Pick or bring one</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_public_game</t>
+          <t>emp_ui_sv_cfg_travel</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>公開ゲーム</t>
+          <t>旅</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Public game</t>
+          <t>Travel</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_public_game</t>
+          <t>emp_ui_sv_desc_travel</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>ゲーム一覧で見つけた人は誰でも参加できる（ホストのSteamフレンドや招待されたプレイヤーだけでなく）。自動で開いたゲーム（保管庫、共有ワールド）はそのワールドのプレイヤーだけ。オフ：フレンドと招待されたプレイヤーのみ</t>
+          <t>一緒に：全員がホストについていきます。
+一人で、共有時計：好きな場所へ行けます。ワールドマップで誰かが一歩進むたびに、全員の日付が進みます。
+一人で、自分のペース：好きな場所へ行けます。一人で旅するプレイヤーは世界より先に進み、その時間は本人の満腹度とクエストが払います。</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Anybody who finds the game in the list of games can join, not only the host's Steam friends and invited players. A game opened by itself (depot, shared world) still lets in only its world's players. Off: friends and invited players only</t>
+          <t>Together: everyone follows the host.
+Alone, shared clock: players go anywhere; every step on the world map moves the date for everyone.
+Alone, own pace: players go anywhere; a player travelling alone runs ahead of the world, paying the hours with their own hunger and quests.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_look_mods_own</t>
+          <t>emp_ui_sv_opt_travel_together</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>見た目だけのModは各自のもの</t>
+          <t>一緒に</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Look-only mods: each player's own</t>
+          <t>Together</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_look_mods_own</t>
+          <t>emp_ui_sv_opt_travel_alone</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>見た目だけを変えるMod（画像、肖像、音、翻訳：コード、アイテム、マップなし）は参加者に求められない：そのために再起動する人はおらず、各プレイヤーは自分のものを使い続ける。オフ：参加者はホストのすべてのModが必要</t>
+          <t>一人で、共有時計</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Mods that only change the look (pictures, portraits, sounds, translations: no code, no items, no maps) are not asked of the players who join: nobody restarts for them, and every player keeps their own. Off: the players who join need every mod of the host</t>
+          <t>Alone, shared clock</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>emp_team_beaten</t>
+          <t>emp_ui_sv_opt_travel_own_pace</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>{0}は{1}に敗れた。</t>
+          <t>一人で、自分のペース</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>{0} was beaten by {1}.</t>
+          <t>Alone, own pace</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_characters</t>
+          <t>emp_ui_sv_sec_friends</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>参加するキャラクター</t>
+          <t>友人はホストと同じことができる</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Characters of joining friends</t>
+          <t>Friends can do what the host does</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_characters</t>
+          <t>emp_player_someone</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>新しいキャラ：毎回新しく作ります。自分のキャラを選ぶ：この世界の自分のキャラを選ぶか、新しく作ります。選ぶか連れてくる：自分のセーブからキャラ（装備、バッグ、お金、名声とカルマ）を連れてくることもできます。</t>
+          <t>プレイヤー</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
-        <is>
-          <t>New character: a new one each time. Pick one of yours: one of their characters in this world, or a new one. Pick or bring one: also a character from their own saves (gear, bag, gold, fame and karma; the save is never changed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_opt_characters_new</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>新しいキャラ</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>New character</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_opt_characters_pick</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>自分のキャラを選ぶ</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>Pick one of yours</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_opt_characters_both</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>選ぶか連れてくる</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>Pick or bring one</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_cfg_travel</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>旅</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_travel</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>一緒に：全員がホストについていきます。一人で、共有時計：好きな場所へ行けて、ワールドマップで誰かが一歩進むたびに日付が進みます。一人で、自分のペース：同じですが、一人で旅するプレイヤーは世界より先に進み、その時間は本人の満腹度とクエストが払います。</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Together: everyone follows the host. Alone, shared clock: players go anywhere; every step of anyone on the world map moves the date. Alone, own pace: the same, but a player travelling alone runs ahead of the world: its hunger and its own quests pay the hours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_opt_travel_together</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>一緒に</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Together</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_opt_travel_alone</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>一人で、共有時計</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Alone, shared clock</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_opt_travel_own_pace</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>一人で、自分のペース</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Alone, own pace</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_sec_friends</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>友人はホストと同じことができる</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Friends can do what the host does</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>emp_player_someone</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>プレイヤー</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
         <is>
           <t>A player</t>
         </is>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D477"/>
+  <dimension ref="A1:D493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは、全員が同時に眠っているときだけです。オフ：全員が揃うまで待ちます。</t>
+          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは「夜が明ける条件」のとおりです。オフ：全員が揃うまで待ちます。</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>A player in bed sleeps at once; the night passes only when everyone sleeps at the same time. Off: everyone waits for everyone.</t>
+          <t>A player in bed sleeps at once; the night passes as "Night passes when" says. Off: everyone waits for everyone.</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>他人のキャラクターへの変更を拒否する</t>
+          <t>他人の物への行為を拒否する</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Refuse changes to others' characters</t>
+          <t>Refuse acts on what others own</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>自分のキャラでも仲間でもないキャラについてプレイヤーのゲームが送る情報（行動、ダメージ、スキル、パーティ）を拒否します。取引、贈り物、自分の仲間への命令は拒否されません。オフ：ログに書くだけです。</t>
+          <t>他人のキャラクターやアイテムへのプレイヤーの行為と、大量のデータ送信を拒否します。公開ゲームでは常にオンです。オフ：ログに書くだけです。</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>What a player's game sends about a character neither theirs nor their companion (task, damage, skills, party) is refused; trades, gifts and orders to own companions never are. Off: it is only logged.</t>
+          <t>A player's acts on others' characters or items and floods of data are refused; always on in a public game. Off: only logged.</t>
         </is>
       </c>
     </row>
@@ -8596,6 +8596,288 @@
         </is>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_night_passes</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>夜が明ける条件</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Night passes when</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_night_passes</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>全員が眠る：オンラインで操作中のプレイヤー全員が眠ると夜が明けます（従来どおり）。
+半数が眠る：そのうち半数以上が眠ると夜が明けます。他の人は起きたままです。
+一人が眠る：そのうち一人が眠るとすぐに夜が明けます。</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Everyone sleeps: the night passes when all online, active players sleep, as before.
+Half the players sleep: it passes when at least half of them sleep; the others stay awake.
+One player sleeps: it passes as soon as one of them sleeps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_night_passes_Everyone</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>全員が眠る</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Everyone sleeps</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_night_passes_Half</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>半数が眠る</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Half the players sleep</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_night_passes_One</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>一人が眠る</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>One player sleeps</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_idle_minutes</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>離席とみなす時間</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Away after</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_idle_minutes</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>オフ：操作のないプレイヤーも従来どおり夜とワールドマップを待たせます。
+5分：キーボード・マウス・自分の行動が5分ないプレイヤーは、夜もワールドマップも日付も待たせません。
+15分：15分後に同じです。
+30分：30分後に同じです。</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Off: a player without input still holds the night and the world map, as before.
+5 min: a player without keyboard, mouse or own act for 5 min no longer holds the night, the world map or the date.
+15 min: the same after 15 min.
+30 min: the same after 30 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_idle_minutes_0</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>オフ</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_idle_minutes_5</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_idle_minutes_15</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_idle_minutes_30</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>emp_ui_player_idle</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>（離席中）</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>(idle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>emp_ui_host_closed</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>ホストがゲームを閉じました。セッションは終了しました。</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>The host closed its game. The session has ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>emp_ui_host_left_waiting</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>ホストがゲームを離れました。戻るのを待っています…</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>The host left the game. Waiting for it to come back…</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_time_stops_empty</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>誰も遊んでいない間は時間が止まる</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Time stops when nobody plays</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_time_stops_empty</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>接続中で操作しているプレイヤーがいない間、世界の日付は止まります。ホストも離席中なら数えません。オフ：従来どおり時間が進みます。</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>With no player connected and active (the host counts unless away), the date of the world stands still. Off: time goes on as before.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D493"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8878,6 +8878,182 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>emp_dc_host_kick_why</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>切断: ホストによりキックされました（{0}）</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Disconnected: kicked by the host ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>emp_dc_banned</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>このワールドから追放されています。</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>You are banned from this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>emp_dc_banned_why</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>このワールドから追放されています：{0}</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>You are banned from this world: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>emp_dc_kick_wait_why</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>このワールドからキックされました。{0}分後にもう一度試してください。</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>You were kicked from this world. Try again in {0} min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_kick_keep_out</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>キック後の待ち時間</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Kicked players wait</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_kick_keep_out</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>オフ：キックされたプレイヤーはすぐに戻れる。
+5分：キックされたプレイヤーは5分間戻れない。
+15分：15分間。
+60分：60分間。</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Off: a kicked player can come back at once.
+5 min: a kicked player cannot come back for 5 min.
+15 min: the same for 15 min.
+60 min: the same for 60 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_kick_keep_out_0</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>オフ</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_kick_keep_out_5</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_kick_keep_out_15</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_kick_keep_out_60</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>60分</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9054,6 +9054,23 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>emp_ui_muted</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>このワールドでは発言できません（管理者によりミュートされています）。</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>You cannot chat in this world (muted by an admin).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D504"/>
+  <dimension ref="A1:D511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9071,6 +9071,125 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>emp_ui_mute</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>ミュート</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Mute</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>emp_ui_unmute</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>ミュート解除</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Unmute</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>emp_ui_ban</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>追放</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Ban</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>emp_ui_unban</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>追放解除</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Unban</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>emp_ui_make_admin</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>管理者にする</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Make admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>emp_ui_admin_tag</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>（管理者）</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>(admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>emp_ui_banned_title</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>追放中のプレイヤー</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Banned players</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D511"/>
+  <dimension ref="A1:D514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9190,6 +9190,57 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>emp_dc_members_only</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>このワールドには、すでにここでプレイしたプレイヤーだけが参加できます。</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Only the players of this world can join it now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_members_only</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>メンバーのみ</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Members only</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_members_only</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>ここにキャラクターがいるプレイヤー、管理者、許可したプレイヤーだけが参加できる。Steamのフレンドや公開ゲームの知らない人も断られる。オフ：今まで通り。</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Only players with a character here, admins and players let in can join; Steam friends and strangers of a public game are refused. Off: as before.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D514"/>
+  <dimension ref="A1:D517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9241,6 +9241,57 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>emp_permadeath_wait</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>あなたのキャラクターは、仲間がバーテンダーで蘇生してくれるのを待っています。別のキャラクターで遊ぶには、メニューからゲームを抜けてください。</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Your character waits for a friend to revive it at a bartender. To play another character, leave the game from the menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_permadeath_revive</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>バーテンダーで蘇生（パーマデス）</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Revive at the bartender (permadeath)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_permadeath_revive</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>パーマデスのワールドのみ：死んだプレイヤーのキャラクターはワールドに残り、誰でもバーテンダーで料金を払って蘇生できる。何も削除されない。オフ：ゲーム本来のパーマデス（ホストが死ぬとワールドが削除される）。</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Permadeath worlds only: a dead player's character stays in the world and anyone can revive it at a bartender for the game's price; nothing is deleted. Off: the game's own permadeath (the host's death deletes the world).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D517"/>
+  <dimension ref="A1:D519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9292,6 +9292,40 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_dead_tag</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>（死亡：バーテンダーでの蘇生待ち）</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>(dead: waiting for a revive at a bartender)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_dead</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>このキャラクターは死んでいて、バーテンダーでの蘇生を待っています。</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>This character is dead and waits for a revive at a bartender.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D519"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9326,6 +9326,23 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>emp_act_duel_giveup</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>決闘を降参する</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Give up the duel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9343,6 +9343,110 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>emp_ui_report_send</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>開発者にバグを報告する</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Report a bug to the developers</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>emp_ui_report_send_desc</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>何が起きたかを書くと、ログと一緒に開発者へ送られ、GitHubに公開の報告が作られます。ログ（Steamの名前とIDを含む）は開発者だけが読めます。</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Write what happened: it goes to the developers with your logs, as a public report on GitHub. The logs (they hold Steam names and ids) are only readable by the developers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>emp_ui_report_what</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>何が起きましたか？（何をしていたか、何を期待したか）</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>What happened? (what you were doing, what you expected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>emp_ui_report_sending</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>報告を送信中…</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Sending the report…</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>emp_ui_report_page</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>報告ページをブラウザで開きました。デスクトップのzipをドラッグしてSubmitしてください。</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>The report page opened in your browser: drag the zip from your desktop into it and click Submit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>emp_ui_report_sent</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>報告を送信しました：{0}
+ブラウザで開きますか？</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Report sent: {0}
+Open it in your browser?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -9368,12 +9368,12 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>何が起きたかを書くと、ログと一緒に開発者へ送られ、GitHubに公開の報告が作られます。ログ（Steamの名前とIDを含む）は開発者だけが読めます。</t>
+          <t>何が起きたかを書くと、ログと一緒に開発者へ送られ、GitHubに公開の報告が作られます（あなたのSteamの名前が表示されます）。ログ（SteamのIDを含む）は開発者だけが読めます。</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Write what happened: it goes to the developers with your logs, as a public report on GitHub. The logs (they hold Steam names and ids) are only readable by the developers.</t>
+          <t>Write what happened: it goes to the developers with your logs, as a public report on GitHub that shows your Steam name. The logs (they hold Steam ids) are only readable by the developers.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D526"/>
+  <dimension ref="A1:D530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9447,6 +9447,74 @@
         </is>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>emp_ui_lobby_official</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>★ Elin Together 公式サーバー</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>★ Official Elin Together server</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>emp_ui_lobby_official_join</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>公式サーバーに参加</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Join the official server</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>emp_ui_lobby_public</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>誰でも参加できます</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Anyone can join</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>emp_ui_lobby_friends</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>ホストのフレンドと招待されたプレイヤーのみ</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Host's friends and invited players only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D530"/>
+  <dimension ref="A1:D544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9515,6 +9515,244 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_title</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>プレイヤーのキャラクター</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Players' characters</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_desc</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>プレイヤーがこの世界で作ったキャラクター。戻ってこないプレイヤーのキャラクターは削除できます（持ち物ごと、元に戻せません）。</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>The characters players made in this world. A character of a player who will not come back can be deleted (with what it carries, it cannot be undone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_line</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>{0}：{1}（Lv {2}）</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>{0}: {1} (Lv {2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_playing</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>プレイ中（削除するには先にキックしてください）</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Playing now (kick the player first to delete it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_delete</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>削除</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_confirm</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>{1} のキャラクター {0} を持ち物ごと削除しますか？元に戻せません。</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Delete {0}, the character of {1}, with what it carries? This cannot be undone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_max_characters</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>プレイヤーごとのキャラクター数</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Characters per player</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_max_characters</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>1人のプレイヤーがこの世界で持てるキャラクターの数。上限に達すると、1人削除するまで新しく作ったり持ち込んだりできません。すでにいるキャラクターはそのまま残ります。</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>How many characters one player may have in this world. At the limit, a player cannot make or bring another until it deletes one. Characters already made are kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_max_characters_1</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_max_characters_3</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_max_characters_5</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_max_characters_10</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_max_characters_0</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>無制限</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_limit</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>この世界でのキャラクター数の上限に達しています。新しく作るには、1人削除してください。</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>You have as many characters as this world allows: delete one to make or bring another.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -9385,12 +9385,12 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>何が起きましたか？（何をしていたか、何を期待したか）</t>
+          <t>何が起きましたか？（何をしていたか、何を期待したか）　Enter：改行、Ctrl+Enter：送信、Esc：キャンセル</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>What happened? (what you were doing, what you expected)</t>
+          <t>What happened? (what you were doing, what you expected)   Enter: new line, Ctrl+Enter: send, Esc: cancel</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D544"/>
+  <dimension ref="A1:D545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9368,12 +9368,12 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>何が起きたかを書くと、ログと一緒に開発者へ送られ、GitHubに公開の報告が作られます（あなたのSteamの名前が表示されます）。ログ（SteamのIDを含む）は開発者だけが読めます。</t>
+          <t>何が起きたかを書くと、ログと最後の30秒の画面と一緒に開発者へ送られ、GitHubに公開の報告が作られます（あなたのSteamの名前が表示されます）。ログと画面（SteamのIDを含む）は開発者だけが見られます。</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Write what happened: it goes to the developers with your logs, as a public report on GitHub that shows your Steam name. The logs (they hold Steam ids) are only readable by the developers.</t>
+          <t>Write what happened: it goes to the developers with your logs and the last 30 seconds of your screen, as a public report on GitHub that shows your Steam name. The logs and pictures (they hold Steam ids) are only seen by the developers.</t>
         </is>
       </c>
     </row>
@@ -9750,6 +9750,23 @@
       <c r="D544" t="inlineStr">
         <is>
           <t>You have as many characters as this world allows: delete one to make or bring another.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_record_replay</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>バグ報告に最後の30秒の画面を付ける</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Send the last 30 seconds of the screen with a bug report</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -9368,12 +9368,12 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>何が起きたかを書くと、ログと最後の30秒の画面と一緒に開発者へ送られ、GitHubに公開の報告が作られます（あなたのSteamの名前が表示されます）。ログと画面（SteamのIDを含む）は開発者だけが見られます。</t>
+          <t>何が起きたかを書くと、ログと最後の30秒の画面と一緒に、GitHubの公開の報告になります。誰でも見られます（Steamの名前とIDを含む）。</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Write what happened: it goes to the developers with your logs and the last 30 seconds of your screen, as a public report on GitHub that shows your Steam name. The logs and pictures (they hold Steam ids) are only seen by the developers.</t>
+          <t>Write what happened: it becomes a public report on GitHub with your logs and the last 30 seconds of your screen. Anyone can see it (it shows your Steam name and id).</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9770,6 +9770,57 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>emp_ui_official_players</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>現在 {0} 人がプレイ中</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>{0} players online</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>emp_ui_official_closed</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>公式サーバーは今は開いていません</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>The official server is not open right now</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_import_official</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>公式サーバーではキャラクターの持ち込みはできません</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>The official server does not take imported characters</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -8869,12 +8869,12 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>接続中で操作しているプレイヤーがいない間、世界の日付は止まります。ホストも離席中なら数えません。オフ：従来どおり時間が進みます。</t>
+          <t>接続中で操作しているプレイヤーがいない間、世界の日付は止まります。ホストも離席中なら数えません。一人で自分のマップにいるプレイヤーが離席している間は、そのマップの時間も止まります。オフ：従来どおり時間が進みます。</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>With no player connected and active (the host counts unless away), the date of the world stands still. Off: time goes on as before.</t>
+          <t>With no player connected and active (the host counts unless away), the date of the world stands still; so does the map of a player alone there and away. Off: time goes on as before.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9770,6 +9770,40 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_absent_quests_wait</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>不在の間はクエストが待つ</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Quests wait for absent players</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_absent_quests_wait</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>ゲームを離れたプレイヤーのクエストは残り時間を保ちます。戻ったとき、留守中に世界で過ぎた日数が期限に加わります。オフ：世界の時間とともに期限が過ぎます。</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>A player who left the game finds its quests with the time they had left: the days the world went on without it are added to their deadlines. Off: they run out as the world goes on.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9770,6 +9770,40 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_knowledge</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>チームごとに学ぶ</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Teams learn on their own</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_knowledge</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>各チームが自分のレシピ、作ったものの記録、図鑑を持ちます。プレイヤーが覚えたことはチームの仲間も覚え、ほかのチームは覚えません。物語の報酬のレシピは全チームに届き、セーブには全チームの知識が残ります。オフ：全員で一つのレシピと図鑑を共有します（これまで通り）。</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Each team has its own recipes, list of things crafted and codex: what a player learns, its teammates learn too, the other teams do not. Recipes the story gives reach every team, and the save keeps what every team knows. Off: one book of recipes and one codex for everyone, as before.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D547"/>
+  <dimension ref="A1:D552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9804,6 +9804,97 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_catch_up_days</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>追いつきで過ごす日数</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Catch-up lives</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_catch_up_days</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>世界の日付に大きく遅れたゲーム（誰かの長旅、誰もいなかったマップ）が追いつくとき、最後の何日を1フレーム1日ずつ過ごすか。それより前の時間は、その日々なしに飛ばされます。
+1日：最も軽い。
+3日：中間。
+7日：従来どおり。</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>When a game far behind the world's date catches up (someone's long trip, a map nobody played), how many of the last days it lives, a day per frame. The time before them is skipped over without its days.
+1 day: the lightest.
+3 days: in between.
+7 days: as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_catch_up_days_1</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>1日</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_catch_up_days_3</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_catch_up_days_7</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>7日</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>7 days</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9770,6 +9770,40 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_guest_bouts</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>ゲストも冒険者と決闘できる</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Guests duel adventurers too</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_guest_bouts</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>ゲストは冒険者とホストと同じように決闘します。冒険者は決闘の間町を離れ、終わると回復して戻ります。次の決闘までの一週間は全員共通で、勝てば記録され、報酬は冒険者自身の物です。オフ：ゲストは自分のゲームの中で冒険者の写しと戦い、世界には何も残りません。</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>A guest duels an adventurer as the host does: the adventurer leaves town for the bout and comes back healed, the week before its next bout is the same for everyone, a win counts and the reward is the adventurer's own. Off: the guest fights a copy in its own game and nothing of it stays in the world.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D547"/>
+  <dimension ref="A1:D552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9804,6 +9804,91 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_duel_arena</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>ホストとの決闘は闘技場で</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Duels with the host in an arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_duel_arena</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>ホストとの決闘が受けられると、ホストが野原の闘技場を作って向かい、相手も後を追います。決闘が終わると、それぞれ元いた場所に戻ります。ほかの二人のプレイヤーの決闘はその場で行われます。</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>When a duel with the host is accepted, the host makes a field for it and goes there, the other player follows; after the duel each one comes back to the tile it left. A duel between two other players is fought where they stand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>emp_duel_arena_go</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>{0} と {1} は闘技場へ向かいます。</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>{0} and {1} head for the arena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>emp_duel_arena_host</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>闘技場はホストの決闘だけです。この決闘はその場で行います。</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>The arena is for the host's duels only: this one is fought here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>emp_duel_arena_late</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>相手が闘技場に来ませんでした。決闘は中止です。</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>The other duellist never reached the arena: the duel is called off.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D552"/>
+  <dimension ref="A1:D564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9889,6 +9889,210 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_duel_bets</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>決闘に賭ける</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Bets on duels</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_duel_bets</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>決闘を申し込む側が金貨の賭け金（なし、100、1,000、または二人のうち少ない方の所持金すべて）を決め、相手は答えるときにそれを見ます。両者が賭け金を出し、勝者が全部受け取ります。勝者なしで終わったとき（離れた、接続が切れた、ゲームが止まった）は各自に返されます。降参すると失います。</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>The challenger of a duel names a stake in gold (none, 100, 1,000 or all the poorer of the two has), shown in the box the other one answers; both put it down and the winner takes both. When the duel ends without a winner (a player leaves or drops out, the game stops) each one gets its stake back; giving up loses it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>emp_duel_stake</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>賭け金</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Stake</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>emp_duel_stake_none</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>賭けない</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>No stake</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>emp_duel_stake_gold</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>金貨 {0} 枚</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>{0} gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>emp_duel_stake_all</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>相手と出せるだけ全部</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>As much as both can put down</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>emp_duel_invite_bet</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>{0}が金貨 {1} 枚ずつを賭けて決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>{0} challenges you to a duel for a stake of {1} gold each. Nobody dies, but what you use up stays used. Accept?</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>emp_duel_asked_bet</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>{0} に金貨 {1} 枚ずつを賭けて決闘を申し込みました…</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>You challenge {0} to a duel for {1} gold each…</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>emp_duel_paid</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>賭け金として金貨 {0} 枚を出した。</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>You put down a stake of {0} gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>emp_duel_pot</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>賭け金の金貨 {0} 枚を手に入れた！</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>You take the stakes: {0} gold!</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>emp_duel_refund</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>賭け金が返された。</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Your stake is given back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>emp_duel_unpaid</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>賭け金がそろわず、決闘は中止です。</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>The stakes were not put down: the duel is called off.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9770,6 +9770,40 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_own_journal</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>日誌はプレイヤーごと</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Each player has their own journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_own_journal</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>メッセージの履歴と自分の記録（採掘・死亡・睡眠の回数）は旅をしても自分のものです。図鑑・討伐数・世界の日付は共通です。オフ：旅のあとはホストの日誌が見えます。</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Each player keeps its own message history and its own records (digging, deaths, nights slept) from trip to trip; the codex, kills and the world's dates stay shared. Off: after a trip, a player's journal shows the host's.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D576"/>
+  <dimension ref="A1:D581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10303,6 +10303,91 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_bills</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>チームごとに土地の税を払う</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Teams pay their own land</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_bills</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>土地を持つチームごとに毎月の税の請求書が届きます。自分の土地の分だけで、メンバーの最も高い名声で計算されます（どのチームのものでもない土地は放浪者の分）。未払いの請求書はチームごとに数え、4枚以上になるとそのチームのプレイヤーだけがカルマを失います。オフ：世界全体で請求書は一枚（これまで通り）。</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Each team that holds land gets its own monthly tax bill, for its own lands only, on its members' highest fame (lands of no team: the Wanderers' bill). Unpaid bills are counted per team: four or more cost karma to that team's players only. Off: one bill for the whole world, as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>emp_team_bill</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>{0}の税の請求書：{1}</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Tax bill of {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>emp_ui_teams_title</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>emp_ui_team_bills</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>未払いの税の請求書：{0}</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>unpaid tax bills: {0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D576"/>
+  <dimension ref="A1:D592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10303,6 +10303,278 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_export_chara</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>キャラをソロのセーブへ連れて行ける</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Friends can take a character to a solo save</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_export_chara</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>キャラの一覧から、自分のソロのセーブへキャラを連れて行きます。そのセーブを次に読み込むと、そのセーブのキャラと入れ替わります（先にセーブのコピーを作ります）。キャラはこの世界を離れ、セーブからの持ち込みで戻るか、そのまま呼び戻すまで遊べません。持ち込みがオンのときだけ。オフ：連れて行けません。</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>From the character list, friends take a character to one of their solo saves, where it replaces that save's character when it is next loaded (a copy of the save is made first). It leaves this world until it comes back by being brought from that save, or is brought back unchanged. Only with saved characters allowed. Off: they cannot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>キャラをソロのセーブへ連れて行く…</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Take a character to a solo save…</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_pick</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>どのキャラをソロのセーブへ連れて行きますか？</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Which character goes to a solo save?</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_save</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>どのセーブへ？そのセーブのキャラは入れ替わります。</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Into which save? Its own character will be replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_confirm</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>#1 はこの世界を離れ、#2 へ行きます。先にそのセーブのコピーを作ります。次にそのセーブを読み込むと、#1 がそのセーブのキャラと入れ替わり、元のキャラはコピーにだけ残ります。#1 は、そのセーブからの持ち込みで戻るまで、ここでは遊べません。よろしいですか？</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>#1 leaves this world for #2. A copy of that save is made first. When you next load it, #1 takes the place of its character, which then stays only in the copy. #1 cannot be played here until it is brought back from that save. Go?</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_exported</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>キャラはソロのセーブで待っています。タイトル画面からそのセーブを読み込んでください。</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>The character waits in your solo save: load that save from the title screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_fail</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>キャラをそのセーブへ連れて行けませんでした。この世界に残ります。</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>The character could not be taken to that save. It stays in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_stale</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>このキャラの旅は終わっています（呼び戻し済み、またはすでに戻っています）。もう一度は来られません。</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>This character's trip is over (brought back, or already returned): it cannot come in again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_away_tag</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>（ソロのセーブ中：#1）</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>(in a solo save: #1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_away</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>このキャラはソロのセーブにいます。</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>This character is in a solo save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_recall</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>そのまま呼び戻す…</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Bring back unchanged…</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_recall_confirm</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>#1 を出発したときのまま呼び戻しますか？ソロのセーブにいるキャラは、もうここへは戻れません。</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Bring #1 back as it left? The one in the solo save can then never come here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_recalled</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>キャラを出発したときのまま呼び戻しました。</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>The character is back as it left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_arrived</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>#1 が協力プレイの世界から来て、このセーブのキャラと入れ替わりました（前のセーブはバックアップにあります）。</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>#1 came from a co-op world and took the place of this save's character (the save as it was is in the backups).</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_export_load_fail</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>協力プレイの世界から来たキャラを、このセーブへ入れられませんでした。セーブはそのままです。キャラは ElinMP/Incoming で待っています。</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>A character from a co-op world could not be brought into this save. The save is as it was; the character waits in ElinMP/Incoming.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D581"/>
+  <dimension ref="A1:D592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10388,6 +10388,193 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_story</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>チームごとに物語の記録を残す</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Teams keep their own story journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_story</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>各チームが、メンバーの誰かが参加したメインクエストの最も先の章を覚え、チームの欄に表示します（進めたプレイヤーと同じマップにいたプレイヤーが参加したことになります）。物語そのものは世界のもののままです。オフ：チームごとの記録はありません。</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Each team remembers the furthest chapter of the main quest one of its players took part in (the player who made the step and the players on that map), shown on the Teams card. The story itself stays the world's. Off: no journal per team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>emp_ui_team_story</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>物語：{0}</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>story: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_none</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>まだなし</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_0</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>旅の始まり</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>the journey begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_100</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>アッシュと出会った</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>met Ash</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_200</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>権利書を読んだ</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>read the deed</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_250</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>アッシュに報告した</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>reported to Ash</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_300</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>ファリスと出会った</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>met Farris</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_600</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ナイメルの後</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>after Nymelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>emp_team_chapter_700</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>アッシュが家を去った</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Ash left home</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10881,6 +10881,108 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_own_story</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>チームごとの物語（実験的）</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Teams live their own story (experimental)</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_own_story</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>実験的。各チームが自分のメインストーリーを進める：アッシュのクエストとニメルの探索、物語の会話はチームごと。チェックした時点の物語の進み具合から全チームが始める。ファリスは最初のチームの拠点にだけ加わる。他のチームがすでに攻略した階に着いたチームは、そこから物語を進める。ワールドチーム（チェックした時のホストのチーム）の物語がセーブに残る：チェックを外す、またはMODなしでセーブを開くと、そのチームの物語で続く。チームが必要。</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Experimental. Each team lives its own main story: Ash's quest and the exploration of Nymelle, and their dialogs, are its own. Every team starts at the story point the world is at when the box is ticked. Farris joins the base of the first team only; a team reaching a floor another team already cleared takes the story on from there. The save keeps the story of the world team (the host's team when the box is ticked): unticked, or the save opened without the mod, the world goes on with that team's story. Needs Teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>emp_team_story_moved</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>日誌は今のチームの物語に従う。</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Your journal now follows your team's story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>emp_team_story_caught_up_farris</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>ファリスは他のチームとすでにここを去った。あなたのチームはそこから物語を進める。</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Farris already left here with another team: your team takes the story on from there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>emp_team_story_caught_up_boss</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>ニメルの守護者は他のチームがすでに倒した。あなたのチームはそこから物語を進める。</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Another team already defeated the guardian of Nymelle: your team takes the story on from there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>emp_team_story_caught_up_crystal</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>水晶のそばのフィアマの話は他のチームがすでに聞いた。あなたのチームはそこから物語を進める。</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Another team already heard Fiama by the crystal: your team takes the story on from there.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D616"/>
+  <dimension ref="A1:D617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10889,12 +10889,12 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>チームごとの物語（実験的）</t>
+          <t>プレイヤーとチームごとの物語（実験的）</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Teams live their own story (experimental)</t>
+          <t>Each player or team lives its own story (experimental)</t>
         </is>
       </c>
     </row>
@@ -10906,12 +10906,12 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>実験的。各チームが自分のメインストーリーを進める：アッシュのクエストとニメルの探索、物語の会話はチームごと。チェックした時点の物語の進み具合から全チームが始める。ファリスは最初のチームの拠点にだけ加わる。他のチームがすでに攻略した階に着いたチームは、そこから物語を進める。ワールドチーム（チェックした時のホストのチーム）の物語がセーブに残る：チェックを外す、またはMODなしでセーブを開くと、そのチームの物語で続く。チームが必要。</t>
+          <t>実験的。各プレイヤーが自分のペースでメインストーリーを進める（アッシュのクエスト、ニメルの探索とその会話）。チームの仲間は一緒：チームは一つの物語を共有し、チームのないプレイヤーは自分だけの物語を持つ。チェックした時点の物語の進み具合から全員が始める。ファリスは最初の拠点にだけ加わる。他の人がすでに攻略した階に着いたプレイヤーやチームは、そこから物語を進める。セーブにはホスト自身の物語が残る：チェックを外す、またはMODなしでセーブを開くと、その物語で続く。オフ：全員が一つの物語の進み具合を共有する（従来どおり）。</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Experimental. Each team lives its own main story: Ash's quest and the exploration of Nymelle, and their dialogs, are its own. Every team starts at the story point the world is at when the box is ticked. Farris joins the base of the first team only; a team reaching a floor another team already cleared takes the story on from there. The save keeps the story of the world team (the host's team when the box is ticked): unticked, or the save opened without the mod, the world goes on with that team's story. Needs Teams.</t>
+          <t>Experimental. Each player lives the main story at its own pace (Ash's quest, the exploration of Nymelle and their dialogs), teammates together: a team shares one story, a player without a team has its own. Everyone starts at the story point the world is at when the box is ticked. Farris joins the first base only; a player or team reaching a floor someone already cleared takes the story on from there. The save keeps the host's own story: unticked, or the save opened without the mod, the world goes on with it. Off: all players share one story progression, as before.</t>
         </is>
       </c>
     </row>
@@ -10923,12 +10923,12 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>日誌は今のチームの物語に従う。</t>
+          <t>日誌は今の物語に従う：チームの物語、またはチームがなければ自分の物語。</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Your journal now follows your team's story.</t>
+          <t>Your journal now follows your story: your team's, or your own without a team.</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>ファリスは他のチームとすでにここを去った。あなたのチームはそこから物語を進める。</t>
+          <t>ファリスは他の人とすでにここを去った。あなたの物語はそこから進む。</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Farris already left here with another team: your team takes the story on from there.</t>
+          <t>Farris already left here with someone else: your story goes on from there.</t>
         </is>
       </c>
     </row>
@@ -10957,12 +10957,12 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>ニメルの守護者は他のチームがすでに倒した。あなたのチームはそこから物語を進める。</t>
+          <t>ニメルの守護者は他の人がすでに倒した。あなたの物語はそこから進む。</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Another team already defeated the guardian of Nymelle: your team takes the story on from there.</t>
+          <t>Someone else already defeated the guardian of Nymelle: your story goes on from there.</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,29 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>水晶のそばのフィアマの話は他のチームがすでに聞いた。あなたのチームはそこから物語を進める。</t>
+          <t>水晶のそばのフィアマの話は他の人がすでに聞いた。あなたの物語はそこから進む。</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Another team already heard Fiama by the crystal: your team takes the story on from there.</t>
+          <t>Someone else already heard Fiama by the crystal: your story goes on from there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_own_story_official</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>公式サーバーでは常にオン：プレイヤーとチームごとの物語。</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Always on for the official public server: a story for each player and team.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -9954,12 +9954,12 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>チームごとに学ぶ</t>
+          <t>プレイヤーとチームごとに学ぶ</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Teams learn on their own</t>
+          <t>Each player or team learns on its own</t>
         </is>
       </c>
     </row>
@@ -9971,12 +9971,12 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>各チームが自分のレシピ、作ったものの記録、図鑑を持ちます。プレイヤーが覚えたことはチームの仲間も覚え、ほかのチームは覚えません。物語の報酬のレシピは全チームに届き、セーブには全チームの知識が残ります。オフ：全員で一つのレシピと図鑑を共有します（これまで通り）。</t>
+          <t>各プレイヤーが自分のレシピ、作ったものの記録、図鑑を持つ。チームの仲間は一つを共有し、チームのないプレイヤーは自分だけのものを持つ。物語の報酬のレシピは全員に配られ、セーブには全員の知識が残る。オフ：全員が一つのレシピと図鑑を共有する（従来どおり）。</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Each team has its own recipes, list of things crafted and codex: what a player learns, its teammates learn too, the other teams do not. Recipes the story gives reach every team, and the save keeps what every team knows. Off: one book of recipes and one codex for everyone, as before.</t>
+          <t>Each player has its own recipes, crafted list and codex; teammates share one, a player without a team has its own. Recipes given by the story reach everyone, and the save keeps everything anyone learnt. Off: everyone shares one book of recipes and one codex, as before.</t>
         </is>
       </c>
     </row>
@@ -10991,12 +10991,12 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>公式サーバーでは常にオン：プレイヤーとチームごとの物語。</t>
+          <t>公式サーバーでは常にオン：プレイヤーとチームごと。</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Always on for the official public server: a story for each player and team.</t>
+          <t>Always on for the official public server: one for each player and team.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11000,6 +11000,133 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_living_world</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>生きている世界（現実の時間）</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Living world (real-time clock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_living_world</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>オフ：従来どおり、日付はプレイヤーのターンとともに進みます。
+20分：世界の時計が現実の時間に従い、現実の20分で1日が過ぎます。プレイヤーが動いていても立ち止まっていても同じです。誰も遊んでいない間は止まり（「誰も遊んでいない間は時間が止まる」）、夜のルールが許す睡眠は朝まで続きます。各プレイヤーの行動は今までどおり自分のターンで進みます。
+40分：同じく、現実の40分で1日。
+60分：同じく、現実の1時間で1日。
+120分：同じく、現実の2時間で1日。</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Off: the date moves with the players' turns, as before.
+20 min: the clock of the world follows real time, a day every 20 real minutes, whether the players act or stand still. It stops while nobody plays ("Time stops when nobody plays"), and a night slept as the night rule allows runs to the morning. Each player's own acts still go by its own turns.
+40 min: the same, a day every 40 real minutes.
+60 min: the same, a day every real hour.
+120 min: the same, a day every 2 real hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_living_world_0</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>オフ</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_living_world_20</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>1日 = 20分</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>A day = 20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_living_world_40</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>1日 = 40分</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>A day = 40 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_living_world_60</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>1日 = 1時間</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>A day = 1 hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_living_world_120</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>1日 = 2時間</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>A day = 2 hours</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11000,6 +11000,23 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>emp_travel_stranger_map</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>ここは別のプレイヤーがプレイ中です。公開サーバーでは同じチームの仲間だけがマップを共有できます</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Another player is playing this map. On a public server, only teammates share a map.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>友人は拠点を変更できません（研究、炉の技能、方針、名前、設定、住人、建築）。オフ：全員ができます。拠点を完全に手放せるのはホストだけです。</t>
+          <t>友人は拠点を変更できません（研究、盟約の石の技能、方針、名前、設定、住人、建築）。オフ：全員ができます。拠点を完全に手放せるのはホストだけです。</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>店の仕入れはマップ上で最も良いプレイヤーの特性で決まり、特別な棚（結婚とカセットの店、ロイテルのマート、異国の商人）は店を開いたプレイヤーの進行に従います。オフ：ホストの進行（元のゲームと同じ）。</t>
+          <t>店の仕入れはマップ上で最も良いプレイヤーの特性で決まり、特別な棚（結婚とカセットの店、ロイテルのマート、舶来品商人）は店を開いたプレイヤーの進行に従います。オフ：ホストの進行（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>友人は着陸ポータルで一人で移動する</t>
+          <t>友人は地上転移ポータルで一人で移動する</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>友人の着陸ポータルは、その友人だけをゲートのある場所へ運びます。ホストは動きません。</t>
+          <t>友人の地上転移ポータルは、その友人だけをゲートのある場所へ運びます。ホストは動きません。</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>友人も空の舵を使える</t>
+          <t>友人も飛空艇の舵を使える</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>友人の空の舵は、ホストの行き先の一覧をその友人の画面に出し、その友人の空の切符で払います。ゲートの場所は全員で変わります。</t>
+          <t>友人の飛空艇の舵は、ホストの行き先の一覧をその友人の画面に出し、その友人の旅空券で払います。ゲートの場所は全員で変わります。</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>決闘を申し込む側が金貨の賭け金（なし、100、1,000、または二人のうち少ない方の所持金すべて）を決め、相手は答えるときにそれを見ます。両者が賭け金を出し、勝者が全部受け取ります。勝者なしで終わったとき（離れた、接続が切れた、ゲームが止まった）は各自に返されます。降参すると失います。</t>
+          <t>決闘を申し込む側がオレンの賭け金（なし、100、1,000、または二人のうち少ない方の所持金すべて）を決め、相手は答えるときにそれを見ます。両者が賭け金を出し、勝者が全部受け取ります。勝者なしで終わったとき（離れた、接続が切れた、ゲームが止まった）は各自に返されます。降参すると失います。</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>金貨 {0} 枚</t>
+          <t>{0}オレン</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>{0}が金貨 {1} 枚ずつを賭けて決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
+          <t>{0}が{1}オレンずつを賭けて決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>{0} に金貨 {1} 枚ずつを賭けて決闘を申し込みました…</t>
+          <t>{0} に{1}オレンずつを賭けて決闘を申し込みました…</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>賭け金として金貨 {0} 枚を出した。</t>
+          <t>賭け金として{0}オレンを出した。</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>賭け金の金貨 {0} 枚を手に入れた！</t>
+          <t>賭け金の{0}オレンを手に入れた！</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>土地を持つチームごとに毎月の税の請求書が届きます。自分の土地の分だけで、メンバーの最も高い名声で計算されます（どのチームのものでもない土地は放浪者の分）。未払いの請求書はチームごとに数え、4枚以上になるとそのチームのプレイヤーだけがカルマを失います。オフ：世界全体で請求書は一枚（これまで通り）。</t>
+          <t>土地を持つチームごとに毎月の税金請求書が届きます。自分の土地の分だけで、メンバーの最も高い名声で計算されます（どのチームのものでもない土地は放浪者の分）。未払いの請求書はチームごとに数え、4枚以上になるとそのチームのプレイヤーだけがカルマを失います。オフ：世界全体で請求書は一枚（これまで通り）。</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>{0}の税の請求書：{1}</t>
+          <t>{0}の税金請求書：{1}</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>未払いの税の請求書：{0}</t>
+          <t>未払いの税金請求書：{0}</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>ナイメルの後</t>
+          <t>ナイミールの後</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>実験的。各プレイヤーが自分のペースでメインストーリーを進める（アッシュのクエスト、ニメルの探索とその会話）。チームの仲間は一緒：チームは一つの物語を共有し、チームのないプレイヤーは自分だけの物語を持つ。チェックした時点の物語の進み具合から全員が始める。ファリスは最初の拠点にだけ加わる。他の人がすでに攻略した階に着いたプレイヤーやチームは、そこから物語を進める。セーブにはホスト自身の物語が残る：チェックを外す、またはMODなしでセーブを開くと、その物語で続く。オフ：全員が一つの物語の進み具合を共有する（従来どおり）。</t>
+          <t>実験的。各プレイヤーが自分のペースでメインストーリーを進める（アッシュのクエスト、ナイミールの探索とその会話）。チームの仲間は一緒：チームは一つの物語を共有し、チームのないプレイヤーは自分だけの物語を持つ。チェックした時点の物語の進み具合から全員が始める。ファリスは最初の拠点にだけ加わる。他の人がすでに攻略した階に着いたプレイヤーやチームは、そこから物語を進める。セーブにはホスト自身の物語が残る：チェックを外す、またはMODなしでセーブを開くと、その物語で続く。オフ：全員が一つの物語の進み具合を共有する（従来どおり）。</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>ニメルの守護者は他の人がすでに倒した。あなたの物語はそこから進む。</t>
+          <t>ナイミールの守護者は他の人がすでに倒した。あなたの物語はそこから進む。</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>水晶のそばのフィアマの話は他の人がすでに聞いた。あなたの物語はそこから進む。</t>
+          <t>魔石のそばのフィアマの話は他の人がすでに聞いた。あなたの物語はそこから進む。</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D625"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11144,6 +11144,40 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_server_rests</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>無人のとき専用サーバーを休ませる</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Dedicated server rests when empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_server_rests</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>専用サーバー（-empserver）に誰も接続していない間、毎秒5フレームで動き、音を止めます。誰かが接続するとすぐに元の速さに戻ります。オフ：常にゲームの通常のフレームレートで動きます。</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>While nobody is connected, a dedicated server (-empserver) runs at 5 frames a second with its sound stopped, and goes back to full speed as soon as a player connects. Off: it always runs at the game's own frame rate.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -2390,7 +2390,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Gold: {0}</t>
+          <t>Orens: {0}</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>How much gold?</t>
+          <t>How many orens?</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Click another player to trade items and gold; both must confirm.</t>
+          <t>Click another player to trade items and orens; both must confirm.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Friends bring the character, gear, bag, gold, fame and karma from their own saves, never changing them; not companions, base, quests or bank. Off: they cannot.</t>
+          <t>Friends bring the character, gear, bag, orens, fame and karma from their own saves, never changing them; not companions, base, quests or bank. Off: they cannot.</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Friends use build mode in the base (floors, walls, furniture, mining, cutting) and pay the gold and materials. Off: only the host builds.</t>
+          <t>Friends use build mode in the base (floors, walls, furniture, mining, cutting) and pay the orens and materials. Off: only the host builds.</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Orens</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>{0} now offers {1} gold.</t>
+          <t>{0} now offers {1} orens.</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>{0}: {1} gold, {2}</t>
+          <t>{0}: {1} orens, {2}</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Everyone builds and manages: all players use build mode in the base and manage it (research, policies, names, residents); friends pay their own gold and materials.
+          <t>Everyone builds and manages: all players use build mode in the base and manage it (research, policies, names, residents); friends pay their own orens and materials.
 Everyone manages, only the host builds: all players manage the base; only the host uses build mode.
 Only the host: only the host builds and manages the base.</t>
         </is>
@@ -8418,7 +8418,7 @@
         <is>
           <t>New character: friends make a new character each time they join.
 Pick one of yours: friends pick one of their characters in this world, or make a new one.
-Pick or bring one: friends can also bring a character from their own saves (gear, bag, gold, fame, karma); the save is never changed.</t>
+Pick or bring one: friends can also bring a character from their own saves (gear, bag, orens, fame, karma); the save is never changed.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>The challenger of a duel names a stake in gold (none, 100, 1,000 or all the poorer of the two has), shown in the box the other one answers; both put it down and the winner takes both. When the duel ends without a winner (a player leaves or drops out, the game stops) each one gets its stake back; giving up loses it.</t>
+          <t>The challenger of a duel names a stake in orens (none, 100, 1,000 or all the poorer of the two has), shown in the box the other one answers; both put it down and the winner takes both. When the duel ends without a winner (a player leaves or drops out, the game stops) each one gets its stake back; giving up loses it.</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>{0} gold</t>
+          <t>{0} orens</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>{0} challenges you to a duel for a stake of {1} gold each. Nobody dies, but what you use up stays used. Accept?</t>
+          <t>{0} challenges you to a duel for a stake of {1} orens each. Nobody dies, but what you use up stays used. Accept?</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>You challenge {0} to a duel for {1} gold each…</t>
+          <t>You challenge {0} to a duel for {1} orens each…</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>You put down a stake of {0} gold.</t>
+          <t>You put down a stake of {0} orens.</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>You take the stakes: {0} gold!</t>
+          <t>You take the stakes: {0} orens!</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D625"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11144,6 +11144,40 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_affinity_per_player</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>好感度はプレイヤーごと</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Affinity per player</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_affinity_per_player</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>住人は各プレイヤーに別々の好感度を持つ。贈り物・会話・依頼は行ったプレイヤーにだけ数えられ、会話の選択肢は話しているプレイヤーの好感度に従う。オフ：住人ごとに一団で一つの好感度（従来通り）。</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Each resident has its own affinity with each player: gifts, talks and quests count for the player who made them, and the talk options (invite, marry, sleep beside) follow the one who talks. Off: one affinity per resident for the whole group, as before.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D625"/>
+  <dimension ref="A1:D626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11144,6 +11144,23 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>emp_team_story_caught_up_debt</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>ロイテルはすでに他の人の拠点にいる。あなたの物語にも彼への借金がある：請求書は彼に払う。</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Loytel already lives at someone else's base: your story owes him its own debt too, paid to him.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -10906,12 +10906,12 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>実験的。各プレイヤーが自分のペースでメインストーリーを進める（アッシュのクエスト、ニメルの探索とその会話）。チームの仲間は一緒：チームは一つの物語を共有し、チームのないプレイヤーは自分だけの物語を持つ。チェックした時点の物語の進み具合から全員が始める。ファリスは最初の拠点にだけ加わる。他の人がすでに攻略した階に着いたプレイヤーやチームは、そこから物語を進める。セーブにはホスト自身の物語が残る：チェックを外す、またはMODなしでセーブを開くと、その物語で続く。オフ：全員が一つの物語の進み具合を共有する（従来どおり）。</t>
+          <t>実験的。各プレイヤーが自分のペースで物語を進める（アッシュのクエスト、ニメルの探索、すべての会話の選択、キーアイテム、ロイテルへの借金と追加の税）。チームの仲間は一緒：チームは一つの物語を共有し、チームのないプレイヤーは自分だけの物語を持つ。チェックした時点の物語の進み具合から全員が始める。ファリスは最初の拠点にだけ加わる。他の人がすでに攻略した階に着いたプレイヤーやチームは、そこから物語を進める。セーブにはホスト自身の物語が残る：チェックを外す、またはMODなしでセーブを開くと、その物語で続く（キーアイテムは誰かが得た分すべて）。オフ：全員が一つの物語の進み具合を共有する（従来どおり）。</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Experimental. Each player lives the main story at its own pace (Ash's quest, the exploration of Nymelle and their dialogs), teammates together: a team shares one story, a player without a team has its own. Everyone starts at the story point the world is at when the box is ticked. Farris joins the first base only; a player or team reaching a floor someone already cleared takes the story on from there. The save keeps the host's own story: unticked, or the save opened without the mod, the world goes on with it. Off: all players share one story progression, as before.</t>
+          <t>Experimental. Each player lives the story at its own pace (Ash's quest, the exploration of Nymelle, every dialog choice, the key items, Loytel's debt and the extra tax), teammates together: a team shares one story, a player without a team has its own. Everyone starts at the story point the world is at when the box is ticked. Farris joins the first base only; a player or team reaching a floor someone already cleared takes the story on from there. The save keeps the host's own story: unticked, or the save opened without the mod, the world goes on with it (the key items: all that anyone got). Off: all players share one story progression, as before.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D626"/>
+  <dimension ref="A1:D628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11161,6 +11161,40 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_own_guilds</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>ギルドもプレイヤーとチームごと</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Guilds per player or team too</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_own_guilds</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>「プレイヤーとチームごとの物語」と一緒に：各プレイヤーやチームが戦士、魔術師、盗賊、商人のギルドでも自分の立場を持つ（加入、ランク、貢献、ギルドのクエスト）。チェックした時点の世界のギルドから全員が始める。公式公開サーバーでもオフ。チェックを外す、またはMODなしでセーブを開くと：ホスト自身の物語のギルド。オフ：グループで一つの加入（従来どおり）。</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>With "Each player or team lives its own story": each player or team also has its own place in the Fighters', Mages', Thieves' and Merchants' guilds (membership, rank, contribution, guild quests). Everyone starts with the guilds the world has when the box is ticked. Off on the official public server too. Unticked, or the save opened without the mod: the guilds of the host's own story. Off: one membership for the group, as before.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D632"/>
+  <dimension ref="A1:D634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11263,6 +11263,40 @@
         </is>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_boxes</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>チームごとの銀行と配達ボックス</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Teams keep their own bank and delivery box</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_boxes</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>各チーム（チームのいないプレイヤーは単独）が自分の銀行と配達ボックスを持ちます。古い箱の中身は全員で共有のままです。チームが有効な場合のみ。オフにすると、各チームの箱は共有の箱に戻されます。</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Each team (a player without a team: alone) has its own bank and delivery box. What the old shared boxes hold stays shared, and everyone can still take from them. Needs Teams. Unticked, every team's box is merged back into the shared one.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11297,6 +11297,57 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>emp_parcel_for</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>{0}宛て</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>for {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>emp_mailbox_owner</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>郵便受けの持ち主: {0}</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Mailbox owner: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>emp_mailbox_everyone</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>みんな</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11297,6 +11297,278 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_team</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>emp_tab_team</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>emp_ui_team_title</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>emp_ui_team_none</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>あなたはチームに入っていません（放浪者です）。</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>You are not in a team (you are a Wanderer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>emp_ui_team_name_ask</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>新しいチームの名前</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Name of the new team</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>emp_ui_team_mine</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>あなたのチーム：{0}</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Your team: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>emp_ui_team_leader</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>リーダー：{0}（{1}）</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Leader: {0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>emp_ui_team_open</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>誰でも参加可</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>anyone joins</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>emp_ui_team_closed</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>リーダーが承認</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>the leader answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>emp_ui_team_online</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>オンライン</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>emp_ui_team_offline</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>オフライン</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>emp_ui_team_leader_tag</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>（リーダー）</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>(leader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>emp_ui_team_lands</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>土地</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>emp_ui_team_no_land</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>まだ土地がありません。</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>No land yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>emp_ui_team_others</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>他のチーム</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Other teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>emp_ui_team_line</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>{0}  リーダー {1}  {2}人  {3}</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>{0}  led by {1}  {2} members  {3}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11297,6 +11297,431 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_info</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>サーバー情報</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>emp_info_notice</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>サーバーのルールは Elin Together メニューで読めます。</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Read the server rules in the Elin Together menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>emp_info_motd</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>今日のお知らせ</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Message of the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>emp_info_rules</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>サーバーのルール</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Server rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>emp_info_none</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>ホストはまだ何も書いていません。</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>The host has not written anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>emp_info_edit_motd</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>お知らせを書く</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Write the message of the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>emp_info_edit_rules</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>ルールを書く</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Write the rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>emp_info_reload</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>ファイルを再読込して全員に送る</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Reload the files and send to everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>emp_info_files</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>ホストの ElinMP フォルダの motd.txt と rules.txt を直接編集しても構いません。入力欄では | が改行になります。</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>You can also edit motd.txt and rules.txt in the host's ElinMP folder. In the input box, a | is a line break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>emp_info_announce</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>全員へのお知らせ</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Announcements</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>emp_info_say</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>全員にお知らせを送る</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Tell everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>emp_info_restart_10</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>再起動の予告（10分前）</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Warn of a restart (10 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>emp_info_restart_cancel_button</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>予告を取り消す</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Cancel the warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>emp_info_restart</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>サーバーは{0}分後に再起動します。</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>The server restarts in {0} min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>emp_info_restart_cancel</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>サーバーの再起動は取り消されました。</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>The restart is cancelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>emp_info_friends</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>フレンド</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>emp_info_friend_online</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>{0}（オンライン）  {1}</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>{0} (online)  {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>emp_info_friend_offline</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>{0}（オフライン）</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>{0} (offline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>emp_info_friends_none</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>フレンドはいません。プレイヤー一覧のメニューから追加できます。</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>No friends yet. Add one from a player's menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>emp_info_ignored</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>無視リスト</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Ignored players</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>emp_info_ignored_note</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>このゲームだけで、相手の発言とささやきが非表示になります。相手には知らされません。</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Their chat and whispers are hidden in your game only. They are told nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>emp_ui_ignore</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>無視する</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>emp_ui_unignore</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>無視をやめる</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Stop ignoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>emp_ui_friend</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>フレンドに追加</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Add friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>emp_ui_unfriend</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>フレンドから外す</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Remove friend</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D650"/>
+  <dimension ref="A1:D685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11569,6 +11569,615 @@
         </is>
       </c>
     </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_leaders</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>チームのリーダーが自分のチームを管理する</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Team leaders manage their team</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_leaders</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>リーダーはチームページで名前変更、メンバーの追放、リーダーの委譲、解散、プレイヤーの招待ができます。チームの人数とチーム作成の間隔にも上限があります。オフ：プレイヤー一覧の作成・参加・脱退とリーダーの承認のみ。</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>The leader can rename the team, put a member out, hand the team over, end it and invite players from the Team page. A team's size and how often a player founds a team are limited. Off: only found, join, leave and the leader's yes or no from the list of players.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_max_size</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>チームの最大人数</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Players per team</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_max_size</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>5人：チームは5人まで。
+10人：10人まで。
+20人：20人まで。
+50人：50人まで。
+制限なし：人数の上限なし。</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>5: a team holds up to 5 players.
+10: up to 10.
+20: up to 20.
+50: up to 50.
+No limit: any number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_max_size_5</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_max_size_10</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>10人</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_max_size_20</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>20人</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_max_size_50</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>50人</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_max_size_0</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>制限なし</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_found_cooldown</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>チーム再作成までの待ち時間</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Wait before founding another team</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_found_cooldown</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>なし：すぐに別のチームを作れます。
+5分：5分待ちます。
+30分：30分待ちます。
+60分：60分待ちます。</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>None: a player may found another team at once.
+5 minutes: it waits 5 minutes.
+30 minutes: 30.
+60 minutes: 60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_found_cooldown_0</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_found_cooldown_5</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>5 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_found_cooldown_30</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>30 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_team_found_cooldown_60</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>60分</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>60 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>emp_ui_team_manage</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>リーダーの操作</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Leader's choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rename</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>チーム名を変更</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Rename the team</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rename_ask</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>チームの新しい名前</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>New name of the team</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>emp_ui_team_promote</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>リーダーにする</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Make leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>emp_ui_team_kick</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>チームから外す</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Put out of the team</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>{0}を招待</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Invite {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invited_line</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>{0}を招待済み（返事待ち）</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>{0} is invited (waiting for an answer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>emp_ui_team_disband</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>チームを解散</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Disband the team</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>emp_ui_team_disband_confirm</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>{0}を解散しますか？メンバーは放浪者に戻り、土地は誰のものでもなくなります。</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Disband {0}? Its members become Wanderers and its lands nobody's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite_title</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Invitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite_line</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>{0}（リーダー：{1}）があなたを招待しています。</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>{0} (leader: {1}) invites you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite_accept</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>招待を受ける</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite_refuse</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>断る</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Refuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>emp_team_kicked</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>あなたは{0}から外されました。</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>You were put out of {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>emp_team_promoted</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>あなたが{0}のリーダーになりました。</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>You now lead {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>emp_team_disbanded</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>{0}は解散しました。</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>{0} was disbanded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>emp_team_invited</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>{1}が{0}に招待しています。チームページで答えてください。</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>{1} invites you to {0}. Answer on the Team page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>emp_team_invite_refused</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>{0}は招待を断りました。</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>{0} refused your invitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>emp_team_full</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>{0}はいっぱいです。</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>{0} is full.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>emp_team_found_wait</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>別のチームを作るにはあと{0}分待ってください。</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Wait {0} more minutes before founding another team.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D685"/>
+  <dimension ref="A1:D694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12178,6 +12178,159 @@
         </is>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_land_rules</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>土地ごとのルール</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Rules for each land</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_land_rules</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>チームのリーダーは土地ごとに、自分のチームとそれ以外の人が何をできるか（立入禁止、見学、見学と使用、建築）を決めます。「拠点をチームが所有」が必要です。オフ：土地は従来どおり、チームは建築でき、他の人は見学のみ。</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>A team's leader sets, for each of its lands, what its own team and everyone else may do there: closed, visit, visit and use, or build. Needs "Team ownership of bases". Off: a land is as before, its team builds and others visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_0</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>立入禁止</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_1</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>見学</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_2</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>見学と使用</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Visit and use</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_3</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>建築</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_mine</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>この土地で：自分のチーム</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>On this land: my team</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_others</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>この土地で：それ以外の人</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>On this land: everyone else</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>emp_ui_team_land_line</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>{0}：チーム＝{1}、他の人＝{2}</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>{0}: team = {1}, others = {2}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11297,6 +11297,312 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>emp_container_log</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>アクセスログ</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Access log</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>emp_container_logs_title</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>コンテナのアクセスログ</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Container access logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>emp_container_log_empty</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>(まだ記録なし)</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>(nothing recorded yet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>emp_container_log_put</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>{0}  {1} が {3} を {2} 個入れた</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>{0}  {1} put {2} x {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>emp_container_log_took</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>{0}  {1} が {3} を {2} 個取った</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>{0}  {1} took {2} x {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>emp_ui_container_logs</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>コンテナのアクセスログ</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Container logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>emp_ui_freeze</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>凍結</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>emp_ui_unfreeze</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>凍結解除</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Unfreeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>emp_ui_jail</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>投獄</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Jail</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>emp_ui_set_jail</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ここを牢屋にする</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Use this zone as the jail</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>emp_ui_make_mod</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>モデレーターにする</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Make moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>emp_ui_unmake_mod</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>モデレーター解除</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Remove moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>emp_ui_mod_tag</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>[モデレーター]</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>[moderator]</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>emp_ui_frozen_tag</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>[凍結中]</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>[frozen]</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_container_log</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>コンテナのアクセスログ</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Container access log</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_container_log</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>プレイヤーやチームの土地にあるコンテナ(銀行と宅配ボックスも)ごとに、誰がいつ何を入れた・取ったかを直近50件ホストが記録します。土地のチームと管理者がコンテナの右クリックメニューから読めます。オフ:記録も表示もしません。</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>The host records, per container of a player's or team's land (and the bank and delivery boxes), who put or took what and when (last 50 entries). The land's team and the admins read it from the container's right-click menu. Off: nothing is recorded or shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_admin_extras</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>モデレーター・凍結・投獄</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Moderators, freeze and jail</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_admin_extras</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>ホストが任命するモデレーターはミュートとキックだけ可能。管理者は凍結(解除まで行動不能)と投獄(指定マップへ送って凍結)ができます。ホストと他の管理者は対象外。オフ:これらの命令は拒否されます。</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Moderators the host appoints can only mute and kick. Admins can freeze (no action until released) and jail (sent to the chosen map and frozen). Never the host or another admin. Off: these orders are refused.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D694"/>
+  <dimension ref="A1:D696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12331,6 +12331,40 @@
         </is>
       </c>
     </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>emp_land_closed</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>この土地はあなたに閉ざされています。</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>This land is closed to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>emp_land_leave_notice</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>{0}はあなたに閉ざされています。{1}秒後に外へ移動します。</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>{0} is closed to you. You will be moved out in {1} seconds.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D696"/>
+  <dimension ref="A1:D698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12365,6 +12365,40 @@
         </is>
       </c>
     </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_offline</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>チームの誰もオンラインでない間は他の人に閉ざす</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Closed to others while no member of the team is online</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>emp_ui_team_rule_offline_tag</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>（留守中は閉鎖）</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>(closed while away)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D698"/>
+  <dimension ref="A1:D716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12399,6 +12399,330 @@
         </is>
       </c>
     </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_land_abandon</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>放置された土地を手放す</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Abandoned land</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_land_abandon</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>チームの誰も現実の日数のあいだゲームに入らなかった場合、そのチームは土地の所有権を失い、土地は誰のものでもなく全員に開放されます。オフ：チームは長く留守にしても土地を保持します。</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>A team none of whose members came into the game for the days set below loses its claim on its lands: they become nobody's and open to everyone. Off: a team keeps its lands however long it is away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_abandon_days</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>土地を手放すまでの日数</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Days away before the land is lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_abandon_days</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>7日：チームが1週間来なかった場合。
+14日：2週間。
+30日：30日間。
+60日：60日間。
+90日：90日間。</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>7 days: the team was away a week.
+14 days: two weeks.
+30 days: thirty days.
+60 days: sixty days.
+90 days: ninety days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_abandon_days_7</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>7日</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>7 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_abandon_days_14</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>14日</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>14 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_abandon_days_30</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>30日</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_abandon_days_60</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>60日</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>60 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_abandon_days_90</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>90 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_lands_per_team</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>チームあたりの土地の上限</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Lands per team</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_lands_per_team</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>1：チームは土地を1つまで。
+2：2つまで。
+3：3つまで。
+5：5つまで。
+10：10まで。
+制限なし：上限なし。</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>1: a team claims one land.
+2: two.
+3: three.
+5: five.
+10: ten.
+No limit: any number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_lands_per_team_1</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>1つ</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_lands_per_team_2</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>2つ</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_lands_per_team_3</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>3つ</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_lands_per_team_5</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>5つ</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_lands_per_team_10</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_lands_per_team_0</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>制限なし</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>emp_team_land_cap</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>あなたのチームはすでに{0}つの土地を持っています。これ以上は主張できません。</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Your team already holds {0} lands. It cannot claim more.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D762"/>
+  <dimension ref="A1:D765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13505,6 +13505,57 @@
         </is>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_sibling_lands</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>複数の土地を1マスに</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Several lands per tile</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_sibling_lands</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>世界地図の1マスに、別々のチームの土地を複数置けます。すでに土地があるマスで土地証書を読むと、同じマスに別の区画ができます。複数の土地があるマスに入ると、入る土地を選ぶ一覧が出ます。「拠点をチームが所有」が必要です。オフ：1マスにつき土地は1つ。</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Lands of different teams may share one world-map tile. A deed read on a tile that already holds a land makes another plot there, and stepping onto a tile with several lands lists them to pick one. Needs "Team ownership of bases". Off: one land per tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>emp_sibling_ask</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>この場所にはすでに土地があります。同じマスに別の区画を作りますか？その区画に入り、もう一度証書を読んで主張します。</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>This tile already holds a land. Make another plot on it? You step into the plot and read the deed again to claim it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D765"/>
+  <dimension ref="A1:D766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13556,6 +13556,23 @@
         </is>
       </c>
     </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>emp_sibling_pick</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>どの土地に入りますか</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Which land to enter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D680"/>
+  <dimension ref="A1:D682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12079,6 +12079,40 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_server_avatar</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>サーバーは誰も操作しない</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Server plays no character</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_server_avatar</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>専用サーバー(-empserver)は誰も操作しません。セーブの持ち主のキャラクターは、そのSteam IDに結びついた通常のプレイヤーキャラになり(他の参加者と同じく参加します)、サーバー自身は隠れた無敵の代役を使います。オフ:持ち主のキャラクターは今までどおり拠点に置かれます。メニューから開始したゲームには影響しません。</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>A dedicated server (-empserver) plays no character: the save owner's character becomes an ordinary player character tied to its Steam id (it joins like any guest), and the server's own player is a hidden, untouchable stand-in. Off: the owner's character stays planted at the base as before. Has no effect on a game hosted from the menu.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D768"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13607,6 +13607,193 @@
         </is>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_hidden_server</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>隠しサーバーのゲストとして遊ぶ（ベータ）</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Play as a guest of a hidden server (beta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_hidden_server</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>「サーバー開始」でワールドをこのPC上の隠れた2つ目のElinで動かし、自分のゲームは他のプレイヤーと同じように参加します。ホストキャラクターがなくなり、体験が友達と同じになります。空きメモリが約2GB必要です。2分以内に起動しない場合は従来どおりホストします。Windowsのみ。</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>"Start Server" runs your world in a second, hidden Elin on this PC and your own game joins it like any other player: no host character, you live what your friends live. Needs about 2 GB of free memory; if the hidden game is not up in 2 minutes, the world is hosted as before. Windows only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>emp_hidden_starting</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>ワールドを起動しています...</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Starting your world...</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>emp_hidden_fallback</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>隠しサーバーは使えませんでした（{0}）。ワールドは従来の方法で開放します。</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>The hidden server could not be used ({0}): your world is hosted the usual way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>emp_hidden_why_save</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>ここではゲームを保存できません</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>the game cannot save here</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>emp_hidden_why_mutex</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>ゲームが多重起動の制限を解除できませんでした</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>the game could not lift its one-instance lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>emp_hidden_why_launch</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>隠しゲームを起動できませんでした</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>the hidden game could not be started</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>emp_hidden_why_exit</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>隠しゲームが途中で終了しました</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>the hidden game stopped on its own</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>emp_hidden_why_timeout</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>2分以内に起動しませんでした</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>it was not up in 2 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>emp_hidden_why_cancel</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>起動を中止しました</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>starting was cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>emp_travel_hidden_owner</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>隠しサーバーで遊んでいる間は、一人で別のマップを管理できません。仲間と一緒に移動してください。</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>While you play on a hidden server you cannot hold a map on your own: travel with the others.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13794,6 +13794,23 @@
         </is>
       </c>
     </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>emp_dc_owner_seat</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>この席は隠しサーバーの所有者専用です。</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>This seat belongs to the owner of this hidden server.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -13811,6 +13810,23 @@
         </is>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>emp_ui_team_bank</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>チームの銀行：{0}</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Team bank: {0} gold</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -13827,6 +13828,91 @@
         </is>
       </c>
     </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>emp_box_own_bank</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>個人の銀行</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Personal bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>emp_box_team_bank</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>チームの銀行: {0}</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Team bank: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>emp_box_world_bank</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>共有の銀行(旧ワールド)</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Shared bank (old world)</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>emp_box_own_delivery</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>個人の配達ボックス</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Personal delivery box</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>emp_box_world_delivery</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>共有の配達ボックス(旧ワールド)</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Shared delivery box (old world)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13913,6 +13913,125 @@
         </is>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>LayerElinTogether</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>マルチプレイ</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Multiplayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_session</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>接続中のゲームと参加者</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>The game you are in and who is playing</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_team</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>チームの所属と権限</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Teams: who is in which, and what a leader may do</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_server</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>ホストのワールドルール</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>The world rules set by the host</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_info</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>サーバーの案内とルール</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Server message and rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_lobby</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>ゲームの作成・参加</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Host a game or find one to join</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_client</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>自分用の設定</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Your own settings</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13913,6 +13913,23 @@
         </is>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>emp_ui_set_by_host</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>ホストが設定</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Set by the host</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6962,12 +6962,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>その他の設定は Elin Together のウィンドウ（「ワールドのルール」タブ）にあります。</t>
+          <t>さらに{0}件を表示</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>More options in the Elin Together window (World rules tab).</t>
+          <t>Show {0} more</t>
         </is>
       </c>
     </row>
@@ -13913,6 +13913,244 @@
         </is>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_banner_host</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>あなたが決めます</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>You decide</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_banner_guest</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>{0}が設定</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Set by {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_search</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>ルールを検索</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Search the rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_nomatch</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>一致するルールはありません。</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>No rule matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_preset_current</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>現在</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_diff_title</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>おすすめとの違い（{0}件）</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Differs from Recommended ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_diff_all</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>すべて表示（{0}）</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Show all {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_fewer</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>表示を減らす</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Show fewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_revert</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>元に戻す</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Revert</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_needs</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>「{0}」が必要です</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Needs: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_needs_off</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>「{0}」をオフにする必要があります</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Needs this off: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_needs_notofficial</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>公式サーバーでは使えません</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Not available on the official server</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_needs_other</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>他のルールがオンである必要があります</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Needs another rule to be on</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_changed_many</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>ホストが{0}件のルールを変更しました：{1}</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>The host changed {0} rules: {1}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -680,12 +680,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>サーバー</t>
+          <t>ワールドのルール</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>World rules</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>クライアント設定</t>
+          <t>自分の設定</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Client settings</t>
+          <t>My settings</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>クライアント</t>
+          <t>自分の設定</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>My settings</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>The host has not written anything.</t>
+          <t>The host hasn't written anything yet.</t>
         </is>
       </c>
     </row>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>ホストの ElinMP フォルダの motd.txt と rules.txt を直接編集しても構いません。入力欄では | が改行になります。</t>
+          <t>ホストの ElinMP フォルダの motd.txt と rules.txt を直接編集しても構いません。</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>You can also edit motd.txt and rules.txt in the host's ElinMP folder. In the input box, a | is a line break.</t>
+          <t>You can also edit motd.txt and rules.txt in the host's ElinMP folder.</t>
         </is>
       </c>
     </row>
@@ -13972,12 +13972,12 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>ホストのワールドルール</t>
+          <t>ホストが決めたワールドのルール（ゲストは閲覧のみ）</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>The world rules set by the host</t>
+          <t>The world's rules set by the host (guests read them)</t>
         </is>
       </c>
     </row>
@@ -14023,12 +14023,12 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>自分用の設定</t>
+          <t>自分だけの設定、フレンド、無視リスト</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Your own settings</t>
+          <t>Your own options, friends and ignored players</t>
         </is>
       </c>
     </row>
@@ -14284,6 +14284,499 @@
       <c r="D808" t="inlineStr">
         <is>
           <t>The host changed {0} rules: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>emp_tab_info</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>サーバー</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_help</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>ヘルプ</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>emp_tab_help</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>ヘルプ</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_help</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>使い方、バージョン、バグ報告</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>How it works, version and bug report</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>emp_info_none_host</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>まだ何も書いていません。参加者全員に表示されます。</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Nothing written yet. Every player can read it here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>emp_info_write</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>書く</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Write one</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>emp_info_edit</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>鉛筆で編集</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Edit (pencil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>emp_info_save</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>保存して全員に送る</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Save and send to everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>emp_info_cancel</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>emp_hub_change</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>変更</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>emp_hub_online</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>オンライン: {0}</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Online: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>emp_hub_offline</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>オフライン</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>emp_help_hosting_t</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>ゲームを開く</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Hosting a game</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>emp_help_hosting</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>「プレイ」ページで「このゲームをホストする」を押すと、今のセーブが友達に公開されます。ルールは「ワールドのルール」で決めます。</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>On the Play page, press Host this game: your current save opens to friends. You decide the rules on the World rules page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>emp_help_joining_t</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>友達のゲームに参加する</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Joining a friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>emp_help_joining</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>「プレイ」ページで友達か公開サーバーを選ぶだけです。あなたのキャラクターはそのワールドに保存されます。</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Pick a friend or a public server on the Play page. Your character is kept in that world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>emp_help_teams_t</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>emp_help_teams</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>チームは一緒に行動し、土地や所持品を分け合います。リーダーが仲間を招待・追放できます。ホストが有効にした場合のみ使えます。</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>A team travels together and shares lands. Its leader can invite and remove members. Available when the host turns teams on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>emp_help_lands_t</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>土地</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>emp_help_lands</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>土地は、入れる人と触れる人が決まっています。チームの銀行と配達箱は、チーム全員で使えます。</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Each land says who may enter and who may touch things. The team bank and delivery box are shared by the whole team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>emp_help_trading_t</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>取引</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>emp_help_trading</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>プレイヤー一覧のメニューから「取引」を選ぶと、相手と品物やお金を交換できます。</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Choose Trade in a player's menu to swap items and money with them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>emp_help_duels_t</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>決闘</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Duels</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>emp_help_duels</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>プレイヤーのメニューから決闘を申し込めます。相手が受けた時だけ始まります。</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Challenge a player from their menu. It starts only if they accept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>emp_help_about</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>このMODについて</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>emp_help_version</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Elin Together（独立版）{0}</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Elin Together (independence) {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>emp_help_about_desc</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>最新版、不具合の報告、ソースコードはGitHubにあります。</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>The latest version, bug reports and the source are on GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>emp_help_github</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>GitHubを開く</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Open GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>emp_help_report</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>不具合を報告する</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Report a bug</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14287,6 +14287,482 @@
         </is>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_play</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>プレイ</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_players</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>プレイヤー</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_play</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>ゲームを開く・参加・退出</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Host, join or leave a game</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_players</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>参加中のプレイヤーと操作</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Who is playing, and what you can do with them</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>emp_ui_play_connected</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>接続中</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Connected</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>emp_ui_play_reconnecting</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>再接続中...</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Reconnecting...</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>emp_ui_play_world</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>{0}のワールド</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>{0}'s world</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>emp_ui_play_host_line</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>ホスト: {0}</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Host: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>emp_ui_play_players_line</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>プレイヤー: {0}人</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Players: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>emp_ui_play_where</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>現在地: {0}</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Now in: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>emp_ui_play_host_title</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>このゲームをホストする</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Host this game</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>emp_ui_play_host_desc</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>このワールドを友達に開放します。友達はSteamか下の公開リストから参加できます。</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Open this world to your friends. They join from Steam or from the public list below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>emp_ui_play_host_title_screen</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>先にワールドを読み込み、このページで「サーバー開始」を押してください。</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Load your world first, then open this page and press Start server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>emp_ui_play_host_depot</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>共有ワールドはオンラインに保管されています。ワンクリックで引き継いでホストできます。</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>The shared world is kept online. Take it over and host it in one click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>emp_ui_play_join_title</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>友達に参加する</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Join a friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>emp_ui_play_join_desc</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Steamの招待を受けるか、アドレスでサーバーに参加します。</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Accept a Steam invite from a friend, or join a server by its address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>emp_ui_play_join_ingame</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>参加するにはタイトル画面に戻ってください。</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Go back to the title screen to join a game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>emp_ui_play_public_title</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>公開サーバー</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Public servers</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>emp_ui_play_searching</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>ゲームを探しています...</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Looking for games...</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>emp_ui_play_none</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>今は公開されているゲームがありません。</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>No public game right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>emp_ui_players_title</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>プレイヤー ({0})</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Players ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>emp_ui_player_detail</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>{0}、レベル{1}</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>{0}, level {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>emp_ui_player_host</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>ホスト</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>emp_ui_player_you</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>(あなた)</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>(you)</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>emp_ui_act_whisper</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>ささやく</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Whisper</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>emp_ui_players_alone</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>ここにはあなた一人です。</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>You're alone here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>emp_ui_players_alone_btn</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>友達を招待</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Invite a friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>emp_ui_players_go_play</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>ゲームを開く・参加する</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Host or join a game</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12628,12 +12628,12 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>リーダーの操作</t>
+          <t>リーダーツール</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Leader's choices</t>
+          <t>Leader tools</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Put out of the team</t>
+          <t>Remove from team</t>
         </is>
       </c>
     </row>
@@ -14287,6 +14287,533 @@
         </is>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_lands</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>土地</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>emp_tab_lands</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>土地</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_lands</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>チームの土地：ルール、留守中の保護、銀行と配達ボックス</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>The team's lands: rules, protection while away, bank and delivery box</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>emp_ui_team_chip_open</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>誰でも参加可</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>emp_ui_team_chip_closed</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>リーダーが承認</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Leader approves</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>emp_ui_team_leader_line</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>リーダー：{0}　メンバー{1}人</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Leader: {0}  ·  {1} members</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>emp_ui_team_detail</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Lv {0}、{1}</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Lv {0}, {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>emp_ui_team_crown</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>リーダー</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>emp_ui_team_off</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>このワールドではチームは無効です。</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Teams are off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>emp_ui_team_off_guest</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>このワールドではチームは無効です。ホストだけがオンにできます。</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Teams are off in this world. Only the host can turn them on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>emp_ui_team_unplugged</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>チームはマルチプレイの中で使えます。プレイページでホストするか参加してください。</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Teams work in a multiplayer game. Host or join one on the Play page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>emp_ui_team_turn_on</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>オンにする</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Turn on</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>emp_ui_team_requests</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>参加の申請</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Requests to join</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>emp_ui_team_asks_row</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>{0}が参加を希望しています</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>{0} asks to join</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>emp_ui_team_tools_leader_only</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>リーダーだけが使えます。</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Only the leader of the team can use these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>emp_ui_team_tools_host_off</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>ホストがこのワールドでリーダーの操作をオフにしています。</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>The host turned leader tools off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>emp_ui_team_leader_only_chip</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>リーダーのみ</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Leader only</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>emp_ui_team_joining</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>誰でも参加可</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Anyone may join</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>emp_ui_team_joining_desc</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>オフにすると、リーダーが申請ごとに答えます。</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Off: the leader answers each request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite_any</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>プレイヤーを招待</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Invite a player</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>emp_ui_team_invite_none</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>招待できるチームなしのプレイヤーはいません。</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>No one in the game without a team to invite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>emp_ui_land_where</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>場所：{0}</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>In {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>emp_ui_land_none</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>まだ土地がありません。野原で土地の権利書を読むと手に入ります。</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>No land yet. Read a land deed on a field to claim one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>emp_ui_land_noteam</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>土地を持つには、まずチームを作るか参加してください。</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Found or join a team to hold land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>emp_ui_land_rules_off</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>このワールドでは土地のルールはオフです。</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Land rules are off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>emp_ui_land_leader_decides</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>ルールを変えられるのはリーダーだけです。</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Only the leader changes these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>emp_ui_land_boxes</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>銀行と配達ボックス</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Bank and delivery box</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>emp_ui_land_team_bank</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>チームの銀行</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Team bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>emp_ui_land_bank_line</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>{0}ゴールド、品物{1}個</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>{0} gold, {1} items</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>emp_ui_land_delivery</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>あなたの配達ボックス</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Your delivery box</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>emp_ui_land_items</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>品物{0}個</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>{0} items</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D896"/>
+  <dimension ref="A1:D899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2589,12 +2589,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>これはホストのルールです。変更はすぐ全員に反映されます。</t>
+          <t>これはホストのルールです。変更はプレイ中の全員にすぐ反映されます。</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>These are the host's rules. Changes apply to everyone at once.</t>
+          <t>These are the host's rules. Changes apply at once to every player.</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ワールドを置いておく場所で、誰でもホストになれます。一緒に遊ぶだけなら必要ありません。</t>
+          <t>ワールドを置いておく場所で、どのプレイヤーもホストになれます。一緒に遊ぶだけなら必要ありません。</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Where the world is kept so that any of you can host it. Not needed to play together.</t>
+          <t>Where the world is kept so that any player can host it. Not needed to play together.</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Server info</t>
         </is>
       </c>
     </row>
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>サーバーのルールは Elin Together メニューで読めます。</t>
+          <t>サーバーのルールはマルチプレイメニューで読めます。</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Read the server rules in the Elin Together menu.</t>
+          <t>Read the server rules in the Multiplayer menu.</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>{0}を解散しますか？メンバーは放浪者に戻り、土地は誰のものでもなくなります。</t>
+          <t>{0}を解散しますか？メンバーは放浪者に戻り、土地は持ち主がいなくなります。</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Disband {0}? Its members become Wanderers and its lands nobody's.</t>
+          <t>Disband {0}? Its members become Wanderers and its lands lose their owner.</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>You were put out of {0}.</t>
+          <t>You were removed from {0}.</t>
         </is>
       </c>
     </row>
@@ -13989,12 +13989,12 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>サーバーの案内とルール</t>
+          <t>ホストからの案内とルール</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Server message and rules</t>
+          <t>The host's message and rules</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>サーバー</t>
+          <t>サーバー情報</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Server info</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Anyone may join</t>
+          <t>Open to all</t>
         </is>
       </c>
     </row>
@@ -15570,12 +15570,12 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>オフにすると、リーダーが申請ごとに答えます。</t>
+          <t>オフにすると、リーダーが申請ごとに承認します。</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Off: the leader answers each request.</t>
+          <t>Off: the leader approves each request.</t>
         </is>
       </c>
     </row>
@@ -15780,6 +15780,57 @@
       <c r="D896" t="inlineStr">
         <is>
           <t>{0} items</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_note_title</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>ホストとして使うあなたのルールです。次にホストするゲームに使われます。</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Your rules as host. They are used the next time you host a game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>emp_ui_play_refresh</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>もう一度探す</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Search again</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>emp_ui_land_go_team</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>チームページを開く</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Open the Team page</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15834,6 +15834,23 @@
         </is>
       </c>
     </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_preset_custom</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>自分で選んだルール。下の項目を自由に変更できます。</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Your own mix: change any rule below by hand.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D900"/>
+  <dimension ref="A1:D902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3031,12 +3031,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>デポから世界を取り出してホストする</t>
+          <t>共有ワールドをホストする</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Take the world from the depot and host it</t>
+          <t>Host the shared world</t>
         </is>
       </c>
     </row>
@@ -15851,6 +15851,40 @@
         </is>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>emp_ui_official_title</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>公式サーバー</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Official server</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>emp_ui_official_open</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>開放中、{0}/{1}人</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Open, {0}/{1} players</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15834,6 +15834,40 @@
         </is>
       </c>
     </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_preset_official</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>公開サーバー（公式）</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Public server (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_preset_official</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>公開サーバー向け：誰でも参加でき、各自が自分のキャラクターと物語を持ちます。ワールドの持ち出しや非公開化はできず、チームごとに領地を持ちます。</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>For a server open to everyone: each player has their own characters and story, teams hold their own lands, and the world cannot be copied away or hidden.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D904"/>
+  <dimension ref="A1:D924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15919,6 +15919,346 @@
         </is>
       </c>
     </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_presets</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>プリセット</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Presets</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_joining</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>参加</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Joining</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_together</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>一緒に</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Together</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_host_leaves</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>ホストが抜けたとき</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>When the host leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_friends</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_fallbacks</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>従来ルール</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Fallbacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_time_details</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_comfort</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>快適さ</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Comfort</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_repair</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>修復</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_online</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>オンライン</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_characters</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>キャラクター</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_banned</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>追放</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Banned</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_mods</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Mods</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_depot</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>セーブフォルダ</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Save folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_social</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>フレンドと無視</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Friends and ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_rules</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>ルール</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_how</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>遊び方</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_needs_official</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>公式サーバーが設定</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Set by the official server</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_none</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>このワールドで作られたキャラクターはまだありません。</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>No character has been made in this world yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>emp_ui_banned_none</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>追放されたプレイヤーはいません。</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Nobody is banned.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D924"/>
+  <dimension ref="A1:D925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16259,6 +16259,23 @@
         </is>
       </c>
     </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_adv_title</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>詳細</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D925"/>
+  <dimension ref="A1:D950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16276,6 +16276,431 @@
         </is>
       </c>
     </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_state</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_players</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>プレイヤー</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_host</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>ホスト</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_where</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>現在地</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Now in</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_version</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>バージョン</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_character</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>キャラクター</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_level</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_team</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_ping</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Ping</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Ping</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_role</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_leader</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>リーダー</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_members</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>メンバー</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_joining</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>参加</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Joining</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_bank</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>チーム銀行</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Team bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_bills</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>未払いの税</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Unpaid bills</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_story</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>emp_ui_state_connected</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>接続中</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Connected</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>emp_ui_role_player</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>プレイヤー</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>emp_ui_role_admin</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>emp_ui_role_mod</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>モデレーター</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>emp_ui_role_frozen</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>凍結中</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>emp_ui_role_idle</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>離席中</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Away from the keyboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_pick</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>左のページでプレイヤーを選んでください。</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Pick a player on the left page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_actions</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>emp_ui_team_pick</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>左のページでメンバーを選んでください。</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Pick a member on the left page.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D950"/>
+  <dimension ref="A1:D951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16701,6 +16701,23 @@
         </is>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>emp_ui_play_joining</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>ワールドを受け取っています...</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Receiving the world...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -11254,12 +11254,12 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>「プレイヤーとチームごとの物語」と一緒に：各プレイヤーやチームが戦士、魔術師、盗賊、商人のギルドでも自分の立場を持つ（加入、ランク、貢献、ギルドのクエスト）。チェックした時点の世界のギルドから全員が始める。公式公開サーバーでもオフ。チェックを外す、またはMODなしでセーブを開くと：ホスト自身の物語のギルド。オフ：グループで一つの加入（従来どおり）。</t>
+          <t>「プレイヤーとチームごとの物語」と一緒に：各プレイヤーやチームが戦士、魔術師、盗賊、商人のギルドでも自分の立場を持つ（加入、ランク、貢献、ギルドのクエスト）。チェックした時点の世界のギルドから全員が始める。公式公開サーバーではオン。チェックを外す、またはMODなしでセーブを開くと：ホスト自身の物語のギルド。オフ：グループで一つの加入（従来どおり）。</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>With "Each player or team lives its own story": each player or team also has its own place in the Fighters', Mages', Thieves' and Merchants' guilds (membership, rank, contribution, guild quests). Everyone starts with the guilds the world has when the box is ticked. Off on the official public server too. Unticked, or the save opened without the mod: the guilds of the host's own story. Off: one membership for the group, as before.</t>
+          <t>With "Each player or team lives its own story": each player or team also has its own place in the Fighters', Mages', Thieves' and Merchants' guilds (membership, rank, contribution, guild quests). Everyone starts with the guilds the world has when the box is ticked. On on the official public server. Unticked, or the save opened without the mod: the guilds of the host's own story. Off: one membership for the group, as before.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D951"/>
+  <dimension ref="A1:D954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16718,6 +16718,57 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>emp_travel_map_full</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>このマップは満員です（訪問者10人まで）</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>This map is full (10 visitors at most).</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_stranger_visits</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>他のチームの人もマップを訪問できる</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Strangers may visit a player's map</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_stranger_visits</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>ホストの外でマップを持つプレイヤーが、別のチームのプレイヤーも迎え入れます。土地のルールが先に確認され、訪問者は1人のプレイヤーにつき10人までです。訪問者のキャラクター、バッグ、所持金は本人のアップロードだけが有効で、所持金の増加には1時間あたりの上限があります。オフ：公開サーバーでは、チームの仲間、管理者、「許可」された人だけがマップを共有できます。</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>A player holding a map away from the host also takes in players of other teams. Land rules are checked first, and a map takes 10 visitors at most. A visitor's character, bag and gold are taken only from the visitor's own upload (never from the map's holder), and its gold gain has an hourly cap. Off: on a public server only teammates, admins and players let in with "allow" share a map.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D954"/>
+  <dimension ref="A1:D955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16769,6 +16769,23 @@
         </is>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>emp_chat_flood</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>チャットの書き込みが多すぎます。30秒間ミュートされます。</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>You are typing too fast. Your chat is muted for 30 seconds.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D951"/>
+  <dimension ref="A1:D953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16718,6 +16718,40 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_large_crowds</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>大人数：各プレイヤーには近くのものだけを送る</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Large crowds: send each player only what is near it</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_large_crowds</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>各プレイヤーには、自分のキャラクターの近く（24マス）、仲間、チーム、取引・決闘・戦闘の相手だけを毎回送ります。マップの残りは毎秒1回、マップ全体の確認は4秒ごと。何も消えませんが、遠くのキャラクターはとびとびに動きます。オフ：全員にマップ全体を毎回送ります（従来どおり）。</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Each player is sent at full rate only what is near its character (24 tiles), its companions, its team and whoever it trades, duels or fights with; the rest of the map once a second, and the whole map is checked every 4 seconds. Nothing disappears; far characters move in steps. Off: every player gets the whole map at full rate, as before.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D951"/>
+  <dimension ref="A1:D953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16718,6 +16718,40 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_fast_joins</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>大きな世界の参加と保存を速く</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Fast joins and saves for big worlds</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_fast_joins</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>大きな世界向け：プレイヤーの参加と定期保存でゲームが止まる時間を短くします。世界とマップの写しはゲームの中で作り、その圧縮と送信、保存ファイルの書き込みは横で行います。オフ：すべてゲームの中で行います。</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>For big worlds: a player joining and the periodic save freeze the game for everyone for less time. The copy of the world and of the map is still made in the game; compressing and sending it, and writing the save files, are done beside it. Off: all of it is done in the game.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D959"/>
+  <dimension ref="A1:D960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -16854,6 +16853,23 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>emp_lobby_not_allowed</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>このゲームはホストの Steam フレンドか招待されたプレイヤーのみ参加できます。</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>This game only accepts the host's Steam friends or invited players.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D959"/>
+  <dimension ref="A1:D962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>参加するゲームに足りない Workshop の MOD を、購読せずにダウンロードします。Elin は一度再起動します。</t>
+          <t>参加するゲームに足りない Workshop の Elin MOD を、購読せずにダウンロードします。Elin は一度再起動します。コード（DLL）入りの MOD は下のチェックがあるときだけです。</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Downloads the Workshop mods you lack for the game you join, without subscribing. Elin restarts once.</t>
+          <t>Downloads the Workshop Elin mods you lack for the game you join, without subscribing. Elin restarts once. Mods with code (DLL) only if the box below is ticked.</t>
         </is>
       </c>
     </row>
@@ -16854,6 +16854,57 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_code_mods</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>コードMOD（DLL）も：信頼するホストだけ</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Also code mods (DLL): only for hosts you trust</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_desc_code_mods</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>MOD のコードは、このPCであなたの権限のまま動きます。ホストは Workshop のどの MOD でも指定できます。オフ：コード入りの MOD があるゲームの MOD はダウンロードせず、どの MOD かを伝えます。</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>A mod's code runs on this PC with all your rights, and a host can name any Workshop mod. Off: if the game's mods include code, nothing is downloaded and you are told which mod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_code_refused</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>ゲームのMODを読み込みませんでした：{0} にはコード（DLL）があります。このホストを信頼するときだけ、クライアント設定の「コードMOD（DLL）も」にチェックしてください。</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>The game's mods were not loaded: {0} contains code (DLL). Tick "Also code mods (DLL)" in Client settings only if you trust this host.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D963"/>
+  <dimension ref="A1:D964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -16922,6 +16921,23 @@
         </is>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_diff_line</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>{0}：{1}（おすすめ：{2}）</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>{0}: {1} (recommended: {2})</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D963"/>
+  <dimension ref="A1:D965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11424,12 +11424,14 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>ホストはまだ何も書いていません。</t>
+          <t>ホストはまだ何も書いていません。
+書かれるとここに表示されます。</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>The host hasn't written anything yet.</t>
+          <t>The host hasn't written anything yet.
+It will show up here once they do.</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12140,14 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>あなたはチームに入っていません（放浪者です）。</t>
+          <t>あなたはチームに入っていません（放浪者です）。
+チームを作るか、他のチームに参加しましょう。</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>You are not in a team (you are a Wanderer).</t>
+          <t>You are not in a team (you are a Wanderer).
+Found a team, or join one from the list.</t>
         </is>
       </c>
     </row>
@@ -14363,12 +14367,14 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>まだ何も書いていません。参加者全員に表示されます。</t>
+          <t>まだ何も書いていません。
+書いた内容は参加者全員に表示されます。</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Nothing written yet. Every player can read it here.</t>
+          <t>Nothing written yet.
+What you write is shown to every player.</t>
         </is>
       </c>
     </row>
@@ -15400,12 +15406,14 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>このワールドではチームは無効です。</t>
+          <t>このワールドではチームが無効です。
+チームを使うには、ホストがワールドのルールでオンにします。</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Teams are off in this world.</t>
+          <t>Teams are off in this world.
+The host can turn them on in the World rules.</t>
         </is>
       </c>
     </row>
@@ -15417,12 +15425,14 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>このワールドではチームは無効です。ホストだけがオンにできます。</t>
+          <t>このワールドではチームが無効です。
+オンにできるのはホストだけです。</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Teams are off in this world. Only the host can turn them on.</t>
+          <t>Teams are off in this world.
+Only the host can turn them on.</t>
         </is>
       </c>
     </row>
@@ -15451,12 +15461,12 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>オンにする</t>
+          <t>ワールドのルールでチームをオンにする</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Turn on</t>
+          <t>Turn on teams in World rules</t>
         </is>
       </c>
     </row>
@@ -15638,12 +15648,14 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>まだ土地がありません。野原で土地の権利書を読むと手に入ります。</t>
+          <t>まだ土地がありません。
+野原で土地の権利書を読むと手に入ります。</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>No land yet. Read a land deed on a field to claim one.</t>
+          <t>No land yet.
+Read a land deed on a field to claim one.</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15667,14 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>土地を持つには、まずチームを作るか参加してください。</t>
+          <t>土地を持つには、チームが必要です。
+まずチームを作るか参加してください。</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Found or join a team to hold land.</t>
+          <t>Land belongs to a team.
+Found or join a team to hold some.</t>
         </is>
       </c>
     </row>
@@ -16919,6 +16933,40 @@
       <c r="D963" t="inlineStr">
         <is>
           <t>The game's mods were not loaded: {0} contains code (DLL). Tick "Also code mods (DLL)" in Client settings only if you trust this host.</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>emp_ui_team_leader_short</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>{0}　·　メンバー{1}人</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>{0}  ·  {1} members</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>emp_ui_team_join_short</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>参加</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Join</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D963"/>
+  <dimension ref="A1:D975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16922,6 +16922,210 @@
         </is>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_search</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>名前で検索</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Search by name</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_sort</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>並び順：{0}</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Sort: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_sort_name</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_sort_level</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_sort_ping</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>遅延</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>ping</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_sort_team</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_myteam</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>自分のチーム</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>My team</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_none</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>該当するプレイヤーはいません。</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>No player matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_page</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>{0} / {1}</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>{0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_summary</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>適用中のルール {0} 件、先頭の数件を表示。</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>{0} rules in force, the first ones here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_open</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>ルールを編集</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Edit the rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>emp_ui_help_open</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>開く：{0}</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Open: {0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D978"/>
+  <dimension ref="A1:D996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -17191,6 +17191,312 @@
         </is>
       </c>
     </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_sheets</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>チームメイトのキャラクターシート</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Teammates' character sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_sheets</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>チームメイトの読み取り専用キャラクターシートを、ホストから受け取って開けます。オフ：シートはありません。</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Players can open a read-only character sheet of their teammates, sent by the host. Off: no sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_activity_journal</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>活動の記録</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Activity journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_activity_journal</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>ホストが世界の出来事（チーム結成、決闘の勝利、ボス討伐、死亡、記録）を記録し、「記録」ページに表示します。オフ：記録はありません。</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>The host keeps a journal of the world's events (teams founded, duels won, boss kills, deaths, records), shown on the Journal page. Off: no journal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_banner</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>チームの旗</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Team banners</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_banner</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>各チームのリーダーが紋章と色を選び、チームのページに表示します。オフ：旗はありません。</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Each team gets a banner (an emblem and a colour) chosen by its leader and shown on the Teams page. Off: no banners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_leaderboards</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>ランキング</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Leaderboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_leaderboards</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>ホストがプレイヤーとチームを順位付け（レベル、最深階、決闘の勝利、チームの資産）し、「ランキング」ページに表示します。オフ：順位はありません。</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>The host ranks players and teams (level, deepest floor, duels won, team wealth), shown on the Leaderboards page. Off: no rankings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_journal</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>記録</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>emp_tab_journal</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>記録</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_journal</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>世界の出来事の記録</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>What happened in the world</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_leaderboard</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>ランキング</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Leaderboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>emp_tab_leaderboard</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>ランキング</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Leaderboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_leaderboard</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>プレイヤーとチームの順位</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Rankings of players and teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>emp_ui_journal_off</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>このワールドでは活動の記録はオフです。</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>The activity journal is off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>emp_ui_journal_empty</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>まだ記録はありません。</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Nothing in the journal yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>emp_ui_leaderboard_off</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>このワールドではランキングはオフです。</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Leaderboards are off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>emp_ui_leaderboard_empty</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>まだ順位はありません。</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>No rankings yet.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D996"/>
+  <dimension ref="A1:D1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -17497,6 +17496,125 @@
         </is>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_level</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_deepest</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>最深階</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Deepest floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_duels</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>決闘の勝利</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Duels won</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_wealth</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>チームの資産</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Team wealth</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_you</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_rank</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>{0}位（{1}）</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Rank {0} ({1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_unranked</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>順位なし</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Not ranked</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D996"/>
+  <dimension ref="A1:D997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -17497,6 +17497,23 @@
         </is>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>emp_ui_team_sheet</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>キャラシート</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D996"/>
+  <dimension ref="A1:D1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -17497,6 +17496,227 @@
         </is>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>emp_journal_1</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>{0}がチーム「{1}」を結成した。</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>{0} founded the team {1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>emp_journal_2</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>{0}がチーム「{1}」に加わった。</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>{0} joined the team {1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>emp_journal_3</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>{0}がチーム「{1}」を抜けた。</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>{0} left the team {1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>emp_journal_4</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>{0}が{1}のために土地「{2}」を確保した。</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>{0} claimed the land {2} for {1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>emp_journal_5</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>{1}は不在のため土地{2}か所を失った。</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>{1} lost {2} land(s) after being away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>emp_journal_6</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>{0}が{2}との決闘に勝った。</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>{0} won a duel against {2}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>emp_journal_7</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>{0}が{2}で死んだ。</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>{0} died in {2}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>emp_journal_8</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>{0}が{2}を倒した。</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>{0} defeated {2}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>emp_journal_9</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>{0}が最深記録を更新した：危険度{2}。</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>{0} reached a new record depth: danger {2}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>emp_ui_journal_filter</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>emp_ui_journal_f_all</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>すべて</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>emp_ui_journal_f_team</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>emp_ui_journal_f_mine</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>自分</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1004"/>
+  <dimension ref="A1:D1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -17633,6 +17632,159 @@
         </is>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>チームの旗</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner_tool</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>旗を選ぶ</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner_emblem</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>紋章</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Emblem</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner_color</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>色</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Colour</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>emp_ui_team_lands_map</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>土地の地図</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Land map</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>emp_ui_team_lands_none</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>土地はまだありません</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>No land yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>emp_ui_team_lands_hover</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>点にカーソルを合わせると土地名が出ます</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Hover a dot for the land name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>emp_ui_team_journal</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>チームの記録</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Team journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>emp_ui_team_journal_none</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>まだ何もありません</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1026"/>
+  <dimension ref="A1:D1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18007,6 +18007,24 @@
         </is>
       </c>
     </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner_search</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr"/>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>名前かIDで検索</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Search any item by name or id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -16995,12 +16995,12 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>名前で検索</t>
+          <t>プレイヤーを検索</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Search by name</t>
+          <t>Search a player</t>
         </is>
       </c>
     </row>
@@ -17590,12 +17590,12 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>あなた</t>
+          <t>あなたの順位</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Your rank</t>
         </is>
       </c>
     </row>
@@ -17607,12 +17607,12 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>{0}位（{1}）</t>
+          <t>{1}人中{0}位（{2}）</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Rank {0} ({1})</t>
+          <t>{0} of {1} ({2})</t>
         </is>
       </c>
     </row>
@@ -18013,7 +18013,6 @@
           <t>emp_ui_team_banner_search</t>
         </is>
       </c>
-      <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
           <t>名前かIDで検索</t>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1027"/>
+  <dimension ref="A1:D1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18020,7 +18020,109 @@
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Search any item by name or id</t>
+          <t>Search by name or id</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_community</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>コミュニティ</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>emp_tab_community</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>コミュニティ</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_community</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>世界の記録とランキング</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>The world journal and the leaderboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>emp_ui_lb_board</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>ランキング</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner_items</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>アイテム</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>emp_ui_team_banner_monsters</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>モンスター</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Monsters</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1033"/>
+  <dimension ref="A1:D1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18126,6 +18126,312 @@
         </is>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_layers</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>レイヤー（{0}/{1}）</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Layers ({0}/{1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_add</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>レイヤーを追加</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Add layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_add_close</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>一覧を閉じる</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Close the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_selected</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>選択中のレイヤー：{0}</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Selected layer: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_move</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>移動</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_size</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>大きさ</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_rotate</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>90°回転</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Rotate 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_flip_h</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>左右反転</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Flip horizontally</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_flip_v</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>上下反転</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Flip vertically</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_tint</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>色合い</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Tint</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_tint_none</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_background</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>背景</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Background</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_square</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>四角</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_round</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>丸</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_shield</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>盾</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_undo</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>元に戻す</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Undo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_reset</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_save</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>保存</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1051"/>
+  <dimension ref="A1:D1053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -18432,6 +18431,40 @@
         </is>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>emp_ui_team_tab_team</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>emp_ui_team_tab_emblem</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>エンブレム</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Emblem</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1051"/>
+  <dimension ref="A1:D1070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18432,6 +18432,329 @@
         </is>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_friend</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Steamフレンドの {0} がこのゲームのホストです。参加するには、ElinがこれらのMODをダウンロードして再起動します：</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Your Steam friend {0} hosts this game. To join it, your Elin would download these mods and restart:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_stranger</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>注意：{0} はあなたのSteamフレンドではありません。このホストは、ElinにこれらのMODをダウンロードして再起動するよう求めています：</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Warning: {0} is NOT your Steam friend. This host asks your Elin to download these mods and restart:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_warning</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>MODには有害な内容が含まれることがあります。知っている友達など、信頼できるホストのときだけ受け入れてください。迷ったら「キャンセル」を選んでください。</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Mods can contain harmful content. Accept only if you trust this host, like a friend you know. If in doubt, choose Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_row</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>{0}（作者 {1}、{2} MB）</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>{0} by {1}, {2} MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_code_later</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>（コードの有無はダウンロード後に確認し、あれば再度確認します）</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>(checked for code after the download, you are asked again if it has some)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_code_later_blocked</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>（コードの有無はダウンロード後に確認：あればブロック）</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>(checked for code after the download: blocked if it has some)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_on_pc</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>（このPCにあります）</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>(already on this PC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_has_code</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>コードを含む</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>contains code</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_has_code_blocked</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>コードを含む：ブロック</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>contains code: blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_nothing</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>ダウンロードするものはありません：このゲームのMODだけでElinを再起動します。</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Nothing to download: Elin restarts with only the mods of this game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_code_on</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>「コードMOD（DLL）も」がオンです：MODのコードはあなたの全権限でこのPC上で実行されます。</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>"Also code mods (DLL)" is on: the code of a mod runs on this PC with all your rights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_code_off</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>コードを含むMOD（DLL）はブロックされます（「コードMOD（DLL）も」がオフ）：見つかった場合、これらのMODはどれも読み込まれません。</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Mods with code (DLL) are blocked ("Also code mods (DLL)" is off): if one is found, none of these mods is loaded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_download</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>ダウンロードして再起動</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Download and restart</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_restart</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>これらのMODで再起動</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Restart with them</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_trust</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>このホストを常に信頼：ダウンロードして再起動</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Always trust this host: download and restart</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_without</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>MODなしで参加</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Join without them</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_cancel</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_code_found</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>{0} のゲームのためにダウンロードしたこれらのMODはコードを含みます。Elinの再起動時に、そのコードはあなたの全権限でこのPC上で実行されます：</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>These mods downloaded for the game of {0} contain code. Their code runs on this PC with all your rights when Elin restarts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_ask_code_found_stranger</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>注意：{0} はあなたのSteamフレンドではなく、そのゲームのためにダウンロードしたこれらのMODはコードを含みます。Elinの再起動時に、そのコードはあなたの全権限でこのPC上で実行されます：</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Warning: {0} is NOT your Steam friend, and these mods downloaded for its game contain code. Their code runs on this PC with all your rights when Elin restarts:</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1072"/>
+  <dimension ref="A1:D1075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18789,6 +18789,57 @@
         </is>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_up</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>上へ</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Move up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_down</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>下へ</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Move down</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_remove</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>レイヤーを削除</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Remove the layer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1075"/>
+  <dimension ref="A1:D1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18236,12 +18236,12 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>90°回転</t>
+          <t>45°回転</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Rotate 90°</t>
+          <t>Rotate 45°</t>
         </is>
       </c>
     </row>
@@ -18837,6 +18837,346 @@
       <c r="D1075" t="inlineStr">
         <is>
           <t>Remove the layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_colour1</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>色1</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Colour 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_colour2</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>色2</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Colour 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_shape</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>形</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Shape</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>模様</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_0</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>無地</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_1</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>縦二分割</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Halves (vertical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_2</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>横二分割</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Halves (horizontal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_3</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>四分割</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_4</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>斜め分割</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_5</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>縞</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Stripes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_6</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>山形</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_pattern_7</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>縁取り</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Border</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_banner</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>旗</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_diamond</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>菱形</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_hexagon</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>六角形</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Hexagon</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_opacity</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>不透明度</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Opacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_outline</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>縁取り線</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Outline</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_duplicate</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>複製</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_random</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>ランダム</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_templates</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>ひな形</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Starters</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1095"/>
+  <dimension ref="A1:D1112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -17607,12 +17607,12 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>{1}人中{0}位（{2}）</t>
+          <t>{1}人中{0}位、スコア {2}</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>{0} of {1} ({2})</t>
+          <t>#{0} of {1} players, score {2}</t>
         </is>
       </c>
     </row>
@@ -19177,6 +19177,295 @@
       <c r="D1095" t="inlineStr">
         <is>
           <t>Starters</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>emp_ui_saved_chars_line_alone</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>{0}（Lv {1}）</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>{0} (Lv {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_start</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>まだレイヤーがありません。「レイヤーを追加」でゲームのアイテムやモンスターを選ぶか、左の「ひな形」から始めましょう。</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>No layer yet. Press Add layer to pick any item or monster of the game, or start from Starters on the left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_chat</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_chat</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>みんな、チーム、個人宛てのメッセージ</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Messages: everyone, your team, private</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_off</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>マルチプレイ中にチャットできます。</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Chat works in a multiplayer game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_show</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_all</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>すべて</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_everyone</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_map</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>このマップ</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>This map</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_team</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_private</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_server</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>サーバー</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_to</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>{0} へ</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>To {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_hint</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>メッセージを入力…</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Write a message…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_send</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>送信</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Send</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_empty</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>まだメッセージはありません。</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>No message yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>emp_ui_chat_team_tag</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>{0}（チーム）</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>{0} (team)</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1112"/>
+  <dimension ref="A1:D1120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -19469,6 +19468,142 @@
         </is>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_title</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>称号</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_race_job</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>種族・職業</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Race, job</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_session</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>今回の滞在</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Here for</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_deepest</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>最深階</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Deepest floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>emp_ui_kv_duels</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>決闘の勝利</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Duels won</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>emp_ui_pl_deeds</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>最近の行い</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Recent deeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>emp_ui_time_hm</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>{0}時間{1}分</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>{0} h {1} min</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>emp_ui_time_m</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>{0}分</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>{0} min</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1120"/>
+  <dimension ref="A1:D1131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -19604,6 +19605,193 @@
         </is>
       </c>
     </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>emp_info_status</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>サーバーの状態</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>emp_info_status_off</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>マルチプレイ中に表示されます。</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Shown in a multiplayer game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>emp_info_st_host</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>ホスト</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>emp_info_st_players</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>オンラインのプレイヤー</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Players online</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>emp_info_st_teams</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>emp_info_st_date</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>世界の日付</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>World date</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>emp_info_st_session</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>このセッション</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>This session</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>emp_info_st_ping</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>ping</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Ping</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>emp_info_st_restart</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>再起動まで</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Restart in</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>emp_info_st_mod</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Elin Together</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Elin Together</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>emp_info_st_game</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Elin</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Elin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1112"/>
+  <dimension ref="A1:D1162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -19469,6 +19469,856 @@
         </is>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_market</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>マーケット</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_market</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>プレイヤーが「マーケット」ページに売買の広告（売ります・買います、品物、数量、価格、短いメモ）を出せます。ホストがワールドと一緒に保存します：1人5件まで、各7日間。オフ：マーケットはありません。</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Players post classified ads (selling or looking for an item, a quantity, a price, a short note) on the Market page, kept by the host with the world: 5 ads per player, 7 days each. Off: no market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>emp_ui_tab_market</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>マーケット</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>emp_tab_market</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>マーケット</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_market</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>プレイヤー同士の売買広告</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Classified ads: buy and sell between players</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>emp_ui_market_unplugged</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>マーケットはマルチプレイ中に使えます。</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>The market works in a multiplayer game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>emp_ui_market_off</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>このワールドではマーケットはオフです。</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>The market is off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>emp_ui_market_off_host</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>このワールドではマーケットはオフです。ワールドのルールでオンにできます。</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>The market is off in this world. You can turn it on in the world rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>emp_ui_market_turn_on</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>ルールを開く</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Open the rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>emp_ui_market_board</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>広告</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>emp_ui_market_post</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>広告を出す</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Post an ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>emp_ui_market_show</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>emp_ui_market_filter_all</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>すべて</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>emp_ui_market_selling</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>売ります</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Selling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>emp_ui_market_looking</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>買います</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Looking for</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>emp_ui_market_mine</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>自分の広告</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>emp_ui_market_search</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>品物、プレイヤー、メモで検索…</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Search an item, a player, a note…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>emp_ui_market_loading</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>広告を読み込み中…</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Loading the ads…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>emp_ui_market_empty</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>広告はありません。</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>No ads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>emp_ui_market_price</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>{0} オレン</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>{0} orens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>emp_ui_market_price_ask</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>価格は相談</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Price to discuss</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>emp_ui_market_age_m</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>{0}分前</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>{0} min ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>emp_ui_market_age_h</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>{0}時間前</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>{0} h ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>emp_ui_market_age_d</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>{0}日前</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>{0} d ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>emp_ui_market_message</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>メッセージ</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>emp_ui_market_remove</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>削除</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>emp_ui_market_remove_confirm</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>{0} の広告を削除しますか？</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Remove the ad of {0}?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>emp_ui_market_kind</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>広告の種類</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Ad type</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>emp_ui_market_item</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>品物</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>emp_ui_market_clear</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>選択を外す</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>emp_ui_market_free_text</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>（下に自由に書く）</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>(free text below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>emp_ui_market_text_hint</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>または品物を書く（40文字まで）…</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Or write the item (40 characters max)…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>emp_ui_market_qty</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>emp_ui_market_price_label</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>価格（オレン）</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Price (orens)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>emp_ui_market_note_hint</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>短いメモ（140文字まで、任意）…</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>A short note (140 characters max, optional)…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>emp_ui_market_send</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>emp_ui_market_pick</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>ゲームの品物を選ぶ</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Pick an item of the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>emp_ui_market_count</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>あなたの広告：{0} / {1}</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Your ads: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>emp_ui_market_posted</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>広告を掲載しました。</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Your ad is posted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>emp_ui_market_removed</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>広告を削除しました。</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>The ad is removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_kind</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>広告の種類が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Unknown ad type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_item</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>このゲームにない品物です。</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>This item does not exist in this game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_text</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>品物を選ぶか、40文字までで書いてください。</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Pick an item or write one (40 characters max).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_qty</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>数量は1から9999までです。</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>The quantity goes from 1 to 9999.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_price</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>価格は0から999,999,999オレンまでです。</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>The price goes from 0 to 999,999,999 orens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_note</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>メモは140文字までです。</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>The note is 140 characters at most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_limit</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>広告はすでに5件あります。先に1件削除してください。</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>You have 5 ads already: remove one first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_rate</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>少し待ってから次の広告を出してください（10秒）。</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Wait a little before the next ad (10 seconds).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_gone</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>この広告はもうありません。</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>This ad is gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>emp_ui_market_err_not_yours</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>自分の広告だけ削除できます。</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>You can only remove your own ads.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1112"/>
+  <dimension ref="A1:D1157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -19469,6 +19469,771 @@
         </is>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_mailbox</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>郵便箱</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Mailbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_mailbox</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>プレイヤー同士で手紙（文章、最大5スタックのアイテムとお金）を送れます。オフラインのプレイヤーにも届きます。手紙と中身はホストのワールドのセーブに保管され、30日間受け取られない手紙は差出人に戻ります。オフ：手紙はありません。</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Players send each other letters (a text, up to 5 stacks of items and gold), also to a player who is offline. The host keeps the letters and what they hold in the world save; a letter left unclaimed for 30 days goes back to its sender. Off: no letters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>emp_ui_sub_mail</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>手紙</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_title</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>手紙（未受取 {0}）</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Letters ({0} waiting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_off</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>このワールドでは郵便箱はオフです。</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>The mailbox is off in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_write</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>手紙を書く</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_write_to</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>手紙を書く</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Write a letter</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_asking</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>ホストに問い合わせ中…</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Asking the host…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_none</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>手紙はありません。</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>No letters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_returned_from</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>返送：{0}</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Returned: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_holds</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>{0} スタック、{1} G</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>{0} stacks, {1} gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_date</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_returned_note</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>{0} が30日以内に受け取らなかったため、戻ってきました。</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>{0} did not take it within 30 days: it came back to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_returns_in</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>受け取られないと {0} 日後に差出人に戻ります。</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Goes back to its sender in {0} days if not taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_gold</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>お金</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_take</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>受け取る</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Take</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_delete</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>削除</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_delete_confirm</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>この手紙を削除しますか？</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Delete this letter?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_no_one</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>手紙を送れる相手がいません。</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>There is nobody to write to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_cancel</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_to</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>宛先</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_hint</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>手紙の文章（{0} 文字まで）…</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Your letter (up to {0} characters)…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_have</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>所持 {0}</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>you have {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_items</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>同封するアイテム：{0} / {1}</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Items to send: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_bag_empty</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>送れるアイテムが鞄にありません。</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Nothing in your bag can be sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_add</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>同封</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_remove</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>外す</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>emp_ui_mail_send</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>送る</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Send</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>emp_mail_sent</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>手紙を送りました。</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Letter sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>emp_mail_taken</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>手紙の中身を受け取りました。</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>You took what the letter held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>emp_mail_away</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>ホストのマップにいるときだけ、アイテムやお金を送ったり受け取ったりできます。</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Sending or taking items and gold works only on the host's map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>emp_mail_muted</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>ミュート中は手紙を送れません。</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>You are muted: you cannot send letters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>emp_mail_wait</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>次の手紙まで少し待ってください。</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Wait a moment before sending another letter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>emp_mail_too_long</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>文章が長すぎます（500文字まで）。</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>The text is too long (500 characters at most).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>emp_mail_no_gold</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>そのお金を持っていません。</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>You do not have that much gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>emp_mail_too_many</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>1通に入れられるのは5スタックまでです。</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>A letter holds 5 stacks at most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>emp_mail_no_recipient</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>その相手には手紙を送れません。</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>That player cannot receive letters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>emp_mail_full</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>その相手の郵便箱はいっぱいです（20通）。</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>That player's mailbox is full (20 letters).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>emp_mail_empty</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>空の手紙は送れません。</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>The letter is empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>emp_mail_bad_item</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>そのアイテムは送れないか、もう鞄にありません。</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>An item cannot be sent or is no longer in your bag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>emp_mail_gone</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>その手紙はもうありません。</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>That letter is gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>emp_mail_bag_full</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>鞄に空きが足りません。</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Not enough room in your bag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>emp_mail_broken</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>この手紙の中身を読み込めません。手紙はそのまま残ります。</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>What this letter holds could not be read; the letter is kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>emp_mail_not_empty</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>先に中身を受け取ってください。</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Take what it holds first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>emp_mail_waiting</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>未受取の手紙が {0} 通あります（プレイヤー &gt; 手紙）。</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>You have {0} letters waiting (Players &gt; Mail).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1226"/>
+  <dimension ref="A1:D1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21407,6 +21407,125 @@
         </is>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_team_quest_sharing</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>チームでクエストを共有</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Teammates share quests</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_team_quest_sharing</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>チームのプレイヤーは、チームページのチェックで自分のクエストをチームと共有できます。仲間の日誌に表示され、誰でも進めて報告でき、ゲーム中の仲間全員が報酬を受け取ります。チームと個人クエストが必要です。オフ：クエストは各自のものです。</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>A player in a team can share its own quests with its team (a box on the Team page): they show in its teammates' journals, any of them can advance and turn them in, and every teammate in the game gets the reward. Needs teams and personal quests. Off: each player's quests stay its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>emp_ui_team_share_quests</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>自分のクエストをチームと共有</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Share my quests with my team</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>emp_ui_team_share_quests_desc</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>仲間の日誌に表示され、誰でも報告でき、ゲーム中の仲間全員が報酬を受け取ります。オフにしても、共有済みのクエストは完了まで共有のままです。</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>They show in your teammates' journals, any of them can turn one in, and every teammate in the game gets the reward. Unticked, the quests already shared stay shared until they are done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>emp_team_quest_share_got</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>仲間が「{0}」を報告しました。あなたの分の報酬を受け取りました。</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>A teammate turned in "{0}": you get your share of the reward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>emp_team_quest_share_mail</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>仲間が「{0}」を報告しました。あなたの分の報酬を拠点の郵便に送りました。</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>A teammate turned in "{0}": your share of the reward was sent to the base's mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>emp_team_quest_share_done</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>仲間が「{0}」を報告しました。</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>A teammate turned in "{0}".</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1233"/>
+  <dimension ref="A1:D1235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21526,6 +21526,40 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_mirror</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>左右対称</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Mirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>emp_ui_emblem_unsaved</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>未保存の変更があります。</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Unsaved changes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1235"/>
+  <dimension ref="A1:D1246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9368,12 +9368,12 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>何が起きたかを書くと、ログと最後の30秒の画面と一緒に、GitHubの公開の報告になります。誰でも見られます（Steamの名前とIDを含む）。</t>
+          <t>答えは、ログと最後の30秒の画面と一緒に、GitHubの公開の報告になります。誰でも見られます（Steamの名前を含む）。SteamのID、IPアドレス、Windowsのユーザー名はログから消されます。ゲストの報告には、ホストが許可していればホストのログも付きます。</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Write what happened: it becomes a public report on GitHub with your logs and the last 30 seconds of your screen. Anyone can see it (it shows your Steam name and id).</t>
+          <t>Your answers become a public report on GitHub with your logs and the last 30 seconds of your screen. Anyone can see it (it shows your Steam name). Steam ids, IP addresses and Windows user names are removed from the logs. A guest's report also carries the host's log when the host allows it.</t>
         </is>
       </c>
     </row>
@@ -9385,12 +9385,12 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>何が起きましたか？（何をしていたか、何を期待したか）　Enter：改行、Ctrl+Enter：送信、Esc：キャンセル</t>
+          <t>3つの質問に自分の言葉で答えてください。詳しいほど早く直せます。Enter：改行</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>What happened? (what you were doing, what you expected)   Enter: new line, Ctrl+Enter: send, Esc: cancel</t>
+          <t>Answer the three questions in your own words: the more precise, the sooner it is fixed. Enter: new line</t>
         </is>
       </c>
     </row>
@@ -21560,6 +21560,193 @@
         </is>
       </c>
     </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>emp_ui_report_doing</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>何をしていましたか？</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>What were you doing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>emp_ui_report_happened</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>何が起きましたか？</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>What happened?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>emp_ui_report_expected</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>本来はどうなるはずでしたか？</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>What did you expect?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>emp_ui_report_again</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>もう一度起きますか？</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Does it happen again?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>emp_ui_report_again_yes</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>emp_ui_report_again_no</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>emp_ui_report_again_untried</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>試していない</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Not tried</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>emp_ui_report_need</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>送信するには、各欄に{0}文字以上書いてください：{1}</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>To send, write at least {0} characters in each box: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>emp_ui_report_preparing</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>レポートを作成中…</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Preparing the report…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_share_log_reports</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>不具合レポートにホストのログを付ける</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Share the host's log with bug reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_share_log_reports</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>ゲストが不具合を報告すると、ホストのログの最後（MODのログの直近10分とPlayer.logの最後、最大300KB、ゲストごとに1分に1回）が付きます。報告はGitHubで公開されるため、SteamのID、IPアドレス、Windowsのユーザー名は先に消されます。オフ：ゲストの報告は自分のログだけです。</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>When a guest reports a bug, the end of the host's logs goes with it (the last 10 minutes of the mod's log and the end of Player.log, 300 KB at most, once a minute per guest). The report is public on GitHub: Steam ids, IP addresses and Windows user names are removed first. Off: a guest's report holds only its own logs.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -9455,12 +9455,12 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>★ Elin Together 公式サーバー</t>
+          <t>★ Elin Together 公開サーバー</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>★ Official Elin Together server</t>
+          <t>★ Elin Together public server</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>公式サーバーに参加</t>
+          <t>Elin Together 公開サーバーに参加</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Join the official server</t>
+          <t>Join the Elin Together public server</t>
         </is>
       </c>
     </row>
@@ -9795,12 +9795,12 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>公式サーバーは今は開いていません</t>
+          <t>Elin Together 公開サーバーは今は開いていません</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>The official server is not open right now</t>
+          <t>The Elin Together public server is not open right now</t>
         </is>
       </c>
     </row>
@@ -9812,12 +9812,12 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>公式サーバーではキャラクターの持ち込みはできません</t>
+          <t>Elin Together 公開サーバーではキャラクターの持ち込みはできません</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>The official server does not take imported characters</t>
+          <t>The Elin Together public server does not take imported characters</t>
         </is>
       </c>
     </row>
@@ -10991,12 +10991,12 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>公式サーバーでは常にオン：プレイヤーとチームごと。</t>
+          <t>Elin Together 公開サーバーでは常にオン：プレイヤーとチームごと。</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Always on for the official public server: one for each player and team.</t>
+          <t>Always on for the Elin Together public server: one for each player and team.</t>
         </is>
       </c>
     </row>
@@ -11254,12 +11254,12 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>「プレイヤーとチームごとの物語」と一緒に：各プレイヤーやチームが戦士、魔術師、盗賊、商人のギルドでも自分の立場を持つ（加入、ランク、貢献、ギルドのクエスト）。チェックした時点の世界のギルドから全員が始める。公式公開サーバーではオン。チェックを外す、またはMODなしでセーブを開くと：ホスト自身の物語のギルド。オフ：グループで一つの加入（従来どおり）。</t>
+          <t>「プレイヤーとチームごとの物語」と一緒に：各プレイヤーやチームが戦士、魔術師、盗賊、商人のギルドでも自分の立場を持つ（加入、ランク、貢献、ギルドのクエスト）。チェックした時点の世界のギルドから全員が始める。Elin Together 公開サーバーではオン。チェックを外す、またはMODなしでセーブを開くと：ホスト自身の物語のギルド。オフ：グループで一つの加入（従来どおり）。</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>With "Each player or team lives its own story": each player or team also has its own place in the Fighters', Mages', Thieves' and Merchants' guilds (membership, rank, contribution, guild quests). Everyone starts with the guilds the world has when the box is ticked. On on the official public server. Unticked, or the save opened without the mod: the guilds of the host's own story. Off: one membership for the group, as before.</t>
+          <t>With "Each player or team lives its own story": each player or team also has its own place in the Fighters', Mages', Thieves' and Merchants' guilds (membership, rank, contribution, guild quests). Everyone starts with the guilds the world has when the box is ticked. On on the Elin Together public server. Unticked, or the save opened without the mod: the guilds of the host's own story. Off: one membership for the group, as before.</t>
         </is>
       </c>
     </row>
@@ -14248,12 +14248,12 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>公式サーバーでは使えません</t>
+          <t>Elin Together 公開サーバーでは使えません</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Not available on the official server</t>
+          <t>Not available on the Elin Together public server</t>
         </is>
       </c>
     </row>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>公式サーバー</t>
+          <t>Elin Together 公開サーバー</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Official server</t>
+          <t>Elin Together public server</t>
         </is>
       </c>
     </row>
@@ -15907,12 +15907,12 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>公開サーバー（公式）</t>
+          <t>Elin Together 公開サーバー</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Public server (official)</t>
+          <t>Elin Together public server</t>
         </is>
       </c>
     </row>
@@ -16230,12 +16230,12 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>公式サーバーが設定</t>
+          <t>Elin Together 公開サーバーが設定</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Set by the official server</t>
+          <t>Set by the Elin Together public server</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1246"/>
+  <dimension ref="A1:D1247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21747,6 +21747,23 @@
         </is>
       </c>
     </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_only_server</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>このサーバーは {0} だけで遊びます。参加するため、Elin はあなたの他のMODを外して一度だけ再起動します。他のMODは次にElinを起動したときに戻ります。今すぐ再起動しますか？</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>This server plays with {0} only. Elin will restart once without your other mods to join; they come back the next time you start Elin. Restart now?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1266"/>
+  <dimension ref="A1:D1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22087,6 +22087,23 @@
         </is>
       </c>
     </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>emp_tip_tab_report</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>不具合を開発者に報告</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Tell the developers about a bug</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1267"/>
+  <dimension ref="A1:D1271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22104,6 +22104,74 @@
         </is>
       </c>
     </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_commons_start_land</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>スタート地点はみんなのもの</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>The start land belongs to everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_commons_start_land</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>スタート地点の草原は町のようにみんなのものになります。持ち主はおらず、どのチームも所有できず、税の請求書もありません。ほかの建築ルールにかかわらず、すべてのプレイヤーがそこで建築、採掘、家具の設置と回収ができます。ワールドの拠点（ホストの家）のままで、収納の記録も続きます。オフ：スタート地点は従来どおりホストの拠点です。</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>The start meadow belongs to everyone, like a town: nobody owns it, no team can take it, and it has no tax bill. Every player builds, digs, places and picks up furniture there, whatever the other building rules say. It stays the world's base (the host's home) and the container log still records it. Off: the start land is the host's base, as before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>emp_land_commons</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>共有地</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>The commons</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>emp_ui_land_commons_line</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>{0}：持ち主はいません。すべてのプレイヤーがここで建築できます。</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>{0}: nobody owns it, every player builds there.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1271"/>
+  <dimension ref="A1:D1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22112,12 +22112,12 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>スタート地点はみんなのもの</t>
+          <t>スタート地点とヴェルニースはみんなのもの</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
         <is>
-          <t>The start land belongs to everyone</t>
+          <t>The start land and Vernis belong to everyone</t>
         </is>
       </c>
     </row>
@@ -22129,12 +22129,12 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>スタート地点の草原は町のようにみんなのものになります。持ち主はおらず、どのチームも所有できず、税の請求書もありません。ほかの建築ルールにかかわらず、すべてのプレイヤーがそこで建築、採掘、家具の設置と回収ができます。ワールドの拠点（ホストの家）のままで、収納の記録も続きます。オフ：スタート地点は従来どおりホストの拠点です。</t>
+          <t>スタート地点の草原とヴェルニースは町のようにみんなのものになります。持ち主はおらず、どのチームも所有できず、税の請求書もありません。ほかの建築ルールにかかわらず、すべてのプレイヤーがそこで建築、採掘、家具の設置と回収ができます。草原はワールドの拠点（ホストの家）のままです。ヴェルニースの住人、店、クエストはそのままで、鉱山への入口の周り5マスには誰も建てられません。オフ：スタート地点は従来どおりホストの拠点、ヴェルニースは町のままです。</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
         <is>
-          <t>The start meadow belongs to everyone, like a town: nobody owns it, no team can take it, and it has no tax bill. Every player builds, digs, places and picks up furniture there, whatever the other building rules say. It stays the world's base (the host's home) and the container log still records it. Off: the start land is the host's base, as before.</t>
+          <t>The start meadow and Vernis belong to everyone, like a town: nobody owns them, no team can take them, and they have no tax bill. Every player builds, digs, places and picks up furniture there, whatever the other building rules say. The meadow stays the world's base (the host's home). In Vernis its people, shops and quests go on, and nobody may build within 5 cells of the way down to the mine. Off: the start land is the host's base and Vernis a town, as before.</t>
         </is>
       </c>
     </row>
@@ -22169,6 +22169,23 @@
       <c r="D1271" t="inlineStr">
         <is>
           <t>{0}: nobody owns it, every player builds there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>emp_mine_way</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>ここは鉱山への道です。誰もここに建てることはできません。</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>This is the way to the mine: nobody may build here.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1271"/>
+  <dimension ref="A1:D1275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22172,6 +22172,74 @@
         </is>
       </c>
     </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_client_mods</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>各自が入れても入れなくてもよいMOD</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Mods each player may have or not</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_client_mods</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>MODのID（またはワークショップ番号）をカンマで区切って入力。これらのMODがあってもなくても友人は拒否されず、再起動も求められず、そのコードはMODの確認に含まれません。ゲームデータ（アイテム、キャラ、マップ）を追加しないMOD専用：追加したものは確認に残ります。</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Mod ids (or Workshop numbers), separated by commas. A friend with or without these mods is never refused or asked to restart for them, and their code is left out of the mod check. Only for mods that add no game data (items, characters, maps): what they add still counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_client_mods_hint</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>例：maccha_coffee_somewhat_enhanced_display</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>e.g. maccha_coffee_somewhat_enhanced_display</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_client_mods_none</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
